--- a/stories/archive/arbres/TREE-COL-001.xlsx
+++ b/stories/archive/arbres/TREE-COL-001.xlsx
@@ -696,7 +696,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sami, papa, maman</t>
+          <t>Raphaël, Mila, maman, papa</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>La casserole chante. Raphaël prépare des pommes pour Mila. Il dit bonjour, s'il te plaît, merci, avec le train, le bus ou la voiture.</t>
+          <t>Raphaël veut donner des pommes à Mila. La casserole chante. Il prend un train, un bus ou une voiture. Ils s'installent. Il dit bonjour, s'il te plaît, merci quand il en a besoin. Les pommes sont partagées.</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une goutte glisse le long de la casserole. Ça sent la pomme, toute douce. Le torchon rayé pend près de l'évier. Dehors, le marché parle tout bas. Un rond de soleil pose sur le carrelage. Les chaussons de Raphaël attendent sous la table. La casserole chante un peu, Raphaël. Tu as vu le torchon ? Il est tout rayé. Oui. Il est rouge et blanc. Papa pose des rondelles dans un bol jaune. Le bois de la planche est lisse, un peu humide. En ce moment, Raphaël est dans la cuisine. Il tient une cuillère en bois. Mila va arriver tout à l'heure. On dit bonjour, d'accord ? Bonjour. Et si tu veux une pomme ? S'il te plaît. Bravo. Et après ? Merci. Bonjour. S'il te plaît. Merci. Le train en bois attend sous la table. Le bus rouge est près du tabouret. La petite voiture brille. Mila aime les mots gentils. Toi aussi, tu les connais. Oui, papa. Une pelure de pomme fait un petit colimaçon. Tu es prêt ? Oui, maman.</t>
+          <t>Une goutte glisse le long de la casserole. Ça sent la pomme, toute douce. Le torchon rayé pend près de l'évier. Dehors, le marché parle tout bas. Un rond de soleil pose sur le carrelage. Les chaussons de Raphaël attendent sous la table. La casserole chante un peu, Raphaël. Tu as vu le torchon ? Il est rouge et blanc. Papa pose des rondelles dans un bol jaune. Le bois de la planche est lisse, un peu humide. En ce moment, Raphaël tient une cuillère en bois. Je veux donner des pommes à Mila. Elle arrive tout à l'heure. Tu prends un jouet, en attendant ? Le bol jaune attend au milieu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1345,33 +1345,14 @@
 narrateur|Les chaussons de Raphaël attendent sous la table.
 papa|La casserole chante un peu, Raphaël.
 maman|Tu as vu le torchon ?
-enfant-m|Il est tout rayé.
-maman|Oui.
-maman|Il est rouge et blanc.
+enfant-m|Il est rouge et blanc.
 narrateur|Papa pose des rondelles dans un bol jaune.
 narrateur|Le bois de la planche est lisse, un peu humide.
-narrateur|En ce moment, Raphaël est dans la cuisine.
-narrateur|Il tient une cuillère en bois.
-narrateur|Mila va arriver tout à l'heure.
-maman|On dit bonjour, d'accord ?
-enfant-m|Bonjour.
-papa|Et si tu veux une pomme ?
-enfant-m|S'il te plaît.
-maman|Bravo.
-maman|Et après ?
-enfant-m|Merci.
-papa|Bonjour.
-papa|S'il te plaît.
-papa|Merci.
-narrateur|Le train en bois attend sous la table.
-narrateur|Le bus rouge est près du tabouret.
-narrateur|La petite voiture brille.
-maman|Mila aime les mots gentils.
-papa|Toi aussi, tu les connais.
-enfant-m|Oui, papa.
-narrateur|Une pelure de pomme fait un petit colimaçon.
-maman|Tu es prêt ?
-enfant-m|Oui, maman.</t>
+narrateur|En ce moment, Raphaël tient une cuillère en bois.
+enfant-m|Je veux donner des pommes à Mila.
+maman|Elle arrive tout à l'heure.
+papa|Tu prends un jouet, en attendant ?
+narrateur|Le bol jaune attend au milieu.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1568,10 +1549,9 @@
       <c r="AW3" t="inlineStr">
         <is>
           <t>narrateur|Qu'est-ce que Raphaël prend ?
-maman|Le train, le bus, ou la voiture.</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+narrateur|Le train, le bus, ou la voiture.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1596,7 +1576,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Raphaël prend le train en bois. Les roues font un petit clic sur le carrelage. La porte s'ouvre, tout doux. Mila entre, les joues roses. Bonjour, Mila. Bonjour, Raphaël. Bonjour, Mila. Tu veux une rondelle ? S'il te plaît. Papa tend une pomme, toute lisse. Merci. Merci, papa. Bravo, Raphaël. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Le train reste près du bol jaune.</t>
+          <t>Raphaël prend le train en bois. Les roues font un petit clic sur le carrelage. La porte de la cuisine s'ouvre. Mila entre, les joues roses. Bonjour, Mila. Bonjour, Raphaël. Le train s'arrête près de ses pieds. Tu veux une rondelle, Mila ? S'il te plaît. Papa tend une pomme, toute lisse. Merci. Moi aussi ? Demande. S'il te plaît. Une rondelle froide dans sa main. Merci, papa.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1738,22 +1718,20 @@
         <is>
           <t>narrateur|Raphaël prend le train en bois.
 narrateur|Les roues font un petit clic sur le carrelage.
-narrateur|La porte s'ouvre, tout doux.
+narrateur|La porte de la cuisine s'ouvre.
 narrateur|Mila entre, les joues roses.
 enfant-m|Bonjour, Mila.
 enfant-f|Bonjour, Raphaël.
-maman|Bonjour, Mila.
-papa|Tu veux une rondelle ?
-enfant-m|S'il te plaît.
+narrateur|Le train s'arrête près de ses pieds.
+papa|Tu veux une rondelle, Mila ?
+enfant-f|S'il te plaît.
 narrateur|Papa tend une pomme, toute lisse.
 enfant-f|Merci.
-enfant-m|Merci, papa.
-maman|Bravo, Raphaël.
-maman|Tu as dit les trois mots.
-papa|Bonjour.
-papa|S'il te plaît.
-papa|Merci.
-narrateur|Le train reste près du bol jaune.</t>
+enfant-m|Moi aussi ?
+papa|Demande.
+enfant-m|S'il te plaît.
+narrateur|Une rondelle froide dans sa main.
+enfant-m|Merci, papa.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1785,7 +1763,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>On dit bonjour, s'il te plaît, merci ?</t>
+          <t>Mila arrive. Raphaël dit quoi ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1805,22 +1783,22 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>bonjour | s'il te plaît | merci</t>
+          <t>bonjour | bonjour mila</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Oui, c'est la bonne réponse.</t>
+          <t>Oui.</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Tu étais presque.</t>
+          <t>Il dit bonjour.</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Dis : merci.</t>
+          <t>Dis : bonjour.</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr"/>
@@ -1945,10 +1923,9 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|On dit bonjour, s'il te plaît, merci ?</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Mila arrive. Raphaël dit quoi ?</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1973,7 +1950,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. Bonjour. S'il te plaît. Merci. Raphaël respire, tout calme. Bravo, Raphaël. Tu as fait du bon travail. Merci, papa. On continue, tout doux.</t>
+          <t>Raphaël a dit bonjour. Mila a une rondelle. Le train attend près du bol jaune. On joue encore ? Oui. On s'installe.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2117,18 +2094,13 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui.
-maman|Bonjour.
-maman|S'il te plaît.
-maman|Merci.
-narrateur|Raphaël respire, tout calme.
-papa|Bravo, Raphaël.
-papa|Tu as fait du bon travail.
-enfant-m|Merci, papa.
-maman|On continue, tout doux.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Raphaël a dit bonjour.
+narrateur|Mila a une rondelle.
+narrateur|Le train attend près du bol jaune.
+enfant-m|On joue encore ?
+maman|Oui. On s'installe.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2181,7 +2153,7 @@
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Tom</t>
+          <t>la table</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2191,7 +2163,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Léa</t>
+          <t>la fenêtre</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -2201,7 +2173,7 @@
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>Sami</t>
+          <t>le tabouret</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
@@ -2322,10 +2294,9 @@
       <c r="AW7" t="inlineStr">
         <is>
           <t>narrateur|On va où, dans la cuisine ?
-papa|La table, la fenêtre, ou le tabouret.</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr"/>
+narrateur|La table, la fenêtre, ou le tabouret.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2350,7 +2321,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Raphaël pose le train en bois près de la table. Le bol jaune est au milieu. Mila tire une chaise, tout doux. Bonjour, Mila. Bonjour. Une assiette, Raphaël ? S'il te plaît. L'assiette est ronde, un peu froide. Merci, maman. Bravo. Tu as dit les mots. S'il te plaît. Une pomme. Voilà. Merci d'avoir demandé. Une rondelle brille dans l'assiette. Les mots gentils, à table aussi.</t>
+          <t>Raphaël pose le train près de la table. Le bol jaune est au milieu. Mila tire une chaise, tout doux. Une assiette, Raphaël ? S'il te plaît. L'assiette est ronde, un peu froide. Merci, maman. Il pose une rondelle dans l'assiette de Mila. Merci, Raphaël.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2490,23 +2461,15 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël pose le train en bois près de la table.
+          <t>narrateur|Raphaël pose le train près de la table.
 narrateur|Le bol jaune est au milieu.
 narrateur|Mila tire une chaise, tout doux.
-enfant-m|Bonjour, Mila.
-enfant-f|Bonjour.
 maman|Une assiette, Raphaël ?
 enfant-m|S'il te plaît.
 narrateur|L'assiette est ronde, un peu froide.
 enfant-m|Merci, maman.
-papa|Bravo.
-papa|Tu as dit les mots.
-enfant-f|S'il te plaît.
-enfant-f|Une pomme.
-papa|Voilà.
-papa|Merci d'avoir demandé.
-narrateur|Une rondelle brille dans l'assiette.
-maman|Les mots gentils, à table aussi.</t>
+narrateur|Il pose une rondelle dans l'assiette de Mila.
+enfant-f|Merci, Raphaël.</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -2703,10 +2666,9 @@
       <c r="AW9" t="inlineStr">
         <is>
           <t>narrateur|C'est quel moment ?
-maman|Le matin, après la sieste, ou le soir.</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr"/>
+narrateur|Le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2731,7 +2693,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. Le soleil touche une roue du train, sur la table. Ça sent le lait et la pomme. Raphaël est près de la table, avec le train. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
+          <t>C'est le matin. Le soleil touche une roue du train. Ça sent le lait et la pomme. Encore une rondelle, Mila ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Raphaël fait le tour du bol avec le train.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2872,22 +2834,13 @@
       <c r="AW10" t="inlineStr">
         <is>
           <t>narrateur|C'est le matin.
-narrateur|Le soleil touche une roue du train, sur la table.
+narrateur|Le soleil touche une roue du train.
 narrateur|Ça sent le lait et la pomme.
-narrateur|Raphaël est près de la table, avec le train.
-enfant-m|Bonjour, Mila.
-enfant-f|Bonjour.
-papa|Tu veux encore une rondelle ?
-enfant-m|S'il te plaît.
+papa|Encore une rondelle, Mila ?
+enfant-f|S'il te plaît.
 narrateur|La pomme est froide, un peu sucrée.
-enfant-m|Merci, papa.
-maman|Bravo.
-maman|Tu as dit les trois mots.
-papa|Bonjour.
-papa|S'il te plaît.
-papa|Merci.
-enfant-f|Merci, Raphaël.
-maman|C'est du bon travail.</t>
+enfant-f|Merci, papa.
+narrateur|Raphaël fait le tour du bol avec le train.</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -2919,7 +2872,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu le matin, près de la table. Il a joué avec le train en bois, avec Mila. Le soleil a touché le bol jaune. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
+          <t>Le train s'arrête contre le bol jaune. Terminus, les pommes. Merci pour le voyage. Bonne journée, vous deux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3059,19 +3012,13 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël a vécu le matin, près de la table.
-narrateur|Il a joué avec le train en bois, avec Mila.
-narrateur|Le soleil a touché le bol jaune.
-maman|Tu as dit bonjour.
-papa|Tu as dit s'il te plaît.
-enfant-m|Et merci.
-maman|Bravo, Raphaël.
-maman|Tu as fait du bon travail.
-papa|Bonne journée, mon grand.
+          <t>narrateur|Le train s'arrête contre le bol jaune.
+enfant-m|Terminus, les pommes.
+enfant-f|Merci pour le voyage.
+maman|Bonne journée, vous deux.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3096,7 +3043,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>C'est après la sieste. Le train dort encore sur la table. Ça sent le pain chaud. Raphaël est près de la table, avec le train. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
+          <t>C'est après la sieste. La casserole est encore tiède. Mila bâille, tout petit. On joue tout doux. Raphaël pousse le train sans le bruit des roues. Encore une rondelle ? S'il te plaît, papa. Papa en glisse une. Merci.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3237,22 +3184,14 @@
       <c r="AW12" t="inlineStr">
         <is>
           <t>narrateur|C'est après la sieste.
-narrateur|Le train dort encore sur la table.
-narrateur|Ça sent le pain chaud.
-narrateur|Raphaël est près de la table, avec le train.
-enfant-m|Bonjour, Mila.
-enfant-f|Bonjour.
-papa|Tu veux encore une rondelle ?
-enfant-m|S'il te plaît.
-narrateur|La pomme est froide, un peu sucrée.
-enfant-m|Merci, papa.
-maman|Bravo.
-maman|Tu as dit les trois mots.
-papa|Bonjour.
-papa|S'il te plaît.
-papa|Merci.
-enfant-f|Merci, Raphaël.
-maman|C'est du bon travail.</t>
+narrateur|La casserole est encore tiède.
+narrateur|Mila bâille, tout petit.
+papa|On joue tout doux.
+narrateur|Raphaël pousse le train sans le bruit des roues.
+enfant-f|Encore une rondelle ?
+enfant-m|S'il te plaît, papa.
+narrateur|Papa en glisse une.
+enfant-m|Merci.</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -3284,7 +3223,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu après la sieste, près de la table. Il a joué avec le train en bois, avec Mila. Le pain a senti bon, tout calme. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
+          <t>Le train dort contre l'assiette. Chut. Il fait la sieste aussi. Vous avez bien partagé. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3424,19 +3363,12 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël a vécu après la sieste, près de la table.
-narrateur|Il a joué avec le train en bois, avec Mila.
-narrateur|Le pain a senti bon, tout calme.
-maman|Tu as dit bonjour.
-papa|Tu as dit s'il te plaît.
-enfant-m|Et merci.
-maman|Bravo, Raphaël.
-maman|Tu as fait du bon travail.
-papa|Bonne journée, mon grand.
+          <t>narrateur|Le train dort contre l'assiette.
+enfant-m|Chut. Il fait la sieste aussi.
+maman|Vous avez bien partagé.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3461,7 +3393,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>C'est le soir. Une lampe jaune pose un rond sur la table. Le train brille tout doux. Raphaël est près de la table, avec le train. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
+          <t>C'est le soir. Une lampe éclaire la table. Le marché, dehors, s'est tu. On range bientôt. Raphaël gare le train sous sa chaise. Encore une pomme ? S'il te plaît. La dernière rondelle brille. Merci.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3602,22 +3534,14 @@
       <c r="AW14" t="inlineStr">
         <is>
           <t>narrateur|C'est le soir.
-narrateur|Une lampe jaune pose un rond sur la table.
-narrateur|Le train brille tout doux.
-narrateur|Raphaël est près de la table, avec le train.
-enfant-m|Bonjour, Mila.
-enfant-f|Bonjour.
-papa|Tu veux encore une rondelle ?
+narrateur|Une lampe éclaire la table.
+narrateur|Le marché, dehors, s'est tu.
+maman|On range bientôt.
+narrateur|Raphaël gare le train sous sa chaise.
+enfant-f|Encore une pomme ?
 enfant-m|S'il te plaît.
-narrateur|La pomme est froide, un peu sucrée.
-enfant-m|Merci, papa.
-maman|Bravo.
-maman|Tu as dit les trois mots.
-papa|Bonjour.
-papa|S'il te plaît.
-papa|Merci.
-enfant-f|Merci, Raphaël.
-maman|C'est du bon travail.</t>
+narrateur|La dernière rondelle brille.
+enfant-f|Merci.</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
@@ -3649,7 +3573,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu le soir, près de la table. Il a joué avec le train en bois, avec Mila. La lampe a fait un rond doux. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
+          <t>Le bol jaune est vide. Le train est au garage. À demain, Mila. À demain. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3789,19 +3713,13 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël a vécu le soir, près de la table.
-narrateur|Il a joué avec le train en bois, avec Mila.
-narrateur|La lampe a fait un rond doux.
-maman|Tu as dit bonjour.
-papa|Tu as dit s'il te plaît.
-enfant-m|Et merci.
-maman|Bravo, Raphaël.
-maman|Tu as fait du bon travail.
-papa|Bonne journée, mon grand.
+          <t>narrateur|Le bol jaune est vide.
+papa|Le train est au garage.
+enfant-m|À demain, Mila.
+enfant-f|À demain.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3826,7 +3744,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Raphaël va près de la fenêtre, avec le train en bois. La vitre est un peu floue. Mila trace un petit rond du doigt. Bonjour, Mila. Bonjour. Tu veux le torchon, pour la vitre ? S'il te plaît. Le torchon est doux, un peu épais. Merci, papa. Bravo, Raphaël. Merci. Je vois le marché. On dit les mots, même près de la fenêtre. Bonjour. S'il te plaît. Merci. Un oiseau passe derrière la vitre.</t>
+          <t>Raphaël va près de la fenêtre, avec le train. La vitre est un peu floue. Mila trace un petit rond du doigt. Le torchon, pour la vitre ? S'il te plaît. Le torchon est doux, un peu épais. Merci, papa. Il essuie un rond. Le marché apparaît. Je vois le stand des pommes.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3966,23 +3884,15 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël va près de la fenêtre, avec le train en bois.
+          <t>narrateur|Raphaël va près de la fenêtre, avec le train.
 narrateur|La vitre est un peu floue.
 narrateur|Mila trace un petit rond du doigt.
-enfant-m|Bonjour, Mila.
-enfant-f|Bonjour.
-papa|Tu veux le torchon, pour la vitre ?
+papa|Le torchon, pour la vitre ?
 enfant-m|S'il te plaît.
 narrateur|Le torchon est doux, un peu épais.
 enfant-m|Merci, papa.
-maman|Bravo, Raphaël.
-enfant-f|Merci.
-enfant-f|Je vois le marché.
-maman|On dit les mots, même près de la fenêtre.
-papa|Bonjour.
-papa|S'il te plaît.
-papa|Merci.
-narrateur|Un oiseau passe derrière la vitre.</t>
+narrateur|Il essuie un rond. Le marché apparaît.
+enfant-f|Je vois le stand des pommes.</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
@@ -4179,10 +4089,9 @@
       <c r="AW17" t="inlineStr">
         <is>
           <t>narrateur|C'est quel moment ?
-maman|Le matin, après la sieste, ou le soir.</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr"/>
+narrateur|Le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4207,7 +4116,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. La vitre est froide sous le doigt. Le train attend près de la fenêtre. Raphaël est près de la fenêtre, avec le train. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
+          <t>C'est le matin. Le soleil chauffe la vitre. Raphaël pose le train sur le rebord. Une rondelle, en regardant ? S'il te plaît. Mila mange, les yeux dehors. Merci. Mon train va au marché.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4348,22 +4257,13 @@
       <c r="AW18" t="inlineStr">
         <is>
           <t>narrateur|C'est le matin.
-narrateur|La vitre est froide sous le doigt.
-narrateur|Le train attend près de la fenêtre.
-narrateur|Raphaël est près de la fenêtre, avec le train.
-enfant-m|Bonjour, Mila.
-enfant-f|Bonjour.
-papa|Tu veux encore une rondelle ?
-enfant-m|S'il te plaît.
-narrateur|La pomme est froide, un peu sucrée.
-enfant-m|Merci, papa.
-maman|Bravo.
-maman|Tu as dit les trois mots.
-papa|Bonjour.
-papa|S'il te plaît.
-papa|Merci.
-enfant-f|Merci, Raphaël.
-maman|C'est du bon travail.</t>
+narrateur|Le soleil chauffe la vitre.
+narrateur|Raphaël pose le train sur le rebord.
+maman|Une rondelle, en regardant ?
+enfant-f|S'il te plaît.
+narrateur|Mila mange, les yeux dehors.
+enfant-f|Merci.
+enfant-m|Mon train va au marché.</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -4395,7 +4295,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu le matin, près de la fenêtre. Il a joué avec le train en bois, avec Mila. Le soleil a touché le bol jaune. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
+          <t>Un oiseau passe derrière la vitre. Arrêt marché. Vous avez bien regardé ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4535,19 +4435,12 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël a vécu le matin, près de la fenêtre.
-narrateur|Il a joué avec le train en bois, avec Mila.
-narrateur|Le soleil a touché le bol jaune.
-maman|Tu as dit bonjour.
-papa|Tu as dit s'il te plaît.
-enfant-m|Et merci.
-maman|Bravo, Raphaël.
-maman|Tu as fait du bon travail.
-papa|Bonne journée, mon grand.
+          <t>narrateur|Un oiseau passe derrière la vitre.
+enfant-m|Arrêt marché.
+papa|Vous avez bien regardé ensemble.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4572,7 +4465,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>C'est après la sieste. Un rayon paresseux traverse la fenêtre. Le train est tiède. Raphaël est près de la fenêtre, avec le train. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
+          <t>C'est après la sieste. La lumière est douce, un peu jaune. Raphaël pousse le train le long du rebord. Il fait moins de bruit. Une rondelle calme ? S'il te plaît. Merci.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4713,22 +4606,12 @@
       <c r="AW20" t="inlineStr">
         <is>
           <t>narrateur|C'est après la sieste.
-narrateur|Un rayon paresseux traverse la fenêtre.
-narrateur|Le train est tiède.
-narrateur|Raphaël est près de la fenêtre, avec le train.
-enfant-m|Bonjour, Mila.
-enfant-f|Bonjour.
-papa|Tu veux encore une rondelle ?
+narrateur|La lumière est douce, un peu jaune.
+narrateur|Raphaël pousse le train le long du rebord.
+enfant-f|Il fait moins de bruit.
+papa|Une rondelle calme ?
 enfant-m|S'il te plaît.
-narrateur|La pomme est froide, un peu sucrée.
-enfant-m|Merci, papa.
-maman|Bravo.
-maman|Tu as dit les trois mots.
-papa|Bonjour.
-papa|S'il te plaît.
-papa|Merci.
-enfant-f|Merci, Raphaël.
-maman|C'est du bon travail.</t>
+enfant-m|Merci.</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -4760,7 +4643,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu après la sieste, près de la fenêtre. Il a joué avec le train en bois, avec Mila. Le pain a senti bon, tout calme. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
+          <t>Le train s'arrête contre le bois de la fenêtre. Il dort au soleil. On reste encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4900,19 +4783,12 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël a vécu après la sieste, près de la fenêtre.
-narrateur|Il a joué avec le train en bois, avec Mila.
-narrateur|Le pain a senti bon, tout calme.
-maman|Tu as dit bonjour.
-papa|Tu as dit s'il te plaît.
-enfant-m|Et merci.
-maman|Bravo, Raphaël.
-maman|Tu as fait du bon travail.
-papa|Bonne journée, mon grand.
+          <t>narrateur|Le train s'arrête contre le bois de la fenêtre.
+enfant-f|Il dort au soleil.
+maman|On reste encore un peu.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4937,7 +4813,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>C'est le soir. Dehors, le marché s'est tu. Le train repose près de la vitre sombre. Raphaël est près de la fenêtre, avec le train. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
+          <t>C'est le soir. La vitre devient sombre. Des lampes s'allument au marché. On dit au revoir à la rue. Raphaël descend le train du rebord. Encore une pomme ? S'il te plaît, on demande. S'il te plaît. Merci.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -5078,22 +4954,14 @@
       <c r="AW22" t="inlineStr">
         <is>
           <t>narrateur|C'est le soir.
-narrateur|Dehors, le marché s'est tu.
-narrateur|Le train repose près de la vitre sombre.
-narrateur|Raphaël est près de la fenêtre, avec le train.
-enfant-m|Bonjour, Mila.
-enfant-f|Bonjour.
-papa|Tu veux encore une rondelle ?
-enfant-m|S'il te plaît.
-narrateur|La pomme est froide, un peu sucrée.
-enfant-m|Merci, papa.
-maman|Bravo.
-maman|Tu as dit les trois mots.
-papa|Bonjour.
-papa|S'il te plaît.
-papa|Merci.
-enfant-f|Merci, Raphaël.
-maman|C'est du bon travail.</t>
+narrateur|La vitre devient sombre.
+narrateur|Des lampes s'allument au marché.
+maman|On dit au revoir à la rue.
+narrateur|Raphaël descend le train du rebord.
+enfant-f|Encore une pomme ?
+papa|S'il te plaît, on demande.
+enfant-f|S'il te plaît.
+enfant-f|Merci.</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
@@ -5125,7 +4993,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu le soir, près de la fenêtre. Il a joué avec le train en bois, avec Mila. La lampe a fait un rond doux. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
+          <t>Le train rentre dans la gare, sous la table. Les lampes, c'est fini. À demain, le marché. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5265,19 +5133,12 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël a vécu le soir, près de la fenêtre.
-narrateur|Il a joué avec le train en bois, avec Mila.
-narrateur|La lampe a fait un rond doux.
-maman|Tu as dit bonjour.
-papa|Tu as dit s'il te plaît.
-enfant-m|Et merci.
-maman|Bravo, Raphaël.
-maman|Tu as fait du bon travail.
-papa|Bonne journée, mon grand.
+          <t>narrateur|Le train rentre dans la gare, sous la table.
+enfant-m|Les lampes, c'est fini.
+papa|À demain, le marché.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5302,7 +5163,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Raphaël glisse le train en bois près du tabouret. Le tabouret est bas, en bois clair. Mila s'assoit, les pieds qui balancent. Bonjour, Mila. Bonjour. Tu veux le tabouret, Raphaël ? S'il te plaît. Tu peux. Merci. Raphaël pose une main sur le bois lisse. Bravo. Tu as demandé. Merci, Mila. Les trois mots, même pour un tabouret. Bonjour. S'il te plaît. Merci. Le tabouret fait un tout petit craquement.</t>
+          <t>Raphaël glisse le train près du tabouret. Le tabouret est bas, en bois clair. Mila s'assoit, les pieds qui balancent. Je peux le tabouret, après ? S'il te plaît, tu attends. D'accord. Il pose le bol jaune sur les genoux de Mila. Merci. Le tabouret fait un tout petit craquement.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5442,23 +5303,14 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël glisse le train en bois près du tabouret.
+          <t>narrateur|Raphaël glisse le train près du tabouret.
 narrateur|Le tabouret est bas, en bois clair.
 narrateur|Mila s'assoit, les pieds qui balancent.
-enfant-m|Bonjour, Mila.
-enfant-f|Bonjour.
-maman|Tu veux le tabouret, Raphaël ?
-enfant-m|S'il te plaît.
-enfant-f|Tu peux.
+enfant-m|Je peux le tabouret, après ?
+enfant-f|S'il te plaît, tu attends.
+enfant-m|D'accord.
+narrateur|Il pose le bol jaune sur les genoux de Mila.
 enfant-f|Merci.
-narrateur|Raphaël pose une main sur le bois lisse.
-papa|Bravo.
-papa|Tu as demandé.
-enfant-m|Merci, Mila.
-maman|Les trois mots, même pour un tabouret.
-papa|Bonjour.
-papa|S'il te plaît.
-papa|Merci.
 narrateur|Le tabouret fait un tout petit craquement.</t>
         </is>
       </c>
@@ -5656,10 +5508,9 @@
       <c r="AW25" t="inlineStr">
         <is>
           <t>narrateur|C'est quel moment ?
-maman|Le matin, après la sieste, ou le soir.</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr"/>
+narrateur|Le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5684,7 +5535,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. Le tabouret est un peu froid. Le train passe entre les pieds de Mila. Raphaël est près de le tabouret, avec le train. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
+          <t>C'est le matin. Le soleil touche les pieds de Mila. Raphaël fait le tour du tabouret avec le train. Une rondelle, du haut du tabouret ? S'il te plaît. Merci. Mon tour ? Oui. Merci d'avoir attendu.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5825,22 +5676,13 @@
       <c r="AW26" t="inlineStr">
         <is>
           <t>narrateur|C'est le matin.
-narrateur|Le tabouret est un peu froid.
-narrateur|Le train passe entre les pieds de Mila.
-narrateur|Raphaël est près de le tabouret, avec le train.
-enfant-m|Bonjour, Mila.
-enfant-f|Bonjour.
-papa|Tu veux encore une rondelle ?
-enfant-m|S'il te plaît.
-narrateur|La pomme est froide, un peu sucrée.
-enfant-m|Merci, papa.
-maman|Bravo.
-maman|Tu as dit les trois mots.
-papa|Bonjour.
-papa|S'il te plaît.
-papa|Merci.
-enfant-f|Merci, Raphaël.
-maman|C'est du bon travail.</t>
+narrateur|Le soleil touche les pieds de Mila.
+narrateur|Raphaël fait le tour du tabouret avec le train.
+papa|Une rondelle, du haut du tabouret ?
+enfant-f|S'il te plaît.
+enfant-f|Merci.
+enfant-m|Mon tour ?
+enfant-f|Oui. Merci d'avoir attendu.</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
@@ -5872,7 +5714,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu le matin, près de le tabouret. Il a joué avec le train en bois, avec Mila. Le soleil a touché le bol jaune. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
+          <t>Raphaël s'assoit. Le train monte avec lui. Vous avez attendu chacun votre tour. Les pommes aussi. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -6012,19 +5854,12 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël a vécu le matin, près de le tabouret.
-narrateur|Il a joué avec le train en bois, avec Mila.
-narrateur|Le soleil a touché le bol jaune.
-maman|Tu as dit bonjour.
-papa|Tu as dit s'il te plaît.
-enfant-m|Et merci.
-maman|Bravo, Raphaël.
-maman|Tu as fait du bon travail.
-papa|Bonne journée, mon grand.
+          <t>narrateur|Raphaël s'assoit. Le train monte avec lui.
+maman|Vous avez attendu chacun votre tour.
+enfant-m|Les pommes aussi.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -6049,7 +5884,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>C'est après la sieste. Le tabouret a gardé un peu de chaleur. Le train fait clic, tout bas. Raphaël est près de le tabouret, avec le train. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
+          <t>C'est après la sieste. Mila pose la tête un instant. Raphaël arrête le train contre un pied du tabouret. Tout doux. Une rondelle, s'il te plaît. Papa en pose deux, tout près. Merci. Une pour Mila.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -6190,22 +6025,12 @@
       <c r="AW28" t="inlineStr">
         <is>
           <t>narrateur|C'est après la sieste.
-narrateur|Le tabouret a gardé un peu de chaleur.
-narrateur|Le train fait clic, tout bas.
-narrateur|Raphaël est près de le tabouret, avec le train.
-enfant-m|Bonjour, Mila.
-enfant-f|Bonjour.
-papa|Tu veux encore une rondelle ?
-enfant-m|S'il te plaît.
-narrateur|La pomme est froide, un peu sucrée.
-enfant-m|Merci, papa.
-maman|Bravo.
-maman|Tu as dit les trois mots.
-papa|Bonjour.
-papa|S'il te plaît.
-papa|Merci.
-enfant-f|Merci, Raphaël.
-maman|C'est du bon travail.</t>
+narrateur|Mila pose la tête un instant.
+narrateur|Raphaël arrête le train contre un pied du tabouret.
+maman|Tout doux.
+enfant-m|Une rondelle, s'il te plaît.
+narrateur|Papa en pose deux, tout près.
+enfant-m|Merci. Une pour Mila.</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
@@ -6237,7 +6062,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu après la sieste, près de le tabouret. Il a joué avec le train en bois, avec Mila. Le pain a senti bon, tout calme. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
+          <t>Mila ouvre les yeux. Merci. Elle était pour moi. Le train a attendu aussi. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6377,19 +6202,12 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël a vécu après la sieste, près de le tabouret.
-narrateur|Il a joué avec le train en bois, avec Mila.
-narrateur|Le pain a senti bon, tout calme.
-maman|Tu as dit bonjour.
-papa|Tu as dit s'il te plaît.
-enfant-m|Et merci.
-maman|Bravo, Raphaël.
-maman|Tu as fait du bon travail.
-papa|Bonne journée, mon grand.
+          <t>narrateur|Mila ouvre les yeux.
+enfant-f|Merci. Elle était pour moi.
+papa|Le train a attendu aussi.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6414,7 +6232,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>C'est le soir. Le tabouret craque, tout petit. Le train rentre sous la chaise. Raphaël est près de le tabouret, avec le train. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
+          <t>C'est le soir. L'ombre du tabouret s'allonge. Raphaël gare le train dessous. Je descends ? Oui. Merci, Mila. Une dernière rondelle ? S'il te plaît. Merci.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6555,22 +6373,13 @@
       <c r="AW30" t="inlineStr">
         <is>
           <t>narrateur|C'est le soir.
-narrateur|Le tabouret craque, tout petit.
-narrateur|Le train rentre sous la chaise.
-narrateur|Raphaël est près de le tabouret, avec le train.
-enfant-m|Bonjour, Mila.
-enfant-f|Bonjour.
-papa|Tu veux encore une rondelle ?
+narrateur|L'ombre du tabouret s'allonge.
+narrateur|Raphaël gare le train dessous.
+enfant-f|Je descends ?
+enfant-m|Oui. Merci, Mila.
+maman|Une dernière rondelle ?
 enfant-m|S'il te plaît.
-narrateur|La pomme est froide, un peu sucrée.
-enfant-m|Merci, papa.
-maman|Bravo.
-maman|Tu as dit les trois mots.
-papa|Bonjour.
-papa|S'il te plaît.
-papa|Merci.
-enfant-f|Merci, Raphaël.
-maman|C'est du bon travail.</t>
+enfant-m|Merci.</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
@@ -6602,7 +6411,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu le soir, près de le tabouret. Il a joué avec le train en bois, avec Mila. La lampe a fait un rond doux. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
+          <t>Le tabouret est vide. Le train dort en dessous. Vous avez partagé le siège et les pommes. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6742,19 +6551,12 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël a vécu le soir, près de le tabouret.
-narrateur|Il a joué avec le train en bois, avec Mila.
-narrateur|La lampe a fait un rond doux.
-maman|Tu as dit bonjour.
-papa|Tu as dit s'il te plaît.
-enfant-m|Et merci.
-maman|Bravo, Raphaël.
-maman|Tu as fait du bon travail.
-papa|Bonne journée, mon grand.
+          <t>narrateur|Le tabouret est vide.
+narrateur|Le train dort en dessous.
+papa|Vous avez partagé le siège et les pommes.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6779,7 +6581,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Raphaël prend le bus rouge. Dehors, un vrai bus passe, tout bas. Mila pousse la porte de la cuisine. Bonjour, Mila. Bonjour. Bonjour, Mila. Raphaël veut le torchon rayé. S'il te plaît. Voilà le torchon. Merci, maman. Merci. Bravo. Tu as demandé, puis remercié. On dit aussi bonjour. Bonjour. Le bus rouge attend près du tabouret.</t>
+          <t>Raphaël prend le bus rouge. Dehors, un vrai bus passe, tout bas. Mila pousse la porte de la cuisine. Bonjour, Mila. Bonjour. Raphaël veut essuyer une miette. Le torchon, s'il te plaît. Voilà le torchon. Merci, maman. Il essuie le rebord du bol. Tu veux une rondelle ? S'il te plaît. Merci.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6924,17 +6726,14 @@
 narrateur|Mila pousse la porte de la cuisine.
 enfant-m|Bonjour, Mila.
 enfant-f|Bonjour.
-papa|Bonjour, Mila.
-narrateur|Raphaël veut le torchon rayé.
-enfant-m|S'il te plaît.
+narrateur|Raphaël veut essuyer une miette.
+enfant-m|Le torchon, s'il te plaît.
 maman|Voilà le torchon.
 enfant-m|Merci, maman.
-enfant-f|Merci.
-maman|Bravo.
-maman|Tu as demandé, puis remercié.
-papa|On dit aussi bonjour.
-enfant-m|Bonjour.
-narrateur|Le bus rouge attend près du tabouret.</t>
+narrateur|Il essuie le rebord du bol.
+papa|Tu veux une rondelle ?
+enfant-m|S'il te plaît.
+enfant-m|Merci.</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
@@ -6981,27 +6780,27 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>bonjour</t>
+          <t>s'il te plaît</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>bonjour | s'il te plaît | merci</t>
+          <t>s'il te plaît | sil te plait | s'il vous plaît</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>Oui, c'est la bonne réponse.</t>
+          <t>Oui.</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>Tu étais presque.</t>
+          <t>Il dit s'il te plaît.</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>Dis : merci.</t>
+          <t>Dis : s'il te plaît.</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr"/>
@@ -7122,11 +6921,9 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël veut le torchon.
-narrateur|Que dit-il ?</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr"/>
+          <t>narrateur|Raphaël veut le torchon. Que dit-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -7151,7 +6948,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. On dit s'il te plaît. Et bonjour. Et merci. Raphaël tient le torchon rayé. Bravo. Tu as demandé gentiment. S'il te plaît. C'est ça.</t>
+          <t>Raphaël a dit s'il te plaît. Le torchon rayé est dans sa main. Le bus rouge attend près du tabouret. On monte ? On s'installe d'abord.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -7295,18 +7092,13 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui.
-papa|On dit s'il te plaît.
-maman|Et bonjour.
-maman|Et merci.
-narrateur|Raphaël tient le torchon rayé.
-papa|Bravo.
-papa|Tu as demandé gentiment.
-enfant-m|S'il te plaît.
-maman|C'est ça.</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr"/>
+          <t>narrateur|Raphaël a dit s'il te plaît.
+narrateur|Le torchon rayé est dans sa main.
+narrateur|Le bus rouge attend près du tabouret.
+enfant-f|On monte ?
+maman|On s'installe d'abord.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7359,7 +7151,7 @@
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>Tom</t>
+          <t>la table</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -7369,7 +7161,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Léa</t>
+          <t>la fenêtre</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -7379,7 +7171,7 @@
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>Sami</t>
+          <t>le tabouret</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
@@ -7500,10 +7292,9 @@
       <c r="AW35" t="inlineStr">
         <is>
           <t>narrateur|On va où, dans la cuisine ?
-papa|La table, la fenêtre, ou le tabouret.</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr"/>
+narrateur|La table, la fenêtre, ou le tabouret.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7528,7 +7319,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Raphaël pose le bus rouge près de la table. Le bol jaune est au milieu. Mila tire une chaise, tout doux. Bonjour, Mila. Bonjour. Une assiette, Raphaël ? S'il te plaît. L'assiette est ronde, un peu froide. Merci, maman. Bravo. Tu as dit les mots. S'il te plaît. Une pomme. Voilà. Merci d'avoir demandé. Une rondelle brille dans l'assiette. Les mots gentils, à table aussi.</t>
+          <t>Raphaël pose le bus rouge près de la table. Le bol jaune est au milieu. Mila tire une chaise. Arrêt table. Deux assiettes ? S'il te plaît. Les assiettes font un petit toc. Merci. Il glisse une rondelle vers Mila. Merci. Ticket pomme.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7670,21 +7461,14 @@
         <is>
           <t>narrateur|Raphaël pose le bus rouge près de la table.
 narrateur|Le bol jaune est au milieu.
-narrateur|Mila tire une chaise, tout doux.
-enfant-m|Bonjour, Mila.
-enfant-f|Bonjour.
-maman|Une assiette, Raphaël ?
+narrateur|Mila tire une chaise.
+enfant-m|Arrêt table.
+maman|Deux assiettes ?
 enfant-m|S'il te plaît.
-narrateur|L'assiette est ronde, un peu froide.
-enfant-m|Merci, maman.
-papa|Bravo.
-papa|Tu as dit les mots.
-enfant-f|S'il te plaît.
-enfant-f|Une pomme.
-papa|Voilà.
-papa|Merci d'avoir demandé.
-narrateur|Une rondelle brille dans l'assiette.
-maman|Les mots gentils, à table aussi.</t>
+narrateur|Les assiettes font un petit toc.
+enfant-m|Merci.
+narrateur|Il glisse une rondelle vers Mila.
+enfant-f|Merci. Ticket pomme.</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
@@ -7881,10 +7665,9 @@
       <c r="AW37" t="inlineStr">
         <is>
           <t>narrateur|C'est quel moment ?
-maman|Le matin, après la sieste, ou le soir.</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr"/>
+narrateur|Le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7909,7 +7692,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. Le bus rouge est sur la table, près du bol. Une miette de pain brille. Raphaël est près de la table, avec le bus rouge. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
+          <t>C'est le matin. Dehors, le vrai bus klaxonne, tout loin. Raphaël ouvre la porte du bus rouge. On charge les pommes ? S'il te plaît, une pour Mila. Papa pose deux rondelles sur les sièges. Merci. On part.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -8050,22 +7833,12 @@
       <c r="AW38" t="inlineStr">
         <is>
           <t>narrateur|C'est le matin.
-narrateur|Le bus rouge est sur la table, près du bol.
-narrateur|Une miette de pain brille.
-narrateur|Raphaël est près de la table, avec le bus rouge.
-enfant-m|Bonjour, Mila.
-enfant-f|Bonjour.
-papa|Tu veux encore une rondelle ?
-enfant-m|S'il te plaît.
-narrateur|La pomme est froide, un peu sucrée.
-enfant-m|Merci, papa.
-maman|Bravo.
-maman|Tu as dit les trois mots.
-papa|Bonjour.
-papa|S'il te plaît.
-papa|Merci.
-enfant-f|Merci, Raphaël.
-maman|C'est du bon travail.</t>
+narrateur|Dehors, le vrai bus klaxonne, tout loin.
+narrateur|Raphaël ouvre la porte du bus rouge.
+papa|On charge les pommes ?
+enfant-m|S'il te plaît, une pour Mila.
+narrateur|Papa pose deux rondelles sur les sièges.
+enfant-f|Merci. On part.</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
@@ -8097,7 +7870,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu le matin, près de la table. Il a joué avec le bus rouge, avec Mila. Le soleil a touché le bol jaune. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
+          <t>Le bus fait le tour de la table. Prochain arrêt : le bol. Vous avez bien chargé. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -8237,19 +8010,12 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël a vécu le matin, près de la table.
-narrateur|Il a joué avec le bus rouge, avec Mila.
-narrateur|Le soleil a touché le bol jaune.
-maman|Tu as dit bonjour.
-papa|Tu as dit s'il te plaît.
-enfant-m|Et merci.
-maman|Bravo, Raphaël.
-maman|Tu as fait du bon travail.
-papa|Bonne journée, mon grand.
+          <t>narrateur|Le bus fait le tour de la table.
+enfant-m|Prochain arrêt : le bol.
+maman|Vous avez bien chargé.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -8274,7 +8040,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>C'est après la sieste. Le bus rouge a glissé vers l'assiette. La nappe est un peu chaude. Raphaël est près de la table, avec le bus rouge. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
+          <t>C'est après la sieste. Le bus rouge avance tout lentement. Les voyageurs ont sommeil. Une rondelle calme ? S'il te plaît. Merci. Raphaël ferme la porte du bus, tout doux.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -8415,22 +8181,12 @@
       <c r="AW40" t="inlineStr">
         <is>
           <t>narrateur|C'est après la sieste.
-narrateur|Le bus rouge a glissé vers l'assiette.
-narrateur|La nappe est un peu chaude.
-narrateur|Raphaël est près de la table, avec le bus rouge.
-enfant-m|Bonjour, Mila.
-enfant-f|Bonjour.
-papa|Tu veux encore une rondelle ?
-enfant-m|S'il te plaît.
-narrateur|La pomme est froide, un peu sucrée.
-enfant-m|Merci, papa.
-maman|Bravo.
-maman|Tu as dit les trois mots.
-papa|Bonjour.
-papa|S'il te plaît.
-papa|Merci.
-enfant-f|Merci, Raphaël.
-maman|C'est du bon travail.</t>
+narrateur|Le bus rouge avance tout lentement.
+enfant-f|Les voyageurs ont sommeil.
+maman|Une rondelle calme ?
+enfant-f|S'il te plaît.
+enfant-f|Merci.
+narrateur|Raphaël ferme la porte du bus, tout doux.</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
@@ -8462,7 +8218,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu après la sieste, près de la table. Il a joué avec le bus rouge, avec Mila. Le pain a senti bon, tout calme. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
+          <t>Le bus reste collé à l'assiette. Terminus sieste. On ne réveille pas les pommes. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8602,19 +8358,12 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël a vécu après la sieste, près de la table.
-narrateur|Il a joué avec le bus rouge, avec Mila.
-narrateur|Le pain a senti bon, tout calme.
-maman|Tu as dit bonjour.
-papa|Tu as dit s'il te plaît.
-enfant-m|Et merci.
-maman|Bravo, Raphaël.
-maman|Tu as fait du bon travail.
-papa|Bonne journée, mon grand.
+          <t>narrateur|Le bus reste collé à l'assiette.
+enfant-m|Terminus sieste.
+papa|On ne réveille pas les pommes.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8639,7 +8388,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>C'est le soir. Le bus rouge attend près de la tasse. Ça sent la soupe. Raphaël est près de la table, avec le bus rouge. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
+          <t>C'est le soir. La table a une petite ombre. Raphaël range le bus sous une serviette. Le dépôt. Dernière rondelle ? S'il te plaît. Merci. Pour Mila aussi.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8780,22 +8529,12 @@
       <c r="AW42" t="inlineStr">
         <is>
           <t>narrateur|C'est le soir.
-narrateur|Le bus rouge attend près de la tasse.
-narrateur|Ça sent la soupe.
-narrateur|Raphaël est près de la table, avec le bus rouge.
-enfant-m|Bonjour, Mila.
-enfant-f|Bonjour.
-papa|Tu veux encore une rondelle ?
+narrateur|La table a une petite ombre.
+narrateur|Raphaël range le bus sous une serviette.
+enfant-f|Le dépôt.
+papa|Dernière rondelle ?
 enfant-m|S'il te plaît.
-narrateur|La pomme est froide, un peu sucrée.
-enfant-m|Merci, papa.
-maman|Bravo.
-maman|Tu as dit les trois mots.
-papa|Bonjour.
-papa|S'il te plaît.
-papa|Merci.
-enfant-f|Merci, Raphaël.
-maman|C'est du bon travail.</t>
+enfant-m|Merci. Pour Mila aussi.</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
@@ -8827,7 +8566,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu le soir, près de la table. Il a joué avec le bus rouge, avec Mila. La lampe a fait un rond doux. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
+          <t>Le bol est vide. Le bus est au dépôt. Bonne soirée, les voyageurs. Merci pour le trajet. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8967,19 +8706,12 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël a vécu le soir, près de la table.
-narrateur|Il a joué avec le bus rouge, avec Mila.
-narrateur|La lampe a fait un rond doux.
-maman|Tu as dit bonjour.
-papa|Tu as dit s'il te plaît.
-enfant-m|Et merci.
-maman|Bravo, Raphaël.
-maman|Tu as fait du bon travail.
-papa|Bonne journée, mon grand.
+          <t>narrateur|Le bol est vide. Le bus est au dépôt.
+maman|Bonne soirée, les voyageurs.
+enfant-f|Merci pour le trajet.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -9004,7 +8736,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Raphaël va près de la fenêtre, avec le bus rouge. La vitre est un peu floue. Mila trace un petit rond du doigt. Bonjour, Mila. Bonjour. Tu veux le torchon, pour la vitre ? S'il te plaît. Le torchon est doux, un peu épais. Merci, papa. Bravo, Raphaël. Merci. Je vois le marché. On dit les mots, même près de la fenêtre. Bonjour. S'il te plaît. Merci. Un oiseau passe derrière la vitre.</t>
+          <t>Raphaël va près de la fenêtre, avec le bus. Un vrai bus passe dans la rue. Mila colle son nez à la vitre. Le torchon, s'il te plaît. Pour voir le bus ? Oui. Il essuie. Le bus rouge de vrai apparaît. Merci, papa. Le nôtre est plus petit.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -9144,23 +8876,15 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël va près de la fenêtre, avec le bus rouge.
-narrateur|La vitre est un peu floue.
-narrateur|Mila trace un petit rond du doigt.
-enfant-m|Bonjour, Mila.
-enfant-f|Bonjour.
-papa|Tu veux le torchon, pour la vitre ?
-enfant-m|S'il te plaît.
-narrateur|Le torchon est doux, un peu épais.
+          <t>narrateur|Raphaël va près de la fenêtre, avec le bus.
+narrateur|Un vrai bus passe dans la rue.
+narrateur|Mila colle son nez à la vitre.
+enfant-m|Le torchon, s'il te plaît.
+papa|Pour voir le bus ?
+enfant-m|Oui.
+narrateur|Il essuie. Le bus rouge de vrai apparaît.
 enfant-m|Merci, papa.
-maman|Bravo, Raphaël.
-enfant-f|Merci.
-enfant-f|Je vois le marché.
-maman|On dit les mots, même près de la fenêtre.
-papa|Bonjour.
-papa|S'il te plaît.
-papa|Merci.
-narrateur|Un oiseau passe derrière la vitre.</t>
+enfant-f|Le nôtre est plus petit.</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
@@ -9357,10 +9081,9 @@
       <c r="AW45" t="inlineStr">
         <is>
           <t>narrateur|C'est quel moment ?
-maman|Le matin, après la sieste, ou le soir.</t>
-        </is>
-      </c>
-      <c r="AX45" t="inlineStr"/>
+narrateur|Le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -9385,7 +9108,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. Un vrai bus passe derrière la fenêtre. Le bus rouge le regarde, tout petit. Raphaël est près de la fenêtre, avec le bus rouge. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
+          <t>C'est le matin. Le vrai bus s'arrête au coin. Raphaël pose le petit bus sur le rebord. Rondelle du chauffeur ? S'il te plaît. Merci. Une pour Mila. Merci. On suit le grand.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -9526,22 +9249,12 @@
       <c r="AW46" t="inlineStr">
         <is>
           <t>narrateur|C'est le matin.
-narrateur|Un vrai bus passe derrière la fenêtre.
-narrateur|Le bus rouge le regarde, tout petit.
-narrateur|Raphaël est près de la fenêtre, avec le bus rouge.
-enfant-m|Bonjour, Mila.
-enfant-f|Bonjour.
-papa|Tu veux encore une rondelle ?
+narrateur|Le vrai bus s'arrête au coin.
+narrateur|Raphaël pose le petit bus sur le rebord.
+maman|Rondelle du chauffeur ?
 enfant-m|S'il te plaît.
-narrateur|La pomme est froide, un peu sucrée.
-enfant-m|Merci, papa.
-maman|Bravo.
-maman|Tu as dit les trois mots.
-papa|Bonjour.
-papa|S'il te plaît.
-papa|Merci.
-enfant-f|Merci, Raphaël.
-maman|C'est du bon travail.</t>
+enfant-m|Merci. Une pour Mila.
+enfant-f|Merci. On suit le grand.</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
@@ -9573,7 +9286,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu le matin, près de la fenêtre. Il a joué avec le bus rouge, avec Mila. Le soleil a touché le bol jaune. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
+          <t>Le vrai bus repart. Le petit reste. On garde les pommes ici. Bon trajet, vous deux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9713,19 +9426,12 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël a vécu le matin, près de la fenêtre.
-narrateur|Il a joué avec le bus rouge, avec Mila.
-narrateur|Le soleil a touché le bol jaune.
-maman|Tu as dit bonjour.
-papa|Tu as dit s'il te plaît.
-enfant-m|Et merci.
-maman|Bravo, Raphaël.
-maman|Tu as fait du bon travail.
-papa|Bonne journée, mon grand.
+          <t>narrateur|Le vrai bus repart. Le petit reste.
+enfant-m|On garde les pommes ici.
+papa|Bon trajet, vous deux.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9750,7 +9456,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>C'est après la sieste. La vitre est tiède. Le bus rouge repose sur le rebord. Raphaël est près de la fenêtre, avec le bus rouge. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
+          <t>C'est après la sieste. La rue est plus calme. Raphaël fait glisser le bus le long du bois. Pas de klaxon. Une pomme, tout bas ? S'il te plaît. Merci.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9891,22 +9597,12 @@
       <c r="AW48" t="inlineStr">
         <is>
           <t>narrateur|C'est après la sieste.
-narrateur|La vitre est tiède.
-narrateur|Le bus rouge repose sur le rebord.
-narrateur|Raphaël est près de la fenêtre, avec le bus rouge.
-enfant-m|Bonjour, Mila.
-enfant-f|Bonjour.
-papa|Tu veux encore une rondelle ?
-enfant-m|S'il te plaît.
-narrateur|La pomme est froide, un peu sucrée.
-enfant-m|Merci, papa.
-maman|Bravo.
-maman|Tu as dit les trois mots.
-papa|Bonjour.
-papa|S'il te plaît.
-papa|Merci.
-enfant-f|Merci, Raphaël.
-maman|C'est du bon travail.</t>
+narrateur|La rue est plus calme.
+narrateur|Raphaël fait glisser le bus le long du bois.
+enfant-f|Pas de klaxon.
+papa|Une pomme, tout bas ?
+enfant-f|S'il te plaît.
+enfant-f|Merci.</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
@@ -9938,7 +9634,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu après la sieste, près de la fenêtre. Il a joué avec le bus rouge, avec Mila. Le pain a senti bon, tout calme. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
+          <t>Le petit bus s'endort contre la vitre. Le grand reviendra plus tard. On l'attendra. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -10078,19 +9774,12 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël a vécu après la sieste, près de la fenêtre.
-narrateur|Il a joué avec le bus rouge, avec Mila.
-narrateur|Le pain a senti bon, tout calme.
-maman|Tu as dit bonjour.
-papa|Tu as dit s'il te plaît.
-enfant-m|Et merci.
-maman|Bravo, Raphaël.
-maman|Tu as fait du bon travail.
-papa|Bonne journée, mon grand.
+          <t>narrateur|Le petit bus s'endort contre la vitre.
+maman|Le grand reviendra plus tard.
+enfant-m|On l'attendra.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -10115,7 +9804,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>C'est le soir. Les lumières de la rue dansent sur la vitre. Le bus rouge est calme. Raphaël est près de la fenêtre, avec le bus rouge. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
+          <t>C'est le soir. Les feux du vrai bus passent, tout rouge. Raphaël descend le petit bus du rebord. On rentre au dépôt. Une rondelle, s'il te plaît. Merci. Bonne nuit, le bus.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -10256,22 +9945,12 @@
       <c r="AW50" t="inlineStr">
         <is>
           <t>narrateur|C'est le soir.
-narrateur|Les lumières de la rue dansent sur la vitre.
-narrateur|Le bus rouge est calme.
-narrateur|Raphaël est près de la fenêtre, avec le bus rouge.
-enfant-m|Bonjour, Mila.
-enfant-f|Bonjour.
-papa|Tu veux encore une rondelle ?
-enfant-m|S'il te plaît.
-narrateur|La pomme est froide, un peu sucrée.
-enfant-m|Merci, papa.
-maman|Bravo.
-maman|Tu as dit les trois mots.
-papa|Bonjour.
-papa|S'il te plaît.
-papa|Merci.
-enfant-f|Merci, Raphaël.
-maman|C'est du bon travail.</t>
+narrateur|Les feux du vrai bus passent, tout rouge.
+narrateur|Raphaël descend le petit bus du rebord.
+maman|On rentre au dépôt.
+enfant-m|Une rondelle, s'il te plaît.
+enfant-m|Merci.
+enfant-f|Bonne nuit, le bus.</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
@@ -10303,7 +9982,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu le soir, près de la fenêtre. Il a joué avec le bus rouge, avec Mila. La lampe a fait un rond doux. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
+          <t>La vitre est noire, maintenant. Le marché est fermé. Notre bus aussi. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -10443,19 +10122,12 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël a vécu le soir, près de la fenêtre.
-narrateur|Il a joué avec le bus rouge, avec Mila.
-narrateur|La lampe a fait un rond doux.
-maman|Tu as dit bonjour.
-papa|Tu as dit s'il te plaît.
-enfant-m|Et merci.
-maman|Bravo, Raphaël.
-maman|Tu as fait du bon travail.
-papa|Bonne journée, mon grand.
+          <t>narrateur|La vitre est noire, maintenant.
+papa|Le marché est fermé.
+enfant-m|Notre bus aussi.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -10480,7 +10152,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Raphaël glisse le bus rouge près du tabouret. Le tabouret est bas, en bois clair. Mila s'assoit, les pieds qui balancent. Bonjour, Mila. Bonjour. Tu veux le tabouret, Raphaël ? S'il te plaît. Tu peux. Merci. Raphaël pose une main sur le bois lisse. Bravo. Tu as demandé. Merci, Mila. Les trois mots, même pour un tabouret. Bonjour. S'il te plaît. Merci. Le tabouret fait un tout petit craquement.</t>
+          <t>Raphaël glisse le bus près du tabouret. Mila s'assoit. Les pieds balancent. Arrêt tabouret. Je descends ? Tu peux rester. Le bol, plus haut ? S'il te plaît. Maman pose le bol sur le tabouret, à côté de Mila. Merci.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -10620,24 +10292,15 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël glisse le bus rouge près du tabouret.
-narrateur|Le tabouret est bas, en bois clair.
-narrateur|Mila s'assoit, les pieds qui balancent.
-enfant-m|Bonjour, Mila.
-enfant-f|Bonjour.
-maman|Tu veux le tabouret, Raphaël ?
+          <t>narrateur|Raphaël glisse le bus près du tabouret.
+narrateur|Mila s'assoit. Les pieds balancent.
+enfant-m|Arrêt tabouret.
+enfant-f|Je descends ?
+enfant-m|Tu peux rester.
+maman|Le bol, plus haut ?
 enfant-m|S'il te plaît.
-enfant-f|Tu peux.
-enfant-f|Merci.
-narrateur|Raphaël pose une main sur le bois lisse.
-papa|Bravo.
-papa|Tu as demandé.
-enfant-m|Merci, Mila.
-maman|Les trois mots, même pour un tabouret.
-papa|Bonjour.
-papa|S'il te plaît.
-papa|Merci.
-narrateur|Le tabouret fait un tout petit craquement.</t>
+narrateur|Maman pose le bol sur le tabouret, à côté de Mila.
+enfant-m|Merci.</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
@@ -10834,10 +10497,9 @@
       <c r="AW53" t="inlineStr">
         <is>
           <t>narrateur|C'est quel moment ?
-maman|Le matin, après la sieste, ou le soir.</t>
-        </is>
-      </c>
-      <c r="AX53" t="inlineStr"/>
+narrateur|Le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10862,7 +10524,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. Le bus rouge est sous le tabouret. Mila balance les pieds. Raphaël est près de le tabouret, avec le bus rouge. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
+          <t>C'est le matin. Le soleil fait un rectangle sur le bois. Raphaël fait monter le bus sur le rectangle. Tickets pommes ? S'il te plaît. Deux rondelles sur les genoux de Mila. Merci. Une pour le chauffeur.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -11003,22 +10665,12 @@
       <c r="AW54" t="inlineStr">
         <is>
           <t>narrateur|C'est le matin.
-narrateur|Le bus rouge est sous le tabouret.
-narrateur|Mila balance les pieds.
-narrateur|Raphaël est près de le tabouret, avec le bus rouge.
-enfant-m|Bonjour, Mila.
-enfant-f|Bonjour.
-papa|Tu veux encore une rondelle ?
-enfant-m|S'il te plaît.
-narrateur|La pomme est froide, un peu sucrée.
-enfant-m|Merci, papa.
-maman|Bravo.
-maman|Tu as dit les trois mots.
-papa|Bonjour.
-papa|S'il te plaît.
-papa|Merci.
-enfant-f|Merci, Raphaël.
-maman|C'est du bon travail.</t>
+narrateur|Le soleil fait un rectangle sur le bois.
+narrateur|Raphaël fait monter le bus sur le rectangle.
+papa|Tickets pommes ?
+enfant-f|S'il te plaît.
+narrateur|Deux rondelles sur les genoux de Mila.
+enfant-f|Merci. Une pour le chauffeur.</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
@@ -11050,7 +10702,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu le matin, près de le tabouret. Il a joué avec le bus rouge, avec Mila. Le soleil a touché le bol jaune. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
+          <t>Raphaël croque. Mila croque. Prochain arrêt : demain. Vous avez bien attendu le bol. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -11190,19 +10842,12 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël a vécu le matin, près de le tabouret.
-narrateur|Il a joué avec le bus rouge, avec Mila.
-narrateur|Le soleil a touché le bol jaune.
-maman|Tu as dit bonjour.
-papa|Tu as dit s'il te plaît.
-enfant-m|Et merci.
-maman|Bravo, Raphaël.
-maman|Tu as fait du bon travail.
-papa|Bonne journée, mon grand.
+          <t>narrateur|Raphaël croque. Mila croque.
+enfant-m|Prochain arrêt : demain.
+maman|Vous avez bien attendu le bol.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -11227,7 +10872,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>C'est après la sieste. Le tabouret a une ombre ronde. Le bus rouge sort tout doux. Raphaël est près de le tabouret, avec le bus rouge. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
+          <t>C'est après la sieste. Mila balance moins les pieds. Raphaël gare le bus contre un pied. On charge tout doux. Une rondelle, s'il te plaît. Merci. Pour Mila.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -11368,22 +11013,11 @@
       <c r="AW56" t="inlineStr">
         <is>
           <t>narrateur|C'est après la sieste.
-narrateur|Le tabouret a une ombre ronde.
-narrateur|Le bus rouge sort tout doux.
-narrateur|Raphaël est près de le tabouret, avec le bus rouge.
-enfant-m|Bonjour, Mila.
-enfant-f|Bonjour.
-papa|Tu veux encore une rondelle ?
-enfant-m|S'il te plaît.
-narrateur|La pomme est froide, un peu sucrée.
-enfant-m|Merci, papa.
-maman|Bravo.
-maman|Tu as dit les trois mots.
-papa|Bonjour.
-papa|S'il te plaît.
-papa|Merci.
-enfant-f|Merci, Raphaël.
-maman|C'est du bon travail.</t>
+narrateur|Mila balance moins les pieds.
+narrateur|Raphaël gare le bus contre un pied.
+papa|On charge tout doux.
+enfant-m|Une rondelle, s'il te plaît.
+enfant-m|Merci. Pour Mila.</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
@@ -11415,7 +11049,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu après la sieste, près de le tabouret. Il a joué avec le bus rouge, avec Mila. Le pain a senti bon, tout calme. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
+          <t>Le bus ne roule plus. Merci. J'avais sommeil. Le tabouret a bien tenu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -11555,19 +11189,12 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël a vécu après la sieste, près de le tabouret.
-narrateur|Il a joué avec le bus rouge, avec Mila.
-narrateur|Le pain a senti bon, tout calme.
-maman|Tu as dit bonjour.
-papa|Tu as dit s'il te plaît.
-enfant-m|Et merci.
-maman|Bravo, Raphaël.
-maman|Tu as fait du bon travail.
-papa|Bonne journée, mon grand.
+          <t>narrateur|Le bus ne roule plus.
+enfant-f|Merci. J'avais sommeil.
+papa|Le tabouret a bien tenu.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -11592,7 +11219,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>C'est le soir. Le tabouret est près de la lampe. Le bus rouge rentre dans sa boîte. Raphaël est près de le tabouret, avec le bus rouge. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
+          <t>C'est le soir. Raphaël range le bus sous le tabouret. Le dépôt est en bas. On descend du siège ? Oui. Merci, tabouret. Dernière pomme ? S'il te plaît. Merci.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -11733,22 +11360,13 @@
       <c r="AW58" t="inlineStr">
         <is>
           <t>narrateur|C'est le soir.
-narrateur|Le tabouret est près de la lampe.
-narrateur|Le bus rouge rentre dans sa boîte.
-narrateur|Raphaël est près de le tabouret, avec le bus rouge.
-enfant-m|Bonjour, Mila.
-enfant-f|Bonjour.
-papa|Tu veux encore une rondelle ?
+narrateur|Raphaël range le bus sous le tabouret.
+enfant-f|Le dépôt est en bas.
+maman|On descend du siège ?
+enfant-f|Oui. Merci, tabouret.
+papa|Dernière pomme ?
 enfant-m|S'il te plaît.
-narrateur|La pomme est froide, un peu sucrée.
-enfant-m|Merci, papa.
-maman|Bravo.
-maman|Tu as dit les trois mots.
-papa|Bonjour.
-papa|S'il te plaît.
-papa|Merci.
-enfant-f|Merci, Raphaël.
-maman|C'est du bon travail.</t>
+enfant-m|Merci.</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
@@ -11780,7 +11398,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu le soir, près de le tabouret. Il a joué avec le bus rouge, avec Mila. La lampe a fait un rond doux. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
+          <t>Mila pose les pieds par terre. Le bus dort en dessous. Vous avez bien partagé le haut et le bas. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11920,19 +11538,12 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël a vécu le soir, près de le tabouret.
-narrateur|Il a joué avec le bus rouge, avec Mila.
-narrateur|La lampe a fait un rond doux.
-maman|Tu as dit bonjour.
-papa|Tu as dit s'il te plaît.
-enfant-m|Et merci.
-maman|Bravo, Raphaël.
-maman|Tu as fait du bon travail.
-papa|Bonne journée, mon grand.
+          <t>narrateur|Mila pose les pieds par terre.
+enfant-m|Le bus dort en dessous.
+maman|Vous avez bien partagé le haut et le bas.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11957,7 +11568,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Raphaël prend la petite voiture. Elle est lisse, un peu froide. Dehors, une portière claque, tout loin. Mila arrive, son manteau sent la pluie. Bonjour, Mila. Bonjour, Raphaël. Bonjour. Donne-moi ton manteau. S'il te plaît. Merci, Mila. Tu veux une pomme, Raphaël ? S'il te plaît. La rondelle est froide et douce. Merci, papa. Bravo, les trois mots. Bonjour. S'il te plaît. Merci. La petite voiture brille près du bol.</t>
+          <t>Raphaël prend la petite voiture. Elle est lisse, un peu froide. Dehors, une portière claque, tout loin. Mila arrive. Son manteau sent la pluie. Bonjour, Mila. Bonjour, Raphaël. Donne-moi ton manteau ? S'il te plaît, tu peux le prendre. Maman accroche le manteau. Merci. Une rondelle, Raphaël ? S'il te plaît. La rondelle est froide et douce. Merci, papa.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -12100,22 +11711,17 @@
           <t>narrateur|Raphaël prend la petite voiture.
 narrateur|Elle est lisse, un peu froide.
 narrateur|Dehors, une portière claque, tout loin.
-narrateur|Mila arrive, son manteau sent la pluie.
+narrateur|Mila arrive. Son manteau sent la pluie.
 enfant-m|Bonjour, Mila.
 enfant-f|Bonjour, Raphaël.
-maman|Bonjour.
-maman|Donne-moi ton manteau.
-enfant-f|S'il te plaît.
-maman|Merci, Mila.
-papa|Tu veux une pomme, Raphaël ?
+maman|Donne-moi ton manteau ?
+enfant-f|S'il te plaît, tu peux le prendre.
+narrateur|Maman accroche le manteau.
+enfant-f|Merci.
+papa|Une rondelle, Raphaël ?
 enfant-m|S'il te plaît.
 narrateur|La rondelle est froide et douce.
-enfant-m|Merci, papa.
-maman|Bravo, les trois mots.
-papa|Bonjour.
-papa|S'il te plaît.
-papa|Merci.
-narrateur|La petite voiture brille près du bol.</t>
+enfant-m|Merci, papa.</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
@@ -12147,7 +11753,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>On dit merci ?</t>
+          <t>Papa donne une rondelle. Que dit Raphaël ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -12162,22 +11768,22 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>bonjour</t>
+          <t>merci</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>bonjour | s'il te plaît | merci</t>
+          <t>merci | merci papa</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>Oui, c'est la bonne réponse.</t>
+          <t>Oui.</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>Tu étais presque.</t>
+          <t>Il dit merci.</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
@@ -12307,10 +11913,9 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|On dit merci ?</t>
-        </is>
-      </c>
-      <c r="AX61" t="inlineStr"/>
+          <t>narrateur|Papa donne une rondelle. Que dit Raphaël ?</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -12335,7 +11940,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. On dit merci. Et bonjour. Et s'il te plaît. Raphaël hoche la tête. Bravo, Raphaël. Tu as fait du bon travail. Merci, maman.</t>
+          <t>Raphaël a dit merci. La petite voiture brille près du bol. Le manteau de Mila sèche un peu. On roule ? On s'installe.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -12479,17 +12084,13 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui.
-maman|On dit merci.
-papa|Et bonjour.
-papa|Et s'il te plaît.
-narrateur|Raphaël hoche la tête.
-maman|Bravo, Raphaël.
-maman|Tu as fait du bon travail.
-enfant-m|Merci, maman.</t>
-        </is>
-      </c>
-      <c r="AX62" t="inlineStr"/>
+          <t>narrateur|Raphaël a dit merci.
+narrateur|La petite voiture brille près du bol.
+narrateur|Le manteau de Mila sèche un peu.
+enfant-m|On roule ?
+papa|On s'installe.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -12542,7 +12143,7 @@
       <c r="L63" s="2" t="inlineStr"/>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>Tom</t>
+          <t>la table</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -12552,7 +12153,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Léa</t>
+          <t>la fenêtre</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -12562,7 +12163,7 @@
       </c>
       <c r="Q63" s="2" t="inlineStr">
         <is>
-          <t>Sami</t>
+          <t>le tabouret</t>
         </is>
       </c>
       <c r="R63" s="2" t="inlineStr">
@@ -12683,10 +12284,9 @@
       <c r="AW63" t="inlineStr">
         <is>
           <t>narrateur|On va où, dans la cuisine ?
-papa|La table, la fenêtre, ou le tabouret.</t>
-        </is>
-      </c>
-      <c r="AX63" t="inlineStr"/>
+narrateur|La table, la fenêtre, ou le tabouret.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12711,7 +12311,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Raphaël pose la petite voiture près de la table. Le bol jaune est au milieu. Mila tire une chaise, tout doux. Bonjour, Mila. Bonjour. Une assiette, Raphaël ? S'il te plaît. L'assiette est ronde, un peu froide. Merci, maman. Bravo. Tu as dit les mots. S'il te plaît. Une pomme. Voilà. Merci d'avoir demandé. Une rondelle brille dans l'assiette. Les mots gentils, à table aussi.</t>
+          <t>Raphaël pose la petite voiture près de la table. Une goutte du manteau tombe. Toc. Mila tire une chaise. Une assiette, pour ne pas mouiller ? S'il te plaît. L'assiette arrive, ronde. Merci. Il y pose une rondelle pour Mila. Merci. Ma voiture à moi, c'est la chaise.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12852,22 +12452,14 @@
       <c r="AW64" t="inlineStr">
         <is>
           <t>narrateur|Raphaël pose la petite voiture près de la table.
-narrateur|Le bol jaune est au milieu.
-narrateur|Mila tire une chaise, tout doux.
-enfant-m|Bonjour, Mila.
-enfant-f|Bonjour.
-maman|Une assiette, Raphaël ?
+narrateur|Une goutte du manteau tombe. Toc.
+narrateur|Mila tire une chaise.
+maman|Une assiette, pour ne pas mouiller ?
 enfant-m|S'il te plaît.
-narrateur|L'assiette est ronde, un peu froide.
-enfant-m|Merci, maman.
-papa|Bravo.
-papa|Tu as dit les mots.
-enfant-f|S'il te plaît.
-enfant-f|Une pomme.
-papa|Voilà.
-papa|Merci d'avoir demandé.
-narrateur|Une rondelle brille dans l'assiette.
-maman|Les mots gentils, à table aussi.</t>
+narrateur|L'assiette arrive, ronde.
+enfant-m|Merci.
+narrateur|Il y pose une rondelle pour Mila.
+enfant-f|Merci. Ma voiture à moi, c'est la chaise.</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
@@ -13064,10 +12656,9 @@
       <c r="AW65" t="inlineStr">
         <is>
           <t>narrateur|C'est quel moment ?
-maman|Le matin, après la sieste, ou le soir.</t>
-        </is>
-      </c>
-      <c r="AX65" t="inlineStr"/>
+narrateur|Le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -13092,7 +12683,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. La petite voiture roule vers le bol, sur la table. Une goutte d'eau brille sur le bois. Raphaël est près de la table, avec la petite voiture. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
+          <t>C'est le matin. La goutte a déjà séché. Raphaël fait le tour des assiettes avec la voiture. Encore une pomme, chauffeur ? S'il te plaît. Merci. Mila aussi. Merci. On va au marché, pour de faux.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -13233,22 +12824,12 @@
       <c r="AW66" t="inlineStr">
         <is>
           <t>narrateur|C'est le matin.
-narrateur|La petite voiture roule vers le bol, sur la table.
-narrateur|Une goutte d'eau brille sur le bois.
-narrateur|Raphaël est près de la table, avec la petite voiture.
-enfant-m|Bonjour, Mila.
-enfant-f|Bonjour.
-papa|Tu veux encore une rondelle ?
+narrateur|La goutte a déjà séché.
+narrateur|Raphaël fait le tour des assiettes avec la voiture.
+papa|Encore une pomme, chauffeur ?
 enfant-m|S'il te plaît.
-narrateur|La pomme est froide, un peu sucrée.
-enfant-m|Merci, papa.
-maman|Bravo.
-maman|Tu as dit les trois mots.
-papa|Bonjour.
-papa|S'il te plaît.
-papa|Merci.
-enfant-f|Merci, Raphaël.
-maman|C'est du bon travail.</t>
+enfant-m|Merci. Mila aussi.
+enfant-f|Merci. On va au marché, pour de faux.</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
@@ -13280,7 +12861,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu le matin, près de la table. Il a joué avec la petite voiture, avec Mila. Le soleil a touché le bol jaune. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
+          <t>La voiture se gare contre le bol jaune. Parking pommes. Vous avez bien servi. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -13420,19 +13001,12 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël a vécu le matin, près de la table.
-narrateur|Il a joué avec la petite voiture, avec Mila.
-narrateur|Le soleil a touché le bol jaune.
-maman|Tu as dit bonjour.
-papa|Tu as dit s'il te plaît.
-enfant-m|Et merci.
-maman|Bravo, Raphaël.
-maman|Tu as fait du bon travail.
-papa|Bonne journée, mon grand.
+          <t>narrateur|La voiture se gare contre le bol jaune.
+enfant-m|Parking pommes.
+maman|Vous avez bien servi.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -13457,7 +13031,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>C'est après la sieste. La petite voiture dort près de l'assiette. Ça sent encore le pain. Raphaël est près de la table, avec la petite voiture. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
+          <t>C'est après la sieste. La voiture avance entre les miettes, tout lent. Pas trop vite. J'ai encore sommeil. Une rondelle ? S'il te plaît. Merci. Raphaël arrête la voiture près de sa main.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -13598,22 +13172,12 @@
       <c r="AW68" t="inlineStr">
         <is>
           <t>narrateur|C'est après la sieste.
-narrateur|La petite voiture dort près de l'assiette.
-narrateur|Ça sent encore le pain.
-narrateur|Raphaël est près de la table, avec la petite voiture.
-enfant-m|Bonjour, Mila.
-enfant-f|Bonjour.
-papa|Tu veux encore une rondelle ?
-enfant-m|S'il te plaît.
-narrateur|La pomme est froide, un peu sucrée.
-enfant-m|Merci, papa.
-maman|Bravo.
-maman|Tu as dit les trois mots.
-papa|Bonjour.
-papa|S'il te plaît.
-papa|Merci.
-enfant-f|Merci, Raphaël.
-maman|C'est du bon travail.</t>
+narrateur|La voiture avance entre les miettes, tout lent.
+enfant-f|Pas trop vite. J'ai encore sommeil.
+maman|Une rondelle ?
+enfant-f|S'il te plaît.
+enfant-f|Merci.
+narrateur|Raphaël arrête la voiture près de sa main.</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
@@ -13645,7 +13209,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu après la sieste, près de la table. Il a joué avec la petite voiture, avec Mila. Le pain a senti bon, tout calme. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
+          <t>La voiture fait un tout petit phare : le soleil. On reste au parking. Les pommes aussi. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -13785,19 +13349,12 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël a vécu après la sieste, près de la table.
-narrateur|Il a joué avec la petite voiture, avec Mila.
-narrateur|Le pain a senti bon, tout calme.
-maman|Tu as dit bonjour.
-papa|Tu as dit s'il te plaît.
-enfant-m|Et merci.
-maman|Bravo, Raphaël.
-maman|Tu as fait du bon travail.
-papa|Bonne journée, mon grand.
+          <t>narrateur|La voiture fait un tout petit phare : le soleil.
+papa|On reste au parking.
+enfant-m|Les pommes aussi.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13822,7 +13379,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>C'est le soir. La petite voiture se gare près de la tasse. La table est tiède. Raphaël est près de la table, avec la petite voiture. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
+          <t>C'est le soir. Raphaël gare la voiture sous la table. On reprend le manteau bientôt. Encore une pomme ? S'il te plaît, papa. La dernière rondelle. Merci.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13963,22 +13520,12 @@
       <c r="AW70" t="inlineStr">
         <is>
           <t>narrateur|C'est le soir.
-narrateur|La petite voiture se gare près de la tasse.
-narrateur|La table est tiède.
-narrateur|Raphaël est près de la table, avec la petite voiture.
-enfant-m|Bonjour, Mila.
-enfant-f|Bonjour.
-papa|Tu veux encore une rondelle ?
-enfant-m|S'il te plaît.
-narrateur|La pomme est froide, un peu sucrée.
-enfant-m|Merci, papa.
-maman|Bravo.
-maman|Tu as dit les trois mots.
-papa|Bonjour.
-papa|S'il te plaît.
-papa|Merci.
-enfant-f|Merci, Raphaël.
-maman|C'est du bon travail.</t>
+narrateur|Raphaël gare la voiture sous la table.
+maman|On reprend le manteau bientôt.
+enfant-f|Encore une pomme ?
+enfant-m|S'il te plaît, papa.
+narrateur|La dernière rondelle.
+enfant-f|Merci.</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
@@ -14010,7 +13557,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu le soir, près de la table. Il a joué avec la petite voiture, avec Mila. La lampe a fait un rond doux. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
+          <t>Mila enfile son manteau. Il est presque sec. À demain. Merci pour les pommes. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -14150,19 +13697,12 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël a vécu le soir, près de la table.
-narrateur|Il a joué avec la petite voiture, avec Mila.
-narrateur|La lampe a fait un rond doux.
-maman|Tu as dit bonjour.
-papa|Tu as dit s'il te plaît.
-enfant-m|Et merci.
-maman|Bravo, Raphaël.
-maman|Tu as fait du bon travail.
-papa|Bonne journée, mon grand.
+          <t>narrateur|Mila enfile son manteau. Il est presque sec.
+enfant-m|À demain.
+enfant-f|Merci pour les pommes.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -14187,7 +13727,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Raphaël va près de la fenêtre, avec la petite voiture. La vitre est un peu floue. Mila trace un petit rond du doigt. Bonjour, Mila. Bonjour. Tu veux le torchon, pour la vitre ? S'il te plaît. Le torchon est doux, un peu épais. Merci, papa. Bravo, Raphaël. Merci. Je vois le marché. On dit les mots, même près de la fenêtre. Bonjour. S'il te plaît. Merci. Un oiseau passe derrière la vitre.</t>
+          <t>Raphaël va près de la fenêtre, avec la voiture. La vitre a encore un peu de buée. Mila dessine une route du doigt. Le torchon, s'il te plaît. Pour la route ? Oui. La buée part. La rue apparaît. Merci, papa. Ta voiture peut y aller.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -14327,23 +13867,15 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël va près de la fenêtre, avec la petite voiture.
-narrateur|La vitre est un peu floue.
-narrateur|Mila trace un petit rond du doigt.
-enfant-m|Bonjour, Mila.
-enfant-f|Bonjour.
-papa|Tu veux le torchon, pour la vitre ?
-enfant-m|S'il te plaît.
-narrateur|Le torchon est doux, un peu épais.
+          <t>narrateur|Raphaël va près de la fenêtre, avec la voiture.
+narrateur|La vitre a encore un peu de buée.
+narrateur|Mila dessine une route du doigt.
+enfant-m|Le torchon, s'il te plaît.
+papa|Pour la route ?
+enfant-m|Oui.
+narrateur|La buée part. La rue apparaît.
 enfant-m|Merci, papa.
-maman|Bravo, Raphaël.
-enfant-f|Merci.
-enfant-f|Je vois le marché.
-maman|On dit les mots, même près de la fenêtre.
-papa|Bonjour.
-papa|S'il te plaît.
-papa|Merci.
-narrateur|Un oiseau passe derrière la vitre.</t>
+enfant-f|Ta voiture peut y aller.</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
@@ -14540,10 +14072,9 @@
       <c r="AW73" t="inlineStr">
         <is>
           <t>narrateur|C'est quel moment ?
-maman|Le matin, après la sieste, ou le soir.</t>
-        </is>
-      </c>
-      <c r="AX73" t="inlineStr"/>
+narrateur|Le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -14568,7 +14099,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. La petite voiture touche la vitre froide. Un oiseau crie une fois. Raphaël est près de la fenêtre, avec la petite voiture. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
+          <t>C'est le matin. Une vraie voiture passe, tout loin. Raphaël suit la route sur la vitre. Rondelle du voyage ? S'il te plaît. Merci. On va au marché des pommes.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -14709,22 +14240,12 @@
       <c r="AW74" t="inlineStr">
         <is>
           <t>narrateur|C'est le matin.
-narrateur|La petite voiture touche la vitre froide.
-narrateur|Un oiseau crie une fois.
-narrateur|Raphaël est près de la fenêtre, avec la petite voiture.
-enfant-m|Bonjour, Mila.
-enfant-f|Bonjour.
-papa|Tu veux encore une rondelle ?
-enfant-m|S'il te plaît.
-narrateur|La pomme est froide, un peu sucrée.
-enfant-m|Merci, papa.
-maman|Bravo.
-maman|Tu as dit les trois mots.
-papa|Bonjour.
-papa|S'il te plaît.
-papa|Merci.
-enfant-f|Merci, Raphaël.
-maman|C'est du bon travail.</t>
+narrateur|Une vraie voiture passe, tout loin.
+narrateur|Raphaël suit la route sur la vitre.
+maman|Rondelle du voyage ?
+enfant-f|S'il te plaît.
+enfant-f|Merci.
+enfant-m|On va au marché des pommes.</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
@@ -14756,7 +14277,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu le matin, près de la fenêtre. Il a joué avec la petite voiture, avec Mila. Le soleil a touché le bol jaune. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
+          <t>La petite voiture s'arrête au bas de la vitre. Vous êtes arrivés. Les pommes aussi. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -14896,19 +14417,12 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël a vécu le matin, près de la fenêtre.
-narrateur|Il a joué avec la petite voiture, avec Mila.
-narrateur|Le soleil a touché le bol jaune.
-maman|Tu as dit bonjour.
-papa|Tu as dit s'il te plaît.
-enfant-m|Et merci.
-maman|Bravo, Raphaël.
-maman|Tu as fait du bon travail.
-papa|Bonne journée, mon grand.
+          <t>narrateur|La petite voiture s'arrête au bas de la vitre.
+papa|Vous êtes arrivés.
+enfant-m|Les pommes aussi.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14933,7 +14447,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>C'est après la sieste. La vitre a un petit nuage. La petite voiture attend sur le rebord. Raphaël est près de la fenêtre, avec la petite voiture. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
+          <t>C'est après la sieste. La rue est calme. Raphaël pose la voiture sur le rebord, sans la pousser. Une pomme, sans bouger ? S'il te plaît. Merci. Pour Mila.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -15074,22 +14588,11 @@
       <c r="AW76" t="inlineStr">
         <is>
           <t>narrateur|C'est après la sieste.
-narrateur|La vitre a un petit nuage.
-narrateur|La petite voiture attend sur le rebord.
-narrateur|Raphaël est près de la fenêtre, avec la petite voiture.
-enfant-m|Bonjour, Mila.
-enfant-f|Bonjour.
-papa|Tu veux encore une rondelle ?
+narrateur|La rue est calme.
+narrateur|Raphaël pose la voiture sur le rebord, sans la pousser.
+papa|Une pomme, sans bouger ?
 enfant-m|S'il te plaît.
-narrateur|La pomme est froide, un peu sucrée.
-enfant-m|Merci, papa.
-maman|Bravo.
-maman|Tu as dit les trois mots.
-papa|Bonjour.
-papa|S'il te plaît.
-papa|Merci.
-enfant-f|Merci, Raphaël.
-maman|C'est du bon travail.</t>
+enfant-m|Merci. Pour Mila.</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
@@ -15121,7 +14624,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu après la sieste, près de la fenêtre. Il a joué avec la petite voiture, avec Mila. Le pain a senti bon, tout calme. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
+          <t>La voiture reste. Mila reste. Merci. On regarde seulement. C'est bien, parfois. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -15261,19 +14764,12 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël a vécu après la sieste, près de la fenêtre.
-narrateur|Il a joué avec la petite voiture, avec Mila.
-narrateur|Le pain a senti bon, tout calme.
-maman|Tu as dit bonjour.
-papa|Tu as dit s'il te plaît.
-enfant-m|Et merci.
-maman|Bravo, Raphaël.
-maman|Tu as fait du bon travail.
-papa|Bonne journée, mon grand.
+          <t>narrateur|La voiture reste. Mila reste.
+enfant-f|Merci. On regarde seulement.
+maman|C'est bien, parfois.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -15298,7 +14794,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>C'est le soir. La vitre est noire, un peu. La petite voiture brille sous la lampe. Raphaël est près de la fenêtre, avec la petite voiture. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
+          <t>C'est le soir. Des phares passent sur la vitre. Raphaël descend la voiture. On rentre. Une pomme avant le manteau ? S'il te plaît. Merci.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -15439,22 +14935,12 @@
       <c r="AW78" t="inlineStr">
         <is>
           <t>narrateur|C'est le soir.
-narrateur|La vitre est noire, un peu.
-narrateur|La petite voiture brille sous la lampe.
-narrateur|Raphaël est près de la fenêtre, avec la petite voiture.
-enfant-m|Bonjour, Mila.
-enfant-f|Bonjour.
-papa|Tu veux encore une rondelle ?
+narrateur|Des phares passent sur la vitre.
+narrateur|Raphaël descend la voiture.
+enfant-f|On rentre.
+maman|Une pomme avant le manteau ?
 enfant-m|S'il te plaît.
-narrateur|La pomme est froide, un peu sucrée.
-enfant-m|Merci, papa.
-maman|Bravo.
-maman|Tu as dit les trois mots.
-papa|Bonjour.
-papa|S'il te plaît.
-papa|Merci.
-enfant-f|Merci, Raphaël.
-maman|C'est du bon travail.</t>
+enfant-m|Merci.</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
@@ -15486,7 +14972,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu le soir, près de la fenêtre. Il a joué avec la petite voiture, avec Mila. La lampe a fait un rond doux. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
+          <t>Mila reprend son manteau. À demain, la route. La voiture est au garage, sous la fenêtre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -15626,19 +15112,12 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël a vécu le soir, près de la fenêtre.
-narrateur|Il a joué avec la petite voiture, avec Mila.
-narrateur|La lampe a fait un rond doux.
-maman|Tu as dit bonjour.
-papa|Tu as dit s'il te plaît.
-enfant-m|Et merci.
-maman|Bravo, Raphaël.
-maman|Tu as fait du bon travail.
-papa|Bonne journée, mon grand.
+          <t>narrateur|Mila reprend son manteau.
+enfant-m|À demain, la route.
+papa|La voiture est au garage, sous la fenêtre.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -15663,7 +15142,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Raphaël glisse la petite voiture près du tabouret. Le tabouret est bas, en bois clair. Mila s'assoit, les pieds qui balancent. Bonjour, Mila. Bonjour. Tu veux le tabouret, Raphaël ? S'il te plaît. Tu peux. Merci. Raphaël pose une main sur le bois lisse. Bravo. Tu as demandé. Merci, Mila. Les trois mots, même pour un tabouret. Bonjour. S'il te plaît. Merci. Le tabouret fait un tout petit craquement.</t>
+          <t>Raphaël glisse la voiture près du tabouret. Mila s'assoit. Les pieds balancent. Je monte la voiture ? S'il te plaît, tout doux. Il pose la voiture sur le bois, près d'elle. Merci, Mila. Le bol, à votre hauteur ? S'il te plaît. Merci.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -15803,24 +15282,15 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël glisse la petite voiture près du tabouret.
-narrateur|Le tabouret est bas, en bois clair.
-narrateur|Mila s'assoit, les pieds qui balancent.
-enfant-m|Bonjour, Mila.
-enfant-f|Bonjour.
-maman|Tu veux le tabouret, Raphaël ?
+          <t>narrateur|Raphaël glisse la voiture près du tabouret.
+narrateur|Mila s'assoit. Les pieds balancent.
+enfant-m|Je monte la voiture ?
+enfant-f|S'il te plaît, tout doux.
+narrateur|Il pose la voiture sur le bois, près d'elle.
+enfant-m|Merci, Mila.
+maman|Le bol, à votre hauteur ?
 enfant-m|S'il te plaît.
-enfant-f|Tu peux.
-enfant-f|Merci.
-narrateur|Raphaël pose une main sur le bois lisse.
-papa|Bravo.
-papa|Tu as demandé.
-enfant-m|Merci, Mila.
-maman|Les trois mots, même pour un tabouret.
-papa|Bonjour.
-papa|S'il te plaît.
-papa|Merci.
-narrateur|Le tabouret fait un tout petit craquement.</t>
+enfant-m|Merci.</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
@@ -16017,10 +15487,9 @@
       <c r="AW81" t="inlineStr">
         <is>
           <t>narrateur|C'est quel moment ?
-maman|Le matin, après la sieste, ou le soir.</t>
-        </is>
-      </c>
-      <c r="AX81" t="inlineStr"/>
+narrateur|Le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -16045,7 +15514,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. La petite voiture tourne autour du tabouret. Le bois est frais. Raphaël est près de le tabouret, avec la petite voiture. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
+          <t>C'est le matin. Le soleil fait un parking sur le tabouret. Raphaël gare la voiture dans le carré de lumière. Pommes du parking ? S'il te plaît. Merci. Une pour Raphaël.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -16186,22 +15655,11 @@
       <c r="AW82" t="inlineStr">
         <is>
           <t>narrateur|C'est le matin.
-narrateur|La petite voiture tourne autour du tabouret.
-narrateur|Le bois est frais.
-narrateur|Raphaël est près de le tabouret, avec la petite voiture.
-enfant-m|Bonjour, Mila.
-enfant-f|Bonjour.
-papa|Tu veux encore une rondelle ?
-enfant-m|S'il te plaît.
-narrateur|La pomme est froide, un peu sucrée.
-enfant-m|Merci, papa.
-maman|Bravo.
-maman|Tu as dit les trois mots.
-papa|Bonjour.
-papa|S'il te plaît.
-papa|Merci.
-enfant-f|Merci, Raphaël.
-maman|C'est du bon travail.</t>
+narrateur|Le soleil fait un parking sur le tabouret.
+narrateur|Raphaël gare la voiture dans le carré de lumière.
+papa|Pommes du parking ?
+enfant-f|S'il te plaît.
+enfant-f|Merci. Une pour Raphaël.</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
@@ -16233,7 +15691,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu le matin, près de le tabouret. Il a joué avec la petite voiture, avec Mila. Le soleil a touché le bol jaune. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
+          <t>Ils croquent, les pieds en l'air. Belle place. Vous avez bien demandé le bol. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -16373,19 +15831,12 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël a vécu le matin, près de le tabouret.
-narrateur|Il a joué avec la petite voiture, avec Mila.
-narrateur|Le soleil a touché le bol jaune.
-maman|Tu as dit bonjour.
-papa|Tu as dit s'il te plaît.
-enfant-m|Et merci.
-maman|Bravo, Raphaël.
-maman|Tu as fait du bon travail.
-papa|Bonne journée, mon grand.
+          <t>narrateur|Ils croquent, les pieds en l'air.
+enfant-m|Belle place.
+maman|Vous avez bien demandé le bol.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -16410,7 +15861,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>C'est après la sieste. Le tabouret a gardé le soleil. La petite voiture est tiède. Raphaël est près de le tabouret, avec la petite voiture. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
+          <t>C'est après la sieste. La voiture ne roule plus. Elle attend. Moi aussi, j'attends. Une rondelle, alors. S'il te plaît. Merci. On partage.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -16551,22 +16002,11 @@
       <c r="AW84" t="inlineStr">
         <is>
           <t>narrateur|C'est après la sieste.
-narrateur|Le tabouret a gardé le soleil.
-narrateur|La petite voiture est tiède.
-narrateur|Raphaël est près de le tabouret, avec la petite voiture.
-enfant-m|Bonjour, Mila.
-enfant-f|Bonjour.
-papa|Tu veux encore une rondelle ?
+narrateur|La voiture ne roule plus. Elle attend.
+enfant-f|Moi aussi, j'attends.
+papa|Une rondelle, alors.
 enfant-m|S'il te plaît.
-narrateur|La pomme est froide, un peu sucrée.
-enfant-m|Merci, papa.
-maman|Bravo.
-maman|Tu as dit les trois mots.
-papa|Bonjour.
-papa|S'il te plaît.
-papa|Merci.
-enfant-f|Merci, Raphaël.
-maman|C'est du bon travail.</t>
+enfant-m|Merci. On partage.</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
@@ -16598,7 +16038,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu après la sieste, près de le tabouret. Il a joué avec la petite voiture, avec Mila. Le pain a senti bon, tout calme. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
+          <t>Deux rondelles. Deux sourires. Le tabouret a tenu le goûter. Merci, tabouret. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -16738,19 +16178,12 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël a vécu après la sieste, près de le tabouret.
-narrateur|Il a joué avec la petite voiture, avec Mila.
-narrateur|Le pain a senti bon, tout calme.
-maman|Tu as dit bonjour.
-papa|Tu as dit s'il te plaît.
-enfant-m|Et merci.
-maman|Bravo, Raphaël.
-maman|Tu as fait du bon travail.
-papa|Bonne journée, mon grand.
+          <t>narrateur|Deux rondelles. Deux sourires.
+maman|Le tabouret a tenu le goûter.
+enfant-f|Merci, tabouret.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -16775,7 +16208,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>C'est le soir. La petite voiture se range sous le tabouret. On entend la casserole, tout loin. Raphaël est près de le tabouret, avec la petite voiture. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
+          <t>C'est le soir. Raphaël descend la voiture du tabouret. Je descends aussi. Merci d'avoir gardé la place. Manteau ? S'il te plaît. Merci. Et une pomme pour la route.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -16916,22 +16349,13 @@
       <c r="AW86" t="inlineStr">
         <is>
           <t>narrateur|C'est le soir.
-narrateur|La petite voiture se range sous le tabouret.
-narrateur|On entend la casserole, tout loin.
-narrateur|Raphaël est près de le tabouret, avec la petite voiture.
-enfant-m|Bonjour, Mila.
-enfant-f|Bonjour.
-papa|Tu veux encore une rondelle ?
-enfant-m|S'il te plaît.
-narrateur|La pomme est froide, un peu sucrée.
-enfant-m|Merci, papa.
-maman|Bravo.
-maman|Tu as dit les trois mots.
-papa|Bonjour.
-papa|S'il te plaît.
-papa|Merci.
-enfant-f|Merci, Raphaël.
-maman|C'est du bon travail.</t>
+narrateur|Raphaël descend la voiture du tabouret.
+enfant-f|Je descends aussi.
+enfant-m|Merci d'avoir gardé la place.
+maman|Manteau ?
+enfant-f|S'il te plaît.
+enfant-f|Merci.
+papa|Et une pomme pour la route.</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
@@ -16963,7 +16387,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu le soir, près de le tabouret. Il a joué avec la petite voiture, avec Mila. La lampe a fait un rond doux. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
+          <t>Mila enfile son manteau. Il sent encore un peu la pluie. À demain. Merci pour les pommes et la voiture. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -17103,19 +16527,12 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël a vécu le soir, près de le tabouret.
-narrateur|Il a joué avec la petite voiture, avec Mila.
-narrateur|La lampe a fait un rond doux.
-maman|Tu as dit bonjour.
-papa|Tu as dit s'il te plaît.
-enfant-m|Et merci.
-maman|Bravo, Raphaël.
-maman|Tu as fait du bon travail.
-papa|Bonne journée, mon grand.
+          <t>narrateur|Mila enfile son manteau. Il sent encore un peu la pluie.
+enfant-m|À demain.
+enfant-f|Merci pour les pommes et la voiture.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -17134,7 +16551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -17193,6 +16610,13 @@
       <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>F-NAR-010…015 texte : désir partager pommes, Mila D16, labels table/fenêtre/tabouret, chaîne Q bonjour/s'il te plaît/merci</t>
         </is>
       </c>
     </row>

--- a/stories/archive/arbres/TREE-COL-001.xlsx
+++ b/stories/archive/arbres/TREE-COL-001.xlsx
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>La casserole et les pommes de Raphaël</t>
+          <t>Le voyage des pommes de Raphaël</t>
         </is>
       </c>
     </row>
@@ -610,11 +610,7 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>COL.ECO.001</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -854,7 +850,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Raphaël veut donner des pommes à Mila. La casserole chante. Il prend un train, un bus ou une voiture. Ils s'installent. Il dit bonjour, s'il te plaît, merci quand il en a besoin. Les pommes sont partagées.</t>
+          <t>Raphaël veut donner des pommes à Mila. Ils font le voyage des pommes avec un train, un bus ou une voiture, jusqu'à un arrêt. Ils poussent, ils livrent, ils croquent.</t>
         </is>
       </c>
     </row>
@@ -1197,17 +1193,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une goutte glisse le long de la casserole. Ça sent la pomme, toute douce. Le torchon rayé pend près de l'évier. Dehors, le marché parle tout bas. Un rond de soleil pose sur le carrelage. Les chaussons de Raphaël attendent sous la table. La casserole chante un peu, Raphaël. Tu as vu le torchon ? Il est rouge et blanc. Papa pose des rondelles dans un bol jaune. Le bois de la planche est lisse, un peu humide. En ce moment, Raphaël tient une cuillère en bois. Je veux donner des pommes à Mila. Elle arrive tout à l'heure. Tu prends un jouet, en attendant ? Le bol jaune attend au milieu.</t>
+          <t>Une goutte glisse le long de la casserole. Ça sent la pomme, toute douce. Le torchon rayé pend près de l'évier. Dehors, le marché parle tout bas. Un rond de soleil se pose sur le carrelage. Papa a mis des rondelles dans un bol jaune. En ce moment, Raphaël tient une cuillère en bois. Je veux donner des pommes à Mila. On fait le voyage des pommes. Elle arrive tout à l'heure. Tu prends un véhicule, en attendant ?</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sami est dans la cuisine, avec maman. Papa coupe une pomme. Des copains vont arriver. On va dire des mots gentils. Maman dit : on dit &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une goutte glisse le long de la casserole. Ça sent la pomme, toute douce. Le torchon rayé pend près de l'évier. Dehors, le marché parle tout bas. Un rond de soleil se pose sur le carrelage. Papa a mis des rondelles dans un bol jaune. En ce moment, Raphaël tient une cuillère en bois. Je veux donner des pommes à Mila. On fait le voyage des pommes. Elle arrive tout à l'heure. Tu prends un véhicule, en attendant ?</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Sami est dans la cuisine, avec maman. Papa coupe une pomme. Des copains vont arriver. On va dire des mots gentils. Maman dit : on dit &lt;emphasis&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. [pause]</t>
+          <t>Une goutte glisse le long de la casserole. Ça sent la pomme, toute douce. Le torchon rayé pend près de l'évier. Dehors, le marché parle tout bas. Un rond de soleil se pose sur le carrelage. Papa a mis des rondelles dans un bol jaune. En ce moment, Raphaël tient une cuillère en bois. Je veux donner des pommes à Mila. On fait le voyage des pommes. Elle arrive tout à l'heure. Tu prends un véhicule, en attendant ?</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -1341,18 +1337,13 @@
 narrateur|Ça sent la pomme, toute douce.
 narrateur|Le torchon rayé pend près de l'évier.
 narrateur|Dehors, le marché parle tout bas.
-narrateur|Un rond de soleil pose sur le carrelage.
-narrateur|Les chaussons de Raphaël attendent sous la table.
-papa|La casserole chante un peu, Raphaël.
-maman|Tu as vu le torchon ?
-enfant-m|Il est rouge et blanc.
-narrateur|Papa pose des rondelles dans un bol jaune.
-narrateur|Le bois de la planche est lisse, un peu humide.
+narrateur|Un rond de soleil se pose sur le carrelage.
+narrateur|Papa a mis des rondelles dans un bol jaune.
 narrateur|En ce moment, Raphaël tient une cuillère en bois.
 enfant-m|Je veux donner des pommes à Mila.
+enfant-m|On fait le voyage des pommes.
 maman|Elle arrive tout à l'heure.
-papa|Tu prends un jouet, en attendant ?
-narrateur|Le bol jaune attend au milieu.</t>
+papa|Tu prends un véhicule, en attendant ?</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1389,12 +1380,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;On peut prendre le train, le bus, ou la voiture.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
+          <t>Qu'est-ce que Raphaël prend ? Le train, le bus, ou la voiture.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;On peut prendre le train, le bus, ou la voiture.&lt;/slow&gt; [pause]</t>
+          <t>Qu'est-ce que Raphaël prend ? Le train, le bus, ou la voiture.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
@@ -1552,6 +1543,7 @@
 narrateur|Le train, le bus, ou la voiture.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1576,17 +1568,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Raphaël prend le train en bois. Les roues font un petit clic sur le carrelage. La porte de la cuisine s'ouvre. Mila entre, les joues roses. Bonjour, Mila. Bonjour, Raphaël. Le train s'arrête près de ses pieds. Tu veux une rondelle, Mila ? S'il te plaît. Papa tend une pomme, toute lisse. Merci. Moi aussi ? Demande. S'il te plaît. Une rondelle froide dans sa main. Merci, papa.</t>
+          <t>Raphaël prend le train en bois. Les roues font un petit clic sur le carrelage. La porte s'ouvre. Mila entre, les joues roses. Bonjour, Mila. Bonjour, Raphaël. Le train s'arrête près de ses pieds. C'est le voyage des pommes. J'apporte le bol ? Il est un peu lourd. On le met sur le train. Ils glissent le bol jaune entre deux wagons. Merci. Il tient.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sami entend le train, tout loin. Un copain entre. Sami dit &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt;. Il tend une pomme. Il dit s'il te plaît. Le copain dit merci. Maman sourit.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël prend le train en bois. Les roues font un petit clic sur le carrelage. La porte s'ouvre. Mila entre, les joues roses. Bonjour, Mila. Bonjour, Raphaël. Le train s'arrête près de ses pieds. C'est le voyage des pommes. J'apporte le bol ? Il est un peu lourd. On le met sur le train. Ils glissent le bol jaune entre deux wagons. Merci. Il tient.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Sami entend le train, tout loin. Un copain entre. Sami dit &lt;emphasis&gt;bonjour&lt;/emphasis&gt;. Il tend une pomme. Il dit s'il te plaît. Le copain dit merci. Maman sourit. [pause]</t>
+          <t>Raphaël prend le train en bois. Les roues font un petit clic sur le carrelage. La porte s'ouvre. Mila entre, les joues roses. Bonjour, Mila. Bonjour, Raphaël. Le train s'arrête près de ses pieds. C'est le voyage des pommes. J'apporte le bol ? Il est un peu lourd. On le met sur le train. Ils glissent le bol jaune entre deux wagons. Merci. Il tient.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -1718,20 +1710,16 @@
         <is>
           <t>narrateur|Raphaël prend le train en bois.
 narrateur|Les roues font un petit clic sur le carrelage.
-narrateur|La porte de la cuisine s'ouvre.
-narrateur|Mila entre, les joues roses.
+narrateur|La porte s'ouvre. Mila entre, les joues roses.
 enfant-m|Bonjour, Mila.
 enfant-f|Bonjour, Raphaël.
 narrateur|Le train s'arrête près de ses pieds.
-papa|Tu veux une rondelle, Mila ?
-enfant-f|S'il te plaît.
-narrateur|Papa tend une pomme, toute lisse.
-enfant-f|Merci.
-enfant-m|Moi aussi ?
-papa|Demande.
-enfant-m|S'il te plaît.
-narrateur|Une rondelle froide dans sa main.
-enfant-m|Merci, papa.</t>
+enfant-m|C'est le voyage des pommes.
+enfant-f|J'apporte le bol ?
+papa|Il est un peu lourd.
+enfant-m|On le met sur le train.
+narrateur|Ils glissent le bol jaune entre deux wagons.
+enfant-f|Merci. Il tient.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1768,12 +1756,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;On dit &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt;, s'il te plaît, merci ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila arrive. Raphaël dit quoi ?</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;On dit &lt;emphasis&gt;bonjour&lt;/emphasis&gt;, s'il te plaît, merci ?&lt;/slow&gt;</t>
+          <t>Mila arrive. Raphaël dit quoi ?</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -1793,12 +1781,12 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
+          <t>Bonjour.</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
           <t>Il dit bonjour.</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>Dis : bonjour.</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr"/>
@@ -1926,6 +1914,7 @@
           <t>narrateur|Mila arrive. Raphaël dit quoi ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1950,17 +1939,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a dit bonjour. Mila a une rondelle. Le train attend près du bol jaune. On joue encore ? Oui. On s'installe.</t>
+          <t>Raphaël a dit bonjour. Le bol est sur le train. On cherche l'arrêt. Choisissez l'endroit.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Oui. &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt;, s'il te plaît, merci. Sami respire. Papa est là. On dit bonjour. On dit s'il te plaît. On dit merci.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël a dit bonjour. Le bol est sur le train. On cherche l'arrêt. Choisissez l'endroit.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Oui. &lt;emphasis&gt;bonjour&lt;/emphasis&gt;, s'il te plaît, merci. Sami respire. Papa est là. On dit bonjour. On dit s'il te plaît. On dit merci. [pause]</t>
+          <t>Raphaël a dit bonjour. Le bol est sur le train. On cherche l'arrêt. Choisissez l'endroit.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -2095,12 +2084,12 @@
       <c r="AW6" t="inlineStr">
         <is>
           <t>narrateur|Raphaël a dit bonjour.
-narrateur|Mila a une rondelle.
-narrateur|Le train attend près du bol jaune.
-enfant-m|On joue encore ?
-maman|Oui. On s'installe.</t>
-        </is>
-      </c>
+narrateur|Le bol est sur le train.
+enfant-m|On cherche l'arrêt.
+maman|Choisissez l'endroit.</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2125,17 +2114,17 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On va où, dans la cuisine ? La table, la fenêtre, ou le tabouret.</t>
+          <t>L'arrêt, c'est où ? La table, la fenêtre, ou le tabouret.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;On peut prendre Tom, Léa, ou Sami.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'arrêt, c'est où ? La table, la fenêtre, ou le tabouret.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;On peut prendre Tom, Léa, ou Sami.&lt;/slow&gt; [pause]</t>
+          <t>L'arrêt, c'est où ? La table, la fenêtre, ou le tabouret.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
@@ -2293,10 +2282,11 @@
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On va où, dans la cuisine ?
+          <t>narrateur|L'arrêt, c'est où ?
 narrateur|La table, la fenêtre, ou le tabouret.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2321,17 +2311,17 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Raphaël pose le train près de la table. Le bol jaune est au milieu. Mila tire une chaise, tout doux. Une assiette, Raphaël ? S'il te plaît. L'assiette est ronde, un peu froide. Merci, maman. Il pose une rondelle dans l'assiette de Mila. Merci, Raphaël.</t>
+          <t>Ils poussent le train jusqu'à la table. Le bol jaune glisse un peu. Raphaël le rattrape. Arrêt table. On décharge ici. Mila tire une chaise. Raphaël pose deux assiettes. Vous avez besoin d'aide ? On fait le voyage.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sami dit &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt; à Tom. Il demande le train en bois : s'il te plaît. Tom dit merci. C'est le matin. Papa montre le geste, lentement. On dit bonjour. On dit s'il te plaît. On dit merci.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Ils poussent le train jusqu'à la table. Le bol jaune glisse un peu. Raphaël le rattrape. Arrêt table. On décharge ici. Mila tire une chaise. Raphaël pose deux assiettes. Vous avez besoin d'aide ? On fait le voyage.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Sami dit &lt;emphasis&gt;bonjour&lt;/emphasis&gt; à Tom. Il demande le train en bois : s'il te plaît. Tom dit merci. C'est le matin. Papa montre le geste, lentement. On dit bonjour. On dit s'il te plaît. On dit merci. [pause]</t>
+          <t>Ils poussent le train jusqu'à la table. Le bol jaune glisse un peu. Raphaël le rattrape. Arrêt table. On décharge ici. Mila tire une chaise. Raphaël pose deux assiettes. Vous avez besoin d'aide ? On fait le voyage.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
@@ -2461,15 +2451,13 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël pose le train près de la table.
-narrateur|Le bol jaune est au milieu.
-narrateur|Mila tire une chaise, tout doux.
-maman|Une assiette, Raphaël ?
-enfant-m|S'il te plaît.
-narrateur|L'assiette est ronde, un peu froide.
-enfant-m|Merci, maman.
-narrateur|Il pose une rondelle dans l'assiette de Mila.
-enfant-f|Merci, Raphaël.</t>
+          <t>narrateur|Ils poussent le train jusqu'à la table.
+narrateur|Le bol jaune glisse un peu. Raphaël le rattrape.
+enfant-m|Arrêt table.
+enfant-f|On décharge ici.
+narrateur|Mila tire une chaise. Raphaël pose deux assiettes.
+maman|Vous avez besoin d'aide ?
+enfant-m|On fait le voyage.</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -2501,17 +2489,17 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>C'est quel moment ? Le matin, après la sieste, ou le soir.</t>
+          <t>Qui pousse pour livrer ? Mila, Raphaël, ou tous les deux.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;On peut prendre le matin, après la sieste, ou le soir.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
+          <t>Qui pousse pour livrer ? Mila, Raphaël, ou tous les deux.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;On peut prendre le matin, après la sieste, ou le soir.&lt;/slow&gt; [pause]</t>
+          <t>Qui pousse pour livrer ? Mila, Raphaël, ou tous les deux.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
@@ -2529,7 +2517,7 @@
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>le matin</t>
+          <t>Mila</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2539,7 +2527,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>après la sieste</t>
+          <t>Raphaël</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -2549,7 +2537,7 @@
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>le soir</t>
+          <t>tous les deux</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
@@ -2665,10 +2653,11 @@
       <c r="AV9" s="2" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|C'est quel moment ?
-narrateur|Le matin, après la sieste, ou le soir.</t>
-        </is>
-      </c>
+          <t>narrateur|Qui pousse pour livrer ?
+narrateur|Mila, Raphaël, ou tous les deux.</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2693,17 +2682,17 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. Le soleil touche une roue du train. Ça sent le lait et la pomme. Encore une rondelle, Mila ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Raphaël fait le tour du bol avec le train.</t>
+          <t>Je pousse. Moi, je garde les pommes. Mila pousse le train, tout autour de l'arrêt. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sami a choisi le train. Puis Tom. Puis le matin. Un crochet tient bien le manteau. Sami marche près de papa. On dit &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Je pousse. Moi, je garde les pommes. Mila pousse le train, tout autour de l'arrêt. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Sami a choisi le train. Puis Tom. Puis le matin. Un crochet tient bien le manteau. Sami marche près de papa. On dit &lt;emphasis&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa. [pause]</t>
+          <t>Je pousse. Moi, je garde les pommes. Mila pousse le train, tout autour de l'arrêt. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
@@ -2833,14 +2822,14 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|C'est le matin.
-narrateur|Le soleil touche une roue du train.
-narrateur|Ça sent le lait et la pomme.
-papa|Encore une rondelle, Mila ?
-enfant-f|S'il te plaît.
-narrateur|La pomme est froide, un peu sucrée.
-enfant-f|Merci, papa.
-narrateur|Raphaël fait le tour du bol avec le train.</t>
+          <t>enfant-f|Je pousse.
+enfant-m|Moi, je garde les pommes.
+narrateur|Mila pousse le train, tout autour de l'arrêt.
+narrateur|Le bol avance. Une rondelle tremble, puis tient.
+enfant-m|Terminus, les pommes.
+narrateur|Ils posent une rondelle chacun.
+enfant-f|On croque.
+narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -2872,17 +2861,17 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Le train s'arrête contre le bol jaune. Terminus, les pommes. Merci pour le voyage. Bonne journée, vous deux. L'histoire est finie.</t>
+          <t>Le train s'arrête contre le bol jaune. Terminus, les pommes. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le train s'arrête contre le bol jaune. Terminus, les pommes. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>Le train s'arrête contre le bol jaune. Terminus, les pommes. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
@@ -3014,11 +3003,12 @@
         <is>
           <t>narrateur|Le train s'arrête contre le bol jaune.
 enfant-m|Terminus, les pommes.
-enfant-f|Merci pour le voyage.
-maman|Bonne journée, vous deux.
+papa|Vous avez fait le voyage.
+narrateur|Les assiettes sont vides, maintenant.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3043,17 +3033,17 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>C'est après la sieste. La casserole est encore tiède. Mila bâille, tout petit. On joue tout doux. Raphaël pousse le train sans le bruit des roues. Encore une rondelle ? S'il te plaît, papa. Papa en glisse une. Merci.</t>
+          <t>Je pousse. Moi, je dis les arrêts. Raphaël pousse le train. Mila annonce. Prochain : les assiettes. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sami s'arrête près de après la sieste. Tom est rangé. Ça sent le pain chaud. Sami boit une gorgée d'eau. On dit &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Je pousse. Moi, je dis les arrêts. Raphaël pousse le train. Mila annonce. Prochain : les assiettes. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Sami s'arrête près de après la sieste. Tom est rangé. Ça sent le pain chaud. Sami boit une gorgée d'eau. On dit &lt;emphasis&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa. [pause]</t>
+          <t>Je pousse. Moi, je dis les arrêts. Raphaël pousse le train. Mila annonce. Prochain : les assiettes. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
@@ -3183,15 +3173,15 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|C'est après la sieste.
-narrateur|La casserole est encore tiède.
-narrateur|Mila bâille, tout petit.
-papa|On joue tout doux.
-narrateur|Raphaël pousse le train sans le bruit des roues.
-enfant-f|Encore une rondelle ?
-enfant-m|S'il te plaît, papa.
-narrateur|Papa en glisse une.
-enfant-m|Merci.</t>
+          <t>enfant-m|Je pousse.
+enfant-f|Moi, je dis les arrêts.
+narrateur|Raphaël pousse le train. Mila annonce.
+enfant-f|Prochain : les assiettes.
+narrateur|Le bol avance. Une rondelle tremble, puis tient.
+enfant-m|Terminus, les pommes.
+narrateur|Ils posent une rondelle chacun.
+enfant-f|On croque.
+narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -3223,17 +3213,17 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Le train dort contre l'assiette. Chut. Il fait la sieste aussi. Vous avez bien partagé. L'histoire est finie.</t>
+          <t>Le train s'arrête contre le bol jaune. Terminus, les pommes. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le train s'arrête contre le bol jaune. Terminus, les pommes. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>Le train s'arrête contre le bol jaune. Terminus, les pommes. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
@@ -3363,12 +3353,14 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|Le train dort contre l'assiette.
-enfant-m|Chut. Il fait la sieste aussi.
-maman|Vous avez bien partagé.
+          <t>narrateur|Le train s'arrête contre le bol jaune.
+enfant-m|Terminus, les pommes.
+papa|Vous avez fait le voyage.
+narrateur|Les assiettes sont vides, maintenant.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3393,17 +3385,17 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>C'est le soir. Une lampe éclaire la table. Le marché, dehors, s'est tu. On range bientôt. Raphaël gare le train sous sa chaise. Encore une pomme ? S'il te plaît. La dernière rondelle brille. Merci.</t>
+          <t>Ensemble. Toi devant. Moi derrière. Ils poussent le train avec quatre mains. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sami se souvient de le train. Et de Tom. Et de le soir. Les chaussures font toc toc. Sami tend le soir à maman. On dit &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Ensemble. Toi devant. Moi derrière. Ils poussent le train avec quatre mains. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Sami se souvient de le train. Et de Tom. Et de le soir. Les chaussures font toc toc. Sami tend le soir à maman. On dit &lt;emphasis&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa. [pause]</t>
+          <t>Ensemble. Toi devant. Moi derrière. Ils poussent le train avec quatre mains. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
@@ -3533,15 +3525,14 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|C'est le soir.
-narrateur|Une lampe éclaire la table.
-narrateur|Le marché, dehors, s'est tu.
-maman|On range bientôt.
-narrateur|Raphaël gare le train sous sa chaise.
-enfant-f|Encore une pomme ?
-enfant-m|S'il te plaît.
-narrateur|La dernière rondelle brille.
-enfant-f|Merci.</t>
+          <t>enfant-m|Ensemble.
+enfant-f|Toi devant. Moi derrière.
+narrateur|Ils poussent le train avec quatre mains.
+narrateur|Le bol avance. Une rondelle tremble, puis tient.
+enfant-m|Terminus, les pommes.
+narrateur|Ils posent une rondelle chacun.
+enfant-f|On croque.
+narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
@@ -3573,17 +3564,17 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Le bol jaune est vide. Le train est au garage. À demain, Mila. À demain. L'histoire est finie.</t>
+          <t>Le train s'arrête contre le bol jaune. Terminus, les pommes. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le train s'arrête contre le bol jaune. Terminus, les pommes. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>Le train s'arrête contre le bol jaune. Terminus, les pommes. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr"/>
@@ -3713,13 +3704,14 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|Le bol jaune est vide.
-papa|Le train est au garage.
-enfant-m|À demain, Mila.
-enfant-f|À demain.
+          <t>narrateur|Le train s'arrête contre le bol jaune.
+enfant-m|Terminus, les pommes.
+papa|Vous avez fait le voyage.
+narrateur|Les assiettes sont vides, maintenant.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3744,17 +3736,17 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Raphaël va près de la fenêtre, avec le train. La vitre est un peu floue. Mila trace un petit rond du doigt. Le torchon, pour la vitre ? S'il te plaît. Le torchon est doux, un peu épais. Merci, papa. Il essuie un rond. Le marché apparaît. Je vois le stand des pommes.</t>
+          <t>Le train va près de la fenêtre. La vitre est un peu floue. Je dessine l'arrêt, dans la buée. Mila trace un petit rond. J'essuie juste à côté. Le rond reste. Le marché apparaît autour du rond. Arrêt fenêtre.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sami dit &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt; à Tom. Il demande le train : s'il te plaît. Tom dit merci. C'est après la sieste. Papa dit : je suis là. On dit bonjour. On dit s'il te plaît. On dit merci.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le train va près de la fenêtre. La vitre est un peu floue. Je dessine l'arrêt, dans la buée. Mila trace un petit rond. J'essuie juste à côté. Le rond reste. Le marché apparaît autour du rond. Arrêt fenêtre.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Sami dit &lt;emphasis&gt;bonjour&lt;/emphasis&gt; à Tom. Il demande le train : s'il te plaît. Tom dit merci. C'est après la sieste. Papa dit : je suis là. On dit bonjour. On dit s'il te plaît. On dit merci. [pause]</t>
+          <t>Le train va près de la fenêtre. La vitre est un peu floue. Je dessine l'arrêt, dans la buée. Mila trace un petit rond. J'essuie juste à côté. Le rond reste. Le marché apparaît autour du rond. Arrêt fenêtre.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
@@ -3884,15 +3876,13 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël va près de la fenêtre, avec le train.
+          <t>narrateur|Le train va près de la fenêtre.
 narrateur|La vitre est un peu floue.
-narrateur|Mila trace un petit rond du doigt.
-papa|Le torchon, pour la vitre ?
-enfant-m|S'il te plaît.
-narrateur|Le torchon est doux, un peu épais.
-enfant-m|Merci, papa.
-narrateur|Il essuie un rond. Le marché apparaît.
-enfant-f|Je vois le stand des pommes.</t>
+enfant-f|Je dessine l'arrêt, dans la buée.
+narrateur|Mila trace un petit rond.
+enfant-m|J'essuie juste à côté. Le rond reste.
+narrateur|Le marché apparaît autour du rond.
+enfant-m|Arrêt fenêtre.</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
@@ -3924,17 +3914,17 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>C'est quel moment ? Le matin, après la sieste, ou le soir.</t>
+          <t>Qui pousse pour livrer ? Mila, Raphaël, ou tous les deux.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;On peut prendre le matin, après la sieste, ou le soir.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
+          <t>Qui pousse pour livrer ? Mila, Raphaël, ou tous les deux.</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;On peut prendre le matin, après la sieste, ou le soir.&lt;/slow&gt; [pause]</t>
+          <t>Qui pousse pour livrer ? Mila, Raphaël, ou tous les deux.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr"/>
@@ -3952,7 +3942,7 @@
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>le matin</t>
+          <t>Mila</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -3962,7 +3952,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>après la sieste</t>
+          <t>Raphaël</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -3972,7 +3962,7 @@
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>le soir</t>
+          <t>tous les deux</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
@@ -4088,10 +4078,11 @@
       <c r="AV17" s="2" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|C'est quel moment ?
-narrateur|Le matin, après la sieste, ou le soir.</t>
-        </is>
-      </c>
+          <t>narrateur|Qui pousse pour livrer ?
+narrateur|Mila, Raphaël, ou tous les deux.</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4116,17 +4107,17 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. Le soleil chauffe la vitre. Raphaël pose le train sur le rebord. Une rondelle, en regardant ? S'il te plaît. Mila mange, les yeux dehors. Merci. Mon train va au marché.</t>
+          <t>Je pousse. Moi, je garde les pommes. Mila pousse le train, tout autour de l'arrêt. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Avec le matin. Après Léa. Près de le train. Sami s'arrête. Un vélo passe au loin. Sami chuchote : c'est fini. On dit &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Je pousse. Moi, je garde les pommes. Mila pousse le train, tout autour de l'arrêt. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Avec le matin. Après Léa. Près de le train. Sami s'arrête. Un vélo passe au loin. Sami chuchote : c'est fini. On dit &lt;emphasis&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa. [pause]</t>
+          <t>Je pousse. Moi, je garde les pommes. Mila pousse le train, tout autour de l'arrêt. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
@@ -4256,14 +4247,14 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|C'est le matin.
-narrateur|Le soleil chauffe la vitre.
-narrateur|Raphaël pose le train sur le rebord.
-maman|Une rondelle, en regardant ?
-enfant-f|S'il te plaît.
-narrateur|Mila mange, les yeux dehors.
-enfant-f|Merci.
-enfant-m|Mon train va au marché.</t>
+          <t>enfant-f|Je pousse.
+enfant-m|Moi, je garde les pommes.
+narrateur|Mila pousse le train, tout autour de l'arrêt.
+narrateur|Le bol avance. Une rondelle tremble, puis tient.
+enfant-m|Terminus, les pommes.
+narrateur|Ils posent une rondelle chacun.
+enfant-f|On croque.
+narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -4295,17 +4286,17 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Un oiseau passe derrière la vitre. Arrêt marché. Vous avez bien regardé ensemble. L'histoire est finie.</t>
+          <t>Le train rentre sous le rebord. Terminus, les pommes. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le train rentre sous le rebord. Terminus, les pommes. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>Le train rentre sous le rebord. Terminus, les pommes. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
@@ -4435,12 +4426,14 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|Un oiseau passe derrière la vitre.
-enfant-m|Arrêt marché.
-papa|Vous avez bien regardé ensemble.
+          <t>narrateur|Le train rentre sous le rebord.
+enfant-m|Terminus, les pommes.
+papa|Vous avez fait le voyage.
+narrateur|Les assiettes sont vides, maintenant.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4465,17 +4458,17 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>C'est après la sieste. La lumière est douce, un peu jaune. Raphaël pousse le train le long du rebord. Il fait moins de bruit. Une rondelle calme ? S'il te plaît. Merci.</t>
+          <t>Je pousse. Moi, je dis les arrêts. Raphaël pousse le train. Mila annonce. Prochain : les assiettes. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sami range Léa. après la sieste reste près de le train. Le savon sent bon. Sami écoute papa encore une fois. On dit &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Je pousse. Moi, je dis les arrêts. Raphaël pousse le train. Mila annonce. Prochain : les assiettes. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Sami range Léa. après la sieste reste près de le train. Le savon sent bon. Sami écoute papa encore une fois. On dit &lt;emphasis&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa. [pause]</t>
+          <t>Je pousse. Moi, je dis les arrêts. Raphaël pousse le train. Mila annonce. Prochain : les assiettes. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
@@ -4605,13 +4598,15 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|C'est après la sieste.
-narrateur|La lumière est douce, un peu jaune.
-narrateur|Raphaël pousse le train le long du rebord.
-enfant-f|Il fait moins de bruit.
-papa|Une rondelle calme ?
-enfant-m|S'il te plaît.
-enfant-m|Merci.</t>
+          <t>enfant-m|Je pousse.
+enfant-f|Moi, je dis les arrêts.
+narrateur|Raphaël pousse le train. Mila annonce.
+enfant-f|Prochain : les assiettes.
+narrateur|Le bol avance. Une rondelle tremble, puis tient.
+enfant-m|Terminus, les pommes.
+narrateur|Ils posent une rondelle chacun.
+enfant-f|On croque.
+narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -4643,17 +4638,17 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Le train s'arrête contre le bois de la fenêtre. Il dort au soleil. On reste encore un peu. L'histoire est finie.</t>
+          <t>Le train rentre sous le rebord. Terminus, les pommes. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le train rentre sous le rebord. Terminus, les pommes. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>Le train rentre sous le rebord. Terminus, les pommes. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr"/>
@@ -4783,12 +4778,14 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|Le train s'arrête contre le bois de la fenêtre.
-enfant-f|Il dort au soleil.
-maman|On reste encore un peu.
+          <t>narrateur|Le train rentre sous le rebord.
+enfant-m|Terminus, les pommes.
+papa|Vous avez fait le voyage.
+narrateur|Les assiettes sont vides, maintenant.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4813,17 +4810,17 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>C'est le soir. La vitre devient sombre. Des lampes s'allument au marché. On dit au revoir à la rue. Raphaël descend le train du rebord. Encore une pomme ? S'il te plaît, on demande. S'il te plaît. Merci.</t>
+          <t>Ensemble. Toi devant. Moi derrière. Ils poussent le train avec quatre mains. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;le soir est là. Léa aussi. le train reste dans le souvenir. Une feuille tombe. Sami raccroche un linge. On dit &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Ensemble. Toi devant. Moi derrière. Ils poussent le train avec quatre mains. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>le soir est là. Léa aussi. le train reste dans le souvenir. Une feuille tombe. Sami raccroche un linge. On dit &lt;emphasis&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa. [pause]</t>
+          <t>Ensemble. Toi devant. Moi derrière. Ils poussent le train avec quatre mains. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
@@ -4953,15 +4950,14 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|C'est le soir.
-narrateur|La vitre devient sombre.
-narrateur|Des lampes s'allument au marché.
-maman|On dit au revoir à la rue.
-narrateur|Raphaël descend le train du rebord.
-enfant-f|Encore une pomme ?
-papa|S'il te plaît, on demande.
-enfant-f|S'il te plaît.
-enfant-f|Merci.</t>
+          <t>enfant-m|Ensemble.
+enfant-f|Toi devant. Moi derrière.
+narrateur|Ils poussent le train avec quatre mains.
+narrateur|Le bol avance. Une rondelle tremble, puis tient.
+enfant-m|Terminus, les pommes.
+narrateur|Ils posent une rondelle chacun.
+enfant-f|On croque.
+narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
@@ -4993,17 +4989,17 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Le train rentre dans la gare, sous la table. Les lampes, c'est fini. À demain, le marché. L'histoire est finie.</t>
+          <t>Le train rentre sous le rebord. Terminus, les pommes. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le train rentre sous le rebord. Terminus, les pommes. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>Le train rentre sous le rebord. Terminus, les pommes. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr"/>
@@ -5133,12 +5129,14 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|Le train rentre dans la gare, sous la table.
-enfant-m|Les lampes, c'est fini.
-papa|À demain, le marché.
+          <t>narrateur|Le train rentre sous le rebord.
+enfant-m|Terminus, les pommes.
+papa|Vous avez fait le voyage.
+narrateur|Les assiettes sont vides, maintenant.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5163,17 +5161,17 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Raphaël glisse le train près du tabouret. Le tabouret est bas, en bois clair. Mila s'assoit, les pieds qui balancent. Je peux le tabouret, après ? S'il te plaît, tu attends. D'accord. Il pose le bol jaune sur les genoux de Mila. Merci. Le tabouret fait un tout petit craquement.</t>
+          <t>Le train glisse jusqu'au tabouret. Le tabouret est bas, en bois clair. Je m'assois. C'est la gare haute. Je peux après ? Oui. Quand le bol est arrivé. Raphaël pose le bol sur le bois, près d'elle. Le tabouret fait un petit craquement.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sami dit &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt; à Tom. Il demande le train : s'il te plaît. Tom dit merci. C'est le soir. Papa reste tout près. On dit bonjour. On dit s'il te plaît. On dit merci.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le train glisse jusqu'au tabouret. Le tabouret est bas, en bois clair. Je m'assois. C'est la gare haute. Je peux après ? Oui. Quand le bol est arrivé. Raphaël pose le bol sur le bois, près d'elle. Le tabouret fait un petit craquement.</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Sami dit &lt;emphasis&gt;bonjour&lt;/emphasis&gt; à Tom. Il demande le train : s'il te plaît. Tom dit merci. C'est le soir. Papa reste tout près. On dit bonjour. On dit s'il te plaît. On dit merci. [pause]</t>
+          <t>Le train glisse jusqu'au tabouret. Le tabouret est bas, en bois clair. Je m'assois. C'est la gare haute. Je peux après ? Oui. Quand le bol est arrivé. Raphaël pose le bol sur le bois, près d'elle. Le tabouret fait un petit craquement.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr"/>
@@ -5303,15 +5301,13 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël glisse le train près du tabouret.
+          <t>narrateur|Le train glisse jusqu'au tabouret.
 narrateur|Le tabouret est bas, en bois clair.
-narrateur|Mila s'assoit, les pieds qui balancent.
-enfant-m|Je peux le tabouret, après ?
-enfant-f|S'il te plaît, tu attends.
-enfant-m|D'accord.
-narrateur|Il pose le bol jaune sur les genoux de Mila.
-enfant-f|Merci.
-narrateur|Le tabouret fait un tout petit craquement.</t>
+enfant-f|Je m'assois. C'est la gare haute.
+enfant-m|Je peux après ?
+enfant-f|Oui. Quand le bol est arrivé.
+narrateur|Raphaël pose le bol sur le bois, près d'elle.
+narrateur|Le tabouret fait un petit craquement.</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
@@ -5343,17 +5339,17 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>C'est quel moment ? Le matin, après la sieste, ou le soir.</t>
+          <t>Qui pousse pour livrer ? Mila, Raphaël, ou tous les deux.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;On peut prendre le matin, après la sieste, ou le soir.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
+          <t>Qui pousse pour livrer ? Mila, Raphaël, ou tous les deux.</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;On peut prendre le matin, après la sieste, ou le soir.&lt;/slow&gt; [pause]</t>
+          <t>Qui pousse pour livrer ? Mila, Raphaël, ou tous les deux.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr"/>
@@ -5371,7 +5367,7 @@
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>le matin</t>
+          <t>Mila</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -5381,7 +5377,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>après la sieste</t>
+          <t>Raphaël</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -5391,7 +5387,7 @@
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>le soir</t>
+          <t>tous les deux</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
@@ -5507,10 +5503,11 @@
       <c r="AV25" s="2" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|C'est quel moment ?
-narrateur|Le matin, après la sieste, ou le soir.</t>
-        </is>
-      </c>
+          <t>narrateur|Qui pousse pour livrer ?
+narrateur|Mila, Raphaël, ou tous les deux.</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5535,17 +5532,17 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. Le soleil touche les pieds de Mila. Raphaël fait le tour du tabouret avec le train. Une rondelle, du haut du tabouret ? S'il te plaît. Merci. Mon tour ? Oui. Merci d'avoir attendu.</t>
+          <t>Je pousse. Moi, je garde les pommes. Mila pousse le train, tout autour de l'arrêt. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sami rejoint le matin. Sami est rangé. le train est fini. Une chaussette est encore sablée. Sami ferme le sac. On dit &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Je pousse. Moi, je garde les pommes. Mila pousse le train, tout autour de l'arrêt. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint le matin. Sami est rangé. le train est fini. Une chaussette est encore sablée. Sami ferme le sac. On dit &lt;emphasis&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa. [pause]</t>
+          <t>Je pousse. Moi, je garde les pommes. Mila pousse le train, tout autour de l'arrêt. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
@@ -5675,14 +5672,14 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|C'est le matin.
-narrateur|Le soleil touche les pieds de Mila.
-narrateur|Raphaël fait le tour du tabouret avec le train.
-papa|Une rondelle, du haut du tabouret ?
-enfant-f|S'il te plaît.
-enfant-f|Merci.
-enfant-m|Mon tour ?
-enfant-f|Oui. Merci d'avoir attendu.</t>
+          <t>enfant-f|Je pousse.
+enfant-m|Moi, je garde les pommes.
+narrateur|Mila pousse le train, tout autour de l'arrêt.
+narrateur|Le bol avance. Une rondelle tremble, puis tient.
+enfant-m|Terminus, les pommes.
+narrateur|Ils posent une rondelle chacun.
+enfant-f|On croque.
+narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
@@ -5714,17 +5711,17 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Raphaël s'assoit. Le train monte avec lui. Vous avez attendu chacun votre tour. Les pommes aussi. L'histoire est finie.</t>
+          <t>Le train dort sous le tabouret. Terminus, les pommes. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le train dort sous le tabouret. Terminus, les pommes. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>Le train dort sous le tabouret. Terminus, les pommes. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr"/>
@@ -5854,12 +5851,14 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël s'assoit. Le train monte avec lui.
-maman|Vous avez attendu chacun votre tour.
-enfant-m|Les pommes aussi.
+          <t>narrateur|Le train dort sous le tabouret.
+enfant-m|Terminus, les pommes.
+papa|Vous avez fait le voyage.
+narrateur|Les assiettes sont vides, maintenant.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5884,17 +5883,17 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>C'est après la sieste. Mila pose la tête un instant. Raphaël arrête le train contre un pied du tabouret. Tout doux. Une rondelle, s'il te plaît. Papa en pose deux, tout près. Merci. Une pour Mila.</t>
+          <t>Je pousse. Moi, je dis les arrêts. Raphaël pousse le train. Mila annonce. Prochain : les assiettes. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Près de après la sieste. Sami pose Sami. le train est derrière. On rit un peu. Sami dit merci à papa. On dit &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Je pousse. Moi, je dis les arrêts. Raphaël pousse le train. Mila annonce. Prochain : les assiettes. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Près de après la sieste. Sami pose Sami. le train est derrière. On rit un peu. Sami dit merci à papa. On dit &lt;emphasis&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa. [pause]</t>
+          <t>Je pousse. Moi, je dis les arrêts. Raphaël pousse le train. Mila annonce. Prochain : les assiettes. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
@@ -6024,13 +6023,15 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|C'est après la sieste.
-narrateur|Mila pose la tête un instant.
-narrateur|Raphaël arrête le train contre un pied du tabouret.
-maman|Tout doux.
-enfant-m|Une rondelle, s'il te plaît.
-narrateur|Papa en pose deux, tout près.
-enfant-m|Merci. Une pour Mila.</t>
+          <t>enfant-m|Je pousse.
+enfant-f|Moi, je dis les arrêts.
+narrateur|Raphaël pousse le train. Mila annonce.
+enfant-f|Prochain : les assiettes.
+narrateur|Le bol avance. Une rondelle tremble, puis tient.
+enfant-m|Terminus, les pommes.
+narrateur|Ils posent une rondelle chacun.
+enfant-f|On croque.
+narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
@@ -6062,17 +6063,17 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Mila ouvre les yeux. Merci. Elle était pour moi. Le train a attendu aussi. L'histoire est finie.</t>
+          <t>Le train dort sous le tabouret. Terminus, les pommes. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le train dort sous le tabouret. Terminus, les pommes. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>Le train dort sous le tabouret. Terminus, les pommes. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr"/>
@@ -6202,12 +6203,14 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|Mila ouvre les yeux.
-enfant-f|Merci. Elle était pour moi.
-papa|Le train a attendu aussi.
+          <t>narrateur|Le train dort sous le tabouret.
+enfant-m|Terminus, les pommes.
+papa|Vous avez fait le voyage.
+narrateur|Les assiettes sont vides, maintenant.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6232,17 +6235,17 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>C'est le soir. L'ombre du tabouret s'allonge. Raphaël gare le train dessous. Je descends ? Oui. Merci, Mila. Une dernière rondelle ? S'il te plaît. Merci.</t>
+          <t>Ensemble. Toi devant. Moi derrière. Ils poussent le train avec quatre mains. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sami montre le soir. Papa a vu le train. Et Sami. Un linge sèche à l'air. Sami pose Sami à sa place. On dit &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Ensemble. Toi devant. Moi derrière. Ils poussent le train avec quatre mains. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Sami montre le soir. Papa a vu le train. Et Sami. Un linge sèche à l'air. Sami pose Sami à sa place. On dit &lt;emphasis&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa. [pause]</t>
+          <t>Ensemble. Toi devant. Moi derrière. Ils poussent le train avec quatre mains. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
@@ -6372,14 +6375,14 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|C'est le soir.
-narrateur|L'ombre du tabouret s'allonge.
-narrateur|Raphaël gare le train dessous.
-enfant-f|Je descends ?
-enfant-m|Oui. Merci, Mila.
-maman|Une dernière rondelle ?
-enfant-m|S'il te plaît.
-enfant-m|Merci.</t>
+          <t>enfant-m|Ensemble.
+enfant-f|Toi devant. Moi derrière.
+narrateur|Ils poussent le train avec quatre mains.
+narrateur|Le bol avance. Une rondelle tremble, puis tient.
+enfant-m|Terminus, les pommes.
+narrateur|Ils posent une rondelle chacun.
+enfant-f|On croque.
+narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
@@ -6411,17 +6414,17 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Le tabouret est vide. Le train dort en dessous. Vous avez partagé le siège et les pommes. L'histoire est finie.</t>
+          <t>Le train dort sous le tabouret. Terminus, les pommes. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le train dort sous le tabouret. Terminus, les pommes. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>Le train dort sous le tabouret. Terminus, les pommes. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
@@ -6551,12 +6554,14 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|Le tabouret est vide.
-narrateur|Le train dort en dessous.
-papa|Vous avez partagé le siège et les pommes.
+          <t>narrateur|Le train dort sous le tabouret.
+enfant-m|Terminus, les pommes.
+papa|Vous avez fait le voyage.
+narrateur|Les assiettes sont vides, maintenant.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6581,17 +6586,17 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Raphaël prend le bus rouge. Dehors, un vrai bus passe, tout bas. Mila pousse la porte de la cuisine. Bonjour, Mila. Bonjour. Raphaël veut essuyer une miette. Le torchon, s'il te plaît. Voilà le torchon. Merci, maman. Il essuie le rebord du bol. Tu veux une rondelle ? S'il te plaît. Merci.</t>
+          <t>Raphaël prend le bus rouge. Dehors, un vrai bus passe, tout bas. Mila pousse la porte. Bonjour, Mila. Bonjour. Une miette colle au rebord du bol. Le torchon, s'il te plaît. Le voilà. Merci. Il essuie. Le bol est propre. Les pommes montent dans le bus. Ils posent deux rondelles sur les sièges.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sami entend le bus. Une copine entre. Sami dit &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt;. Il demande le torchon : s'il te plaît. Il dit merci. Papa coupe encore une pomme.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël prend le bus rouge. Dehors, un vrai bus passe, tout bas. Mila pousse la porte. Bonjour, Mila. Bonjour. Une miette colle au rebord du bol. Le torchon, s'il te plaît. Le voilà. Merci. Il essuie. Le bol est propre. Les pommes montent dans le bus. Ils posent deux rondelles sur les sièges.</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Sami entend le bus. Une copine entre. Sami dit &lt;emphasis&gt;bonjour&lt;/emphasis&gt;. Il demande le torchon : s'il te plaît. Il dit merci. Papa coupe encore une pomme. [pause]</t>
+          <t>Raphaël prend le bus rouge. Dehors, un vrai bus passe, tout bas. Mila pousse la porte. Bonjour, Mila. Bonjour. Une miette colle au rebord du bol. Le torchon, s'il te plaît. Le voilà. Merci. Il essuie. Le bol est propre. Les pommes montent dans le bus. Ils posent deux rondelles sur les sièges.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
@@ -6723,17 +6728,16 @@
         <is>
           <t>narrateur|Raphaël prend le bus rouge.
 narrateur|Dehors, un vrai bus passe, tout bas.
-narrateur|Mila pousse la porte de la cuisine.
+narrateur|Mila pousse la porte.
 enfant-m|Bonjour, Mila.
 enfant-f|Bonjour.
-narrateur|Raphaël veut essuyer une miette.
+narrateur|Une miette colle au rebord du bol.
 enfant-m|Le torchon, s'il te plaît.
-maman|Voilà le torchon.
-enfant-m|Merci, maman.
-narrateur|Il essuie le rebord du bol.
-papa|Tu veux une rondelle ?
-enfant-m|S'il te plaît.
-enfant-m|Merci.</t>
+maman|Le voilà.
+enfant-m|Merci.
+narrateur|Il essuie. Le bol est propre.
+enfant-f|Les pommes montent dans le bus.
+narrateur|Ils posent deux rondelles sur les sièges.</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
@@ -6770,12 +6774,12 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Quel mot dit-on pour demander ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël veut le torchon. Que dit-il ?</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Quel mot dit-on pour demander ?&lt;/slow&gt;</t>
+          <t>Raphaël veut le torchon. Que dit-il ?</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -6785,7 +6789,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>s'il te plaît | sil te plait | s'il vous plaît</t>
+          <t>s'il te plaît | sil te plait</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -6795,12 +6799,12 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
+          <t>S'il te plaît.</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
           <t>Il dit s'il te plaît.</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>Dis : s'il te plaît.</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr"/>
@@ -6924,6 +6928,7 @@
           <t>narrateur|Raphaël veut le torchon. Que dit-il ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6948,17 +6953,17 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a dit s'il te plaît. Le torchon rayé est dans sa main. Le bus rouge attend près du tabouret. On monte ? On s'installe d'abord.</t>
+          <t>Raphaël a dit s'il te plaît. Le torchon a servi. Le bus est chargé. On cherche l'arrêt.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Oui. &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt;, s'il te plaît, merci. Sami retient le geste. Papa sourit. On dit bonjour. On dit s'il te plaît. On dit merci.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël a dit s'il te plaît. Le torchon a servi. Le bus est chargé. On cherche l'arrêt.</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Oui. &lt;emphasis&gt;bonjour&lt;/emphasis&gt;, s'il te plaît, merci. Sami retient le geste. Papa sourit. On dit bonjour. On dit s'il te plaît. On dit merci. [pause]</t>
+          <t>Raphaël a dit s'il te plaît. Le torchon a servi. Le bus est chargé. On cherche l'arrêt.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
@@ -7093,12 +7098,11 @@
       <c r="AW34" t="inlineStr">
         <is>
           <t>narrateur|Raphaël a dit s'il te plaît.
-narrateur|Le torchon rayé est dans sa main.
-narrateur|Le bus rouge attend près du tabouret.
-enfant-f|On monte ?
-maman|On s'installe d'abord.</t>
-        </is>
-      </c>
+narrateur|Le torchon a servi. Le bus est chargé.
+enfant-f|On cherche l'arrêt.</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7123,17 +7127,17 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On va où, dans la cuisine ? La table, la fenêtre, ou le tabouret.</t>
+          <t>L'arrêt, c'est où ? La table, la fenêtre, ou le tabouret.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;On peut prendre Tom, Léa, ou Sami.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'arrêt, c'est où ? La table, la fenêtre, ou le tabouret.</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;On peut prendre Tom, Léa, ou Sami.&lt;/slow&gt; [pause]</t>
+          <t>L'arrêt, c'est où ? La table, la fenêtre, ou le tabouret.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr"/>
@@ -7291,10 +7295,11 @@
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On va où, dans la cuisine ?
+          <t>narrateur|L'arrêt, c'est où ?
 narrateur|La table, la fenêtre, ou le tabouret.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7319,17 +7324,17 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Raphaël pose le bus rouge près de la table. Le bol jaune est au milieu. Mila tire une chaise. Arrêt table. Deux assiettes ? S'il te plaît. Les assiettes font un petit toc. Merci. Il glisse une rondelle vers Mila. Merci. Ticket pomme.</t>
+          <t>Le bus rouge arrive contre la table. Arrêt table. Portes. Mila ouvre la petite porte. Les rondelles descendent. Raphaël pose une assiette. Mila l'autre. Ticket pomme.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sami dit &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt; à Léa. Il demande une place : s'il te plaît. Léa dit merci. C'est le matin. Papa dit : je suis là. On dit bonjour. On dit s'il te plaît. On dit merci.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le bus rouge arrive contre la table. Arrêt table. Portes. Mila ouvre la petite porte. Les rondelles descendent. Raphaël pose une assiette. Mila l'autre. Ticket pomme.</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Sami dit &lt;emphasis&gt;bonjour&lt;/emphasis&gt; à Léa. Il demande une place : s'il te plaît. Léa dit merci. C'est le matin. Papa dit : je suis là. On dit bonjour. On dit s'il te plaît. On dit merci. [pause]</t>
+          <t>Le bus rouge arrive contre la table. Arrêt table. Portes. Mila ouvre la petite porte. Les rondelles descendent. Raphaël pose une assiette. Mila l'autre. Ticket pomme.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr"/>
@@ -7459,16 +7464,11 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël pose le bus rouge près de la table.
-narrateur|Le bol jaune est au milieu.
-narrateur|Mila tire une chaise.
-enfant-m|Arrêt table.
-maman|Deux assiettes ?
-enfant-m|S'il te plaît.
-narrateur|Les assiettes font un petit toc.
-enfant-m|Merci.
-narrateur|Il glisse une rondelle vers Mila.
-enfant-f|Merci. Ticket pomme.</t>
+          <t>narrateur|Le bus rouge arrive contre la table.
+enfant-m|Arrêt table. Portes.
+narrateur|Mila ouvre la petite porte. Les rondelles descendent.
+narrateur|Raphaël pose une assiette. Mila l'autre.
+enfant-f|Ticket pomme.</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
@@ -7500,17 +7500,17 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>C'est quel moment ? Le matin, après la sieste, ou le soir.</t>
+          <t>Qui pousse pour livrer ? Mila, Raphaël, ou tous les deux.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;On peut prendre le matin, après la sieste, ou le soir.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
+          <t>Qui pousse pour livrer ? Mila, Raphaël, ou tous les deux.</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;On peut prendre le matin, après la sieste, ou le soir.&lt;/slow&gt; [pause]</t>
+          <t>Qui pousse pour livrer ? Mila, Raphaël, ou tous les deux.</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
@@ -7528,7 +7528,7 @@
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>le matin</t>
+          <t>Mila</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>après la sieste</t>
+          <t>Raphaël</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -7548,7 +7548,7 @@
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>le soir</t>
+          <t>tous les deux</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
@@ -7664,10 +7664,11 @@
       <c r="AV37" s="2" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|C'est quel moment ?
-narrateur|Le matin, après la sieste, ou le soir.</t>
-        </is>
-      </c>
+          <t>narrateur|Qui pousse pour livrer ?
+narrateur|Mila, Raphaël, ou tous les deux.</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7692,17 +7693,17 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. Dehors, le vrai bus klaxonne, tout loin. Raphaël ouvre la porte du bus rouge. On charge les pommes ? S'il te plaît, une pour Mila. Papa pose deux rondelles sur les sièges. Merci. On part.</t>
+          <t>Je pousse. Moi, je garde les pommes. Mila pousse le bus, tout autour de l'arrêt. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sami a choisi le bus. Puis Tom. Puis le matin. Un ruban reste dans la poche. Sami essuie ses mains. On dit &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Je pousse. Moi, je garde les pommes. Mila pousse le bus, tout autour de l'arrêt. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Sami a choisi le bus. Puis Tom. Puis le matin. Un ruban reste dans la poche. Sami essuie ses mains. On dit &lt;emphasis&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa. [pause]</t>
+          <t>Je pousse. Moi, je garde les pommes. Mila pousse le bus, tout autour de l'arrêt. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
@@ -7832,13 +7833,14 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|C'est le matin.
-narrateur|Dehors, le vrai bus klaxonne, tout loin.
-narrateur|Raphaël ouvre la porte du bus rouge.
-papa|On charge les pommes ?
-enfant-m|S'il te plaît, une pour Mila.
-narrateur|Papa pose deux rondelles sur les sièges.
-enfant-f|Merci. On part.</t>
+          <t>enfant-f|Je pousse.
+enfant-m|Moi, je garde les pommes.
+narrateur|Mila pousse le bus, tout autour de l'arrêt.
+narrateur|Le bol avance. Une rondelle tremble, puis tient.
+enfant-m|Terminus, les pommes.
+narrateur|Ils posent une rondelle chacun.
+enfant-f|On croque.
+narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
@@ -7870,17 +7872,17 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Le bus fait le tour de la table. Prochain arrêt : le bol. Vous avez bien chargé. L'histoire est finie.</t>
+          <t>Le bus reste collé à l'assiette. Ticket utilisé. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le bus reste collé à l'assiette. Ticket utilisé. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>Le bus reste collé à l'assiette. Ticket utilisé. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr"/>
@@ -8010,12 +8012,14 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|Le bus fait le tour de la table.
-enfant-m|Prochain arrêt : le bol.
-maman|Vous avez bien chargé.
+          <t>narrateur|Le bus reste collé à l'assiette.
+enfant-f|Ticket utilisé.
+papa|Vous avez fait le voyage.
+narrateur|Les assiettes sont vides, maintenant.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -8040,17 +8044,17 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>C'est après la sieste. Le bus rouge avance tout lentement. Les voyageurs ont sommeil. Une rondelle calme ? S'il te plaît. Merci. Raphaël ferme la porte du bus, tout doux.</t>
+          <t>Je pousse. Moi, je dis les arrêts. Raphaël pousse le bus. Mila annonce. Prochain : les assiettes. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sami s'arrête près de après la sieste. Tom est rangé. Un chat miaule une fois. Sami range la tasse. On dit &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Je pousse. Moi, je dis les arrêts. Raphaël pousse le bus. Mila annonce. Prochain : les assiettes. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Sami s'arrête près de après la sieste. Tom est rangé. Un chat miaule une fois. Sami range la tasse. On dit &lt;emphasis&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa. [pause]</t>
+          <t>Je pousse. Moi, je dis les arrêts. Raphaël pousse le bus. Mila annonce. Prochain : les assiettes. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
@@ -8180,13 +8184,15 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|C'est après la sieste.
-narrateur|Le bus rouge avance tout lentement.
-enfant-f|Les voyageurs ont sommeil.
-maman|Une rondelle calme ?
-enfant-f|S'il te plaît.
-enfant-f|Merci.
-narrateur|Raphaël ferme la porte du bus, tout doux.</t>
+          <t>enfant-m|Je pousse.
+enfant-f|Moi, je dis les arrêts.
+narrateur|Raphaël pousse le bus. Mila annonce.
+enfant-f|Prochain : les assiettes.
+narrateur|Le bol avance. Une rondelle tremble, puis tient.
+enfant-m|Terminus, les pommes.
+narrateur|Ils posent une rondelle chacun.
+enfant-f|On croque.
+narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
@@ -8218,17 +8224,17 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Le bus reste collé à l'assiette. Terminus sieste. On ne réveille pas les pommes. L'histoire est finie.</t>
+          <t>Le bus reste collé à l'assiette. Ticket utilisé. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le bus reste collé à l'assiette. Ticket utilisé. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>Le bus reste collé à l'assiette. Ticket utilisé. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
@@ -8359,11 +8365,13 @@
       <c r="AW41" t="inlineStr">
         <is>
           <t>narrateur|Le bus reste collé à l'assiette.
-enfant-m|Terminus sieste.
-papa|On ne réveille pas les pommes.
+enfant-f|Ticket utilisé.
+papa|Vous avez fait le voyage.
+narrateur|Les assiettes sont vides, maintenant.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8388,17 +8396,17 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>C'est le soir. La table a une petite ombre. Raphaël range le bus sous une serviette. Le dépôt. Dernière rondelle ? S'il te plaît. Merci. Pour Mila aussi.</t>
+          <t>Ensemble. Toi devant. Moi derrière. Ils poussent le bus avec quatre mains. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sami se souvient de le bus. Et de Tom. Et de le soir. Un ballon s'immobilise. Sami dit : j'ai appris. On dit &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Ensemble. Toi devant. Moi derrière. Ils poussent le bus avec quatre mains. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Sami se souvient de le bus. Et de Tom. Et de le soir. Un ballon s'immobilise. Sami dit : j'ai appris. On dit &lt;emphasis&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa. [pause]</t>
+          <t>Ensemble. Toi devant. Moi derrière. Ils poussent le bus avec quatre mains. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr"/>
@@ -8528,13 +8536,14 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|C'est le soir.
-narrateur|La table a une petite ombre.
-narrateur|Raphaël range le bus sous une serviette.
-enfant-f|Le dépôt.
-papa|Dernière rondelle ?
-enfant-m|S'il te plaît.
-enfant-m|Merci. Pour Mila aussi.</t>
+          <t>enfant-m|Ensemble.
+enfant-f|Toi devant. Moi derrière.
+narrateur|Ils poussent le bus avec quatre mains.
+narrateur|Le bol avance. Une rondelle tremble, puis tient.
+enfant-m|Terminus, les pommes.
+narrateur|Ils posent une rondelle chacun.
+enfant-f|On croque.
+narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
@@ -8566,17 +8575,17 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Le bol est vide. Le bus est au dépôt. Bonne soirée, les voyageurs. Merci pour le trajet. L'histoire est finie.</t>
+          <t>Le bus reste collé à l'assiette. Ticket utilisé. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le bus reste collé à l'assiette. Ticket utilisé. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>Le bus reste collé à l'assiette. Ticket utilisé. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
@@ -8706,12 +8715,14 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|Le bol est vide. Le bus est au dépôt.
-maman|Bonne soirée, les voyageurs.
-enfant-f|Merci pour le trajet.
+          <t>narrateur|Le bus reste collé à l'assiette.
+enfant-f|Ticket utilisé.
+papa|Vous avez fait le voyage.
+narrateur|Les assiettes sont vides, maintenant.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8736,17 +8747,17 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Raphaël va près de la fenêtre, avec le bus. Un vrai bus passe dans la rue. Mila colle son nez à la vitre. Le torchon, s'il te plaît. Pour voir le bus ? Oui. Il essuie. Le bus rouge de vrai apparaît. Merci, papa. Le nôtre est plus petit.</t>
+          <t>Le bus va près de la fenêtre. Un vrai bus passe dans la rue. On suit le grand. Mila essuie un coin. Raphaël garde un trait de buée. C'est notre ligne. Arrêt fenêtre.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sami dit &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt; à Léa. Il demande une place : s'il te plaît. Léa dit merci. C'est après la sieste. Papa reste tout près. On dit bonjour. On dit s'il te plaît. On dit merci.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le bus va près de la fenêtre. Un vrai bus passe dans la rue. On suit le grand. Mila essuie un coin. Raphaël garde un trait de buée. C'est notre ligne. Arrêt fenêtre.</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Sami dit &lt;emphasis&gt;bonjour&lt;/emphasis&gt; à Léa. Il demande une place : s'il te plaît. Léa dit merci. C'est après la sieste. Papa reste tout près. On dit bonjour. On dit s'il te plaît. On dit merci. [pause]</t>
+          <t>Le bus va près de la fenêtre. Un vrai bus passe dans la rue. On suit le grand. Mila essuie un coin. Raphaël garde un trait de buée. C'est notre ligne. Arrêt fenêtre.</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
@@ -8876,15 +8887,12 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël va près de la fenêtre, avec le bus.
+          <t>narrateur|Le bus va près de la fenêtre.
 narrateur|Un vrai bus passe dans la rue.
-narrateur|Mila colle son nez à la vitre.
-enfant-m|Le torchon, s'il te plaît.
-papa|Pour voir le bus ?
-enfant-m|Oui.
-narrateur|Il essuie. Le bus rouge de vrai apparaît.
-enfant-m|Merci, papa.
-enfant-f|Le nôtre est plus petit.</t>
+enfant-m|On suit le grand.
+narrateur|Mila essuie un coin. Raphaël garde un trait de buée.
+enfant-f|C'est notre ligne.
+enfant-m|Arrêt fenêtre.</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
@@ -8916,17 +8924,17 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>C'est quel moment ? Le matin, après la sieste, ou le soir.</t>
+          <t>Qui pousse pour livrer ? Mila, Raphaël, ou tous les deux.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;On peut prendre le matin, après la sieste, ou le soir.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
+          <t>Qui pousse pour livrer ? Mila, Raphaël, ou tous les deux.</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;On peut prendre le matin, après la sieste, ou le soir.&lt;/slow&gt; [pause]</t>
+          <t>Qui pousse pour livrer ? Mila, Raphaël, ou tous les deux.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr"/>
@@ -8944,7 +8952,7 @@
       <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>le matin</t>
+          <t>Mila</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -8954,7 +8962,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>après la sieste</t>
+          <t>Raphaël</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -8964,7 +8972,7 @@
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>le soir</t>
+          <t>tous les deux</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
@@ -9080,10 +9088,11 @@
       <c r="AV45" s="2" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|C'est quel moment ?
-narrateur|Le matin, après la sieste, ou le soir.</t>
-        </is>
-      </c>
+          <t>narrateur|Qui pousse pour livrer ?
+narrateur|Mila, Raphaël, ou tous les deux.</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -9108,17 +9117,17 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. Le vrai bus s'arrête au coin. Raphaël pose le petit bus sur le rebord. Rondelle du chauffeur ? S'il te plaît. Merci. Une pour Mila. Merci. On suit le grand.</t>
+          <t>Je pousse. Moi, je garde les pommes. Mila pousse le bus, tout autour de l'arrêt. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Avec le matin. Après Léa. Près de le bus. Sami s'arrête. On dit merci. Maman n'est pas loin. Sami les rejoint. On dit &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Je pousse. Moi, je garde les pommes. Mila pousse le bus, tout autour de l'arrêt. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Avec le matin. Après Léa. Près de le bus. Sami s'arrête. On dit merci. Maman n'est pas loin. Sami les rejoint. On dit &lt;emphasis&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa. [pause]</t>
+          <t>Je pousse. Moi, je garde les pommes. Mila pousse le bus, tout autour de l'arrêt. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
@@ -9248,13 +9257,14 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|C'est le matin.
-narrateur|Le vrai bus s'arrête au coin.
-narrateur|Raphaël pose le petit bus sur le rebord.
-maman|Rondelle du chauffeur ?
-enfant-m|S'il te plaît.
-enfant-m|Merci. Une pour Mila.
-enfant-f|Merci. On suit le grand.</t>
+          <t>enfant-f|Je pousse.
+enfant-m|Moi, je garde les pommes.
+narrateur|Mila pousse le bus, tout autour de l'arrêt.
+narrateur|Le bol avance. Une rondelle tremble, puis tient.
+enfant-m|Terminus, les pommes.
+narrateur|Ils posent une rondelle chacun.
+enfant-f|On croque.
+narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
@@ -9286,17 +9296,17 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Le vrai bus repart. Le petit reste. On garde les pommes ici. Bon trajet, vous deux. L'histoire est finie.</t>
+          <t>Le petit bus s'endort contre la vitre. Ticket utilisé. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le petit bus s'endort contre la vitre. Ticket utilisé. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>Le petit bus s'endort contre la vitre. Ticket utilisé. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
@@ -9426,12 +9436,14 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|Le vrai bus repart. Le petit reste.
-enfant-m|On garde les pommes ici.
-papa|Bon trajet, vous deux.
+          <t>narrateur|Le petit bus s'endort contre la vitre.
+enfant-f|Ticket utilisé.
+papa|Vous avez fait le voyage.
+narrateur|Les assiettes sont vides, maintenant.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9456,17 +9468,17 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>C'est après la sieste. La rue est plus calme. Raphaël fait glisser le bus le long du bois. Pas de klaxon. Une pomme, tout bas ? S'il te plaît. Merci.</t>
+          <t>Je pousse. Moi, je dis les arrêts. Raphaël pousse le bus. Mila annonce. Prochain : les assiettes. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sami range Léa. après la sieste reste près de le bus. On se tient la main. Sami souffle, puis sourit à papa. On dit &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Je pousse. Moi, je dis les arrêts. Raphaël pousse le bus. Mila annonce. Prochain : les assiettes. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Sami range Léa. après la sieste reste près de le bus. On se tient la main. Sami souffle, puis sourit à papa. On dit &lt;emphasis&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa. [pause]</t>
+          <t>Je pousse. Moi, je dis les arrêts. Raphaël pousse le bus. Mila annonce. Prochain : les assiettes. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr"/>
@@ -9596,13 +9608,15 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|C'est après la sieste.
-narrateur|La rue est plus calme.
-narrateur|Raphaël fait glisser le bus le long du bois.
-enfant-f|Pas de klaxon.
-papa|Une pomme, tout bas ?
-enfant-f|S'il te plaît.
-enfant-f|Merci.</t>
+          <t>enfant-m|Je pousse.
+enfant-f|Moi, je dis les arrêts.
+narrateur|Raphaël pousse le bus. Mila annonce.
+enfant-f|Prochain : les assiettes.
+narrateur|Le bol avance. Une rondelle tremble, puis tient.
+enfant-m|Terminus, les pommes.
+narrateur|Ils posent une rondelle chacun.
+enfant-f|On croque.
+narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
@@ -9634,17 +9648,17 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Le petit bus s'endort contre la vitre. Le grand reviendra plus tard. On l'attendra. L'histoire est finie.</t>
+          <t>Le petit bus s'endort contre la vitre. Ticket utilisé. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le petit bus s'endort contre la vitre. Ticket utilisé. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>Le petit bus s'endort contre la vitre. Ticket utilisé. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
@@ -9775,11 +9789,13 @@
       <c r="AW49" t="inlineStr">
         <is>
           <t>narrateur|Le petit bus s'endort contre la vitre.
-maman|Le grand reviendra plus tard.
-enfant-m|On l'attendra.
+enfant-f|Ticket utilisé.
+papa|Vous avez fait le voyage.
+narrateur|Les assiettes sont vides, maintenant.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9804,17 +9820,17 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>C'est le soir. Les feux du vrai bus passent, tout rouge. Raphaël descend le petit bus du rebord. On rentre au dépôt. Une rondelle, s'il te plaît. Merci. Bonne nuit, le bus.</t>
+          <t>Ensemble. Toi devant. Moi derrière. Ils poussent le bus avec quatre mains. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;le soir est là. Léa aussi. le bus reste dans le souvenir. Un panier est posé sur le banc. Sami sourit. Papa sourit aussi. On dit &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Ensemble. Toi devant. Moi derrière. Ils poussent le bus avec quatre mains. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>le soir est là. Léa aussi. le bus reste dans le souvenir. Un panier est posé sur le banc. Sami sourit. Papa sourit aussi. On dit &lt;emphasis&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa. [pause]</t>
+          <t>Ensemble. Toi devant. Moi derrière. Ils poussent le bus avec quatre mains. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
@@ -9944,13 +9960,14 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|C'est le soir.
-narrateur|Les feux du vrai bus passent, tout rouge.
-narrateur|Raphaël descend le petit bus du rebord.
-maman|On rentre au dépôt.
-enfant-m|Une rondelle, s'il te plaît.
-enfant-m|Merci.
-enfant-f|Bonne nuit, le bus.</t>
+          <t>enfant-m|Ensemble.
+enfant-f|Toi devant. Moi derrière.
+narrateur|Ils poussent le bus avec quatre mains.
+narrateur|Le bol avance. Une rondelle tremble, puis tient.
+enfant-m|Terminus, les pommes.
+narrateur|Ils posent une rondelle chacun.
+enfant-f|On croque.
+narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
@@ -9982,17 +9999,17 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>La vitre est noire, maintenant. Le marché est fermé. Notre bus aussi. L'histoire est finie.</t>
+          <t>Le petit bus s'endort contre la vitre. Ticket utilisé. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le petit bus s'endort contre la vitre. Ticket utilisé. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>Le petit bus s'endort contre la vitre. Ticket utilisé. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr"/>
@@ -10122,12 +10139,14 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|La vitre est noire, maintenant.
-papa|Le marché est fermé.
-enfant-m|Notre bus aussi.
+          <t>narrateur|Le petit bus s'endort contre la vitre.
+enfant-f|Ticket utilisé.
+papa|Vous avez fait le voyage.
+narrateur|Les assiettes sont vides, maintenant.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -10152,17 +10171,17 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Raphaël glisse le bus près du tabouret. Mila s'assoit. Les pieds balancent. Arrêt tabouret. Je descends ? Tu peux rester. Le bol, plus haut ? S'il te plaît. Maman pose le bol sur le tabouret, à côté de Mila. Merci.</t>
+          <t>Le bus s'arrête au pied du tabouret. Arrêt tabouret. On monte la cargaison. Mila s'assoit. Les pieds balancent. Raphaël hisse le bol à côté d'elle. Gare haute. Les pommes voient tout.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sami dit &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt; à Léa. Il demande une place : s'il te plaît. Léa dit merci. C'est le soir. Papa montre le geste, lentement. On dit bonjour. On dit s'il te plaît. On dit merci.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le bus s'arrête au pied du tabouret. Arrêt tabouret. On monte la cargaison. Mila s'assoit. Les pieds balancent. Raphaël hisse le bol à côté d'elle. Gare haute. Les pommes voient tout.</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Sami dit &lt;emphasis&gt;bonjour&lt;/emphasis&gt; à Léa. Il demande une place : s'il te plaît. Léa dit merci. C'est le soir. Papa montre le geste, lentement. On dit bonjour. On dit s'il te plaît. On dit merci. [pause]</t>
+          <t>Le bus s'arrête au pied du tabouret. Arrêt tabouret. On monte la cargaison. Mila s'assoit. Les pieds balancent. Raphaël hisse le bol à côté d'elle. Gare haute. Les pommes voient tout.</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
@@ -10292,15 +10311,11 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël glisse le bus près du tabouret.
+          <t>narrateur|Le bus s'arrête au pied du tabouret.
+enfant-m|Arrêt tabouret. On monte la cargaison.
 narrateur|Mila s'assoit. Les pieds balancent.
-enfant-m|Arrêt tabouret.
-enfant-f|Je descends ?
-enfant-m|Tu peux rester.
-maman|Le bol, plus haut ?
-enfant-m|S'il te plaît.
-narrateur|Maman pose le bol sur le tabouret, à côté de Mila.
-enfant-m|Merci.</t>
+narrateur|Raphaël hisse le bol à côté d'elle.
+enfant-f|Gare haute. Les pommes voient tout.</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
@@ -10332,17 +10347,17 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>C'est quel moment ? Le matin, après la sieste, ou le soir.</t>
+          <t>Qui pousse pour livrer ? Mila, Raphaël, ou tous les deux.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;On peut prendre le matin, après la sieste, ou le soir.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
+          <t>Qui pousse pour livrer ? Mila, Raphaël, ou tous les deux.</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;On peut prendre le matin, après la sieste, ou le soir.&lt;/slow&gt; [pause]</t>
+          <t>Qui pousse pour livrer ? Mila, Raphaël, ou tous les deux.</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
@@ -10360,7 +10375,7 @@
       <c r="L53" s="2" t="inlineStr"/>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>le matin</t>
+          <t>Mila</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -10370,7 +10385,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>après la sieste</t>
+          <t>Raphaël</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -10380,7 +10395,7 @@
       </c>
       <c r="Q53" s="2" t="inlineStr">
         <is>
-          <t>le soir</t>
+          <t>tous les deux</t>
         </is>
       </c>
       <c r="R53" s="2" t="inlineStr">
@@ -10496,10 +10511,11 @@
       <c r="AV53" s="2" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|C'est quel moment ?
-narrateur|Le matin, après la sieste, ou le soir.</t>
-        </is>
-      </c>
+          <t>narrateur|Qui pousse pour livrer ?
+narrateur|Mila, Raphaël, ou tous les deux.</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10524,17 +10540,17 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. Le soleil fait un rectangle sur le bois. Raphaël fait monter le bus sur le rectangle. Tickets pommes ? S'il te plaît. Deux rondelles sur les genoux de Mila. Merci. Une pour le chauffeur.</t>
+          <t>Je pousse. Moi, je garde les pommes. Mila pousse le bus, tout autour de l'arrêt. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sami rejoint le matin. Sami est rangé. le bus est fini. L'eau coule, tout petit bruit. Sami prend la main de papa. On dit &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Je pousse. Moi, je garde les pommes. Mila pousse le bus, tout autour de l'arrêt. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint le matin. Sami est rangé. le bus est fini. L'eau coule, tout petit bruit. Sami prend la main de papa. On dit &lt;emphasis&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa. [pause]</t>
+          <t>Je pousse. Moi, je garde les pommes. Mila pousse le bus, tout autour de l'arrêt. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
@@ -10664,13 +10680,14 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|C'est le matin.
-narrateur|Le soleil fait un rectangle sur le bois.
-narrateur|Raphaël fait monter le bus sur le rectangle.
-papa|Tickets pommes ?
-enfant-f|S'il te plaît.
-narrateur|Deux rondelles sur les genoux de Mila.
-enfant-f|Merci. Une pour le chauffeur.</t>
+          <t>enfant-f|Je pousse.
+enfant-m|Moi, je garde les pommes.
+narrateur|Mila pousse le bus, tout autour de l'arrêt.
+narrateur|Le bol avance. Une rondelle tremble, puis tient.
+enfant-m|Terminus, les pommes.
+narrateur|Ils posent une rondelle chacun.
+enfant-f|On croque.
+narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
@@ -10702,17 +10719,17 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Raphaël croque. Mila croque. Prochain arrêt : demain. Vous avez bien attendu le bol. L'histoire est finie.</t>
+          <t>Le bus dort sous le tabouret. Ticket utilisé. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le bus dort sous le tabouret. Ticket utilisé. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>Le bus dort sous le tabouret. Ticket utilisé. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
@@ -10842,12 +10859,14 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël croque. Mila croque.
-enfant-m|Prochain arrêt : demain.
-maman|Vous avez bien attendu le bol.
+          <t>narrateur|Le bus dort sous le tabouret.
+enfant-f|Ticket utilisé.
+papa|Vous avez fait le voyage.
+narrateur|Les assiettes sont vides, maintenant.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10872,17 +10891,17 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>C'est après la sieste. Mila balance moins les pieds. Raphaël gare le bus contre un pied. On charge tout doux. Une rondelle, s'il te plaît. Merci. Pour Mila.</t>
+          <t>Je pousse. Moi, je dis les arrêts. Raphaël pousse le bus. Mila annonce. Prochain : les assiettes. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Près de après la sieste. Sami pose Sami. le bus est derrière. Une pomme brille un peu. Sami caresse le doudou. On dit &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Je pousse. Moi, je dis les arrêts. Raphaël pousse le bus. Mila annonce. Prochain : les assiettes. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Près de après la sieste. Sami pose Sami. le bus est derrière. Une pomme brille un peu. Sami caresse le doudou. On dit &lt;emphasis&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa. [pause]</t>
+          <t>Je pousse. Moi, je dis les arrêts. Raphaël pousse le bus. Mila annonce. Prochain : les assiettes. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
@@ -11012,12 +11031,15 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|C'est après la sieste.
-narrateur|Mila balance moins les pieds.
-narrateur|Raphaël gare le bus contre un pied.
-papa|On charge tout doux.
-enfant-m|Une rondelle, s'il te plaît.
-enfant-m|Merci. Pour Mila.</t>
+          <t>enfant-m|Je pousse.
+enfant-f|Moi, je dis les arrêts.
+narrateur|Raphaël pousse le bus. Mila annonce.
+enfant-f|Prochain : les assiettes.
+narrateur|Le bol avance. Une rondelle tremble, puis tient.
+enfant-m|Terminus, les pommes.
+narrateur|Ils posent une rondelle chacun.
+enfant-f|On croque.
+narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
@@ -11049,17 +11071,17 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Le bus ne roule plus. Merci. J'avais sommeil. Le tabouret a bien tenu. L'histoire est finie.</t>
+          <t>Le bus dort sous le tabouret. Ticket utilisé. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le bus dort sous le tabouret. Ticket utilisé. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>Le bus dort sous le tabouret. Ticket utilisé. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
@@ -11189,12 +11211,14 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|Le bus ne roule plus.
-enfant-f|Merci. J'avais sommeil.
-papa|Le tabouret a bien tenu.
+          <t>narrateur|Le bus dort sous le tabouret.
+enfant-f|Ticket utilisé.
+papa|Vous avez fait le voyage.
+narrateur|Les assiettes sont vides, maintenant.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -11219,17 +11243,17 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>C'est le soir. Raphaël range le bus sous le tabouret. Le dépôt est en bas. On descend du siège ? Oui. Merci, tabouret. Dernière pomme ? S'il te plaît. Merci.</t>
+          <t>Ensemble. Toi devant. Moi derrière. Ils poussent le bus avec quatre mains. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sami montre le soir. Papa a vu le bus. Et Sami. Une tasse cliquette. Sami enfile ses chaussons. On dit &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Ensemble. Toi devant. Moi derrière. Ils poussent le bus avec quatre mains. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Sami montre le soir. Papa a vu le bus. Et Sami. Une tasse cliquette. Sami enfile ses chaussons. On dit &lt;emphasis&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa. [pause]</t>
+          <t>Ensemble. Toi devant. Moi derrière. Ils poussent le bus avec quatre mains. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
@@ -11359,14 +11383,14 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|C'est le soir.
-narrateur|Raphaël range le bus sous le tabouret.
-enfant-f|Le dépôt est en bas.
-maman|On descend du siège ?
-enfant-f|Oui. Merci, tabouret.
-papa|Dernière pomme ?
-enfant-m|S'il te plaît.
-enfant-m|Merci.</t>
+          <t>enfant-m|Ensemble.
+enfant-f|Toi devant. Moi derrière.
+narrateur|Ils poussent le bus avec quatre mains.
+narrateur|Le bol avance. Une rondelle tremble, puis tient.
+enfant-m|Terminus, les pommes.
+narrateur|Ils posent une rondelle chacun.
+enfant-f|On croque.
+narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
@@ -11398,17 +11422,17 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Mila pose les pieds par terre. Le bus dort en dessous. Vous avez bien partagé le haut et le bas. L'histoire est finie.</t>
+          <t>Le bus dort sous le tabouret. Ticket utilisé. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le bus dort sous le tabouret. Ticket utilisé. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>Le bus dort sous le tabouret. Ticket utilisé. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
@@ -11538,12 +11562,14 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|Mila pose les pieds par terre.
-enfant-m|Le bus dort en dessous.
-maman|Vous avez bien partagé le haut et le bas.
+          <t>narrateur|Le bus dort sous le tabouret.
+enfant-f|Ticket utilisé.
+papa|Vous avez fait le voyage.
+narrateur|Les assiettes sont vides, maintenant.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11568,17 +11594,17 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Raphaël prend la petite voiture. Elle est lisse, un peu froide. Dehors, une portière claque, tout loin. Mila arrive. Son manteau sent la pluie. Bonjour, Mila. Bonjour, Raphaël. Donne-moi ton manteau ? S'il te plaît, tu peux le prendre. Maman accroche le manteau. Merci. Une rondelle, Raphaël ? S'il te plaît. La rondelle est froide et douce. Merci, papa.</t>
+          <t>Raphaël prend la petite voiture. Elle est lisse, un peu froide. Mila arrive. Son manteau sent la pluie. Bonjour, Mila. Bonjour. Tu accroches mon manteau, s'il te plaît ? Oui. Maman accroche le manteau. Merci. Une rondelle pour la route ? Oui, merci. Il pose la rondelle sur le capot, pour de faux. Cargaison prête.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sami entend une voiture. Un copain entre. Sami dit &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt;. Il demande une part : s'il te plaît. Il dit merci. On dit bonjour. On dit s'il te plaît. On dit merci.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël prend la petite voiture. Elle est lisse, un peu froide. Mila arrive. Son manteau sent la pluie. Bonjour, Mila. Bonjour. Tu accroches mon manteau, s'il te plaît ? Oui. Maman accroche le manteau. Merci. Une rondelle pour la route ? Oui, merci. Il pose la rondelle sur le capot, pour de faux. Cargaison prête.</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Sami entend une voiture. Un copain entre. Sami dit &lt;emphasis&gt;bonjour&lt;/emphasis&gt;. Il demande une part : s'il te plaît. Il dit merci. On dit bonjour. On dit s'il te plaît. On dit merci. [pause]</t>
+          <t>Raphaël prend la petite voiture. Elle est lisse, un peu froide. Mila arrive. Son manteau sent la pluie. Bonjour, Mila. Bonjour. Tu accroches mon manteau, s'il te plaît ? Oui. Maman accroche le manteau. Merci. Une rondelle pour la route ? Oui, merci. Il pose la rondelle sur le capot, pour de faux. Cargaison prête.</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr"/>
@@ -11710,18 +11736,17 @@
         <is>
           <t>narrateur|Raphaël prend la petite voiture.
 narrateur|Elle est lisse, un peu froide.
-narrateur|Dehors, une portière claque, tout loin.
 narrateur|Mila arrive. Son manteau sent la pluie.
 enfant-m|Bonjour, Mila.
-enfant-f|Bonjour, Raphaël.
-maman|Donne-moi ton manteau ?
-enfant-f|S'il te plaît, tu peux le prendre.
+enfant-f|Bonjour.
+enfant-f|Tu accroches mon manteau, s'il te plaît ?
+maman|Oui.
 narrateur|Maman accroche le manteau.
 enfant-f|Merci.
-papa|Une rondelle, Raphaël ?
-enfant-m|S'il te plaît.
-narrateur|La rondelle est froide et douce.
-enfant-m|Merci, papa.</t>
+papa|Une rondelle pour la route ?
+enfant-m|Oui, merci.
+narrateur|Il pose la rondelle sur le capot, pour de faux.
+enfant-m|Cargaison prête.</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
@@ -11758,12 +11783,12 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;On dit &lt;emphasis level="moderate"&gt;merci&lt;/emphasis&gt; ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa donne une rondelle. Que dit Raphaël ?</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;On dit &lt;emphasis&gt;merci&lt;/emphasis&gt; ?&lt;/slow&gt;</t>
+          <t>Papa donne une rondelle. Que dit Raphaël ?</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -11773,7 +11798,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>merci | merci papa</t>
+          <t>merci | merci papa | oui merci</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -11783,12 +11808,12 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
+          <t>Merci.</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
           <t>Il dit merci.</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>Dis : merci.</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr"/>
@@ -11916,6 +11941,7 @@
           <t>narrateur|Papa donne une rondelle. Que dit Raphaël ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11940,17 +11966,17 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a dit merci. La petite voiture brille près du bol. Le manteau de Mila sèche un peu. On roule ? On s'installe.</t>
+          <t>Raphaël a dit merci. La voiture a sa cargaison. On cherche l'arrêt.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Oui. &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt;, s'il te plaît, merci. Sami hoche la tête. On continue, avec papa. On dit bonjour. On dit s'il te plaît. On dit merci.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël a dit merci. La voiture a sa cargaison. On cherche l'arrêt.</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Oui. &lt;emphasis&gt;bonjour&lt;/emphasis&gt;, s'il te plaît, merci. Sami hoche la tête. On continue, avec papa. On dit bonjour. On dit s'il te plaît. On dit merci. [pause]</t>
+          <t>Raphaël a dit merci. La voiture a sa cargaison. On cherche l'arrêt.</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr"/>
@@ -12085,12 +12111,11 @@
       <c r="AW62" t="inlineStr">
         <is>
           <t>narrateur|Raphaël a dit merci.
-narrateur|La petite voiture brille près du bol.
-narrateur|Le manteau de Mila sèche un peu.
-enfant-m|On roule ?
-papa|On s'installe.</t>
-        </is>
-      </c>
+narrateur|La voiture a sa cargaison.
+enfant-m|On cherche l'arrêt.</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -12115,17 +12140,17 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On va où, dans la cuisine ? La table, la fenêtre, ou le tabouret.</t>
+          <t>L'arrêt, c'est où ? La table, la fenêtre, ou le tabouret.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;On peut prendre Tom, Léa, ou Sami.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'arrêt, c'est où ? La table, la fenêtre, ou le tabouret.</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;On peut prendre Tom, Léa, ou Sami.&lt;/slow&gt; [pause]</t>
+          <t>L'arrêt, c'est où ? La table, la fenêtre, ou le tabouret.</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr"/>
@@ -12283,10 +12308,11 @@
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On va où, dans la cuisine ?
+          <t>narrateur|L'arrêt, c'est où ?
 narrateur|La table, la fenêtre, ou le tabouret.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12311,17 +12337,17 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Raphaël pose la petite voiture près de la table. Une goutte du manteau tombe. Toc. Mila tire une chaise. Une assiette, pour ne pas mouiller ? S'il te plaît. L'assiette arrive, ronde. Merci. Il y pose une rondelle pour Mila. Merci. Ma voiture à moi, c'est la chaise.</t>
+          <t>La voiture tourne autour de la table. Une goutte du manteau a séché. Parking table. Ils glissent la rondelle du capot dans une assiette. Livraison faite. Presque.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sami dit &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt; à un copain Sami. Il dit s'il te plaît. Il dit merci. C'est le matin. Papa reste tout près. On dit bonjour. On dit s'il te plaît. On dit merci.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>La voiture tourne autour de la table. Une goutte du manteau a séché. Parking table. Ils glissent la rondelle du capot dans une assiette. Livraison faite. Presque.</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Sami dit &lt;emphasis&gt;bonjour&lt;/emphasis&gt; à un copain Sami. Il dit s'il te plaît. Il dit merci. C'est le matin. Papa reste tout près. On dit bonjour. On dit s'il te plaît. On dit merci. [pause]</t>
+          <t>La voiture tourne autour de la table. Une goutte du manteau a séché. Parking table. Ils glissent la rondelle du capot dans une assiette. Livraison faite. Presque.</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr"/>
@@ -12451,15 +12477,11 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël pose la petite voiture près de la table.
-narrateur|Une goutte du manteau tombe. Toc.
-narrateur|Mila tire une chaise.
-maman|Une assiette, pour ne pas mouiller ?
-enfant-m|S'il te plaît.
-narrateur|L'assiette arrive, ronde.
-enfant-m|Merci.
-narrateur|Il y pose une rondelle pour Mila.
-enfant-f|Merci. Ma voiture à moi, c'est la chaise.</t>
+          <t>narrateur|La voiture tourne autour de la table.
+narrateur|Une goutte du manteau a séché.
+enfant-m|Parking table.
+narrateur|Ils glissent la rondelle du capot dans une assiette.
+enfant-f|Livraison faite. Presque.</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
@@ -12491,17 +12513,17 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>C'est quel moment ? Le matin, après la sieste, ou le soir.</t>
+          <t>Qui pousse pour livrer ? Mila, Raphaël, ou tous les deux.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;On peut prendre le matin, après la sieste, ou le soir.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
+          <t>Qui pousse pour livrer ? Mila, Raphaël, ou tous les deux.</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;On peut prendre le matin, après la sieste, ou le soir.&lt;/slow&gt; [pause]</t>
+          <t>Qui pousse pour livrer ? Mila, Raphaël, ou tous les deux.</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr"/>
@@ -12519,7 +12541,7 @@
       <c r="L65" s="2" t="inlineStr"/>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>le matin</t>
+          <t>Mila</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -12529,7 +12551,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>après la sieste</t>
+          <t>Raphaël</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -12539,7 +12561,7 @@
       </c>
       <c r="Q65" s="2" t="inlineStr">
         <is>
-          <t>le soir</t>
+          <t>tous les deux</t>
         </is>
       </c>
       <c r="R65" s="2" t="inlineStr">
@@ -12655,10 +12677,11 @@
       <c r="AV65" s="2" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|C'est quel moment ?
-narrateur|Le matin, après la sieste, ou le soir.</t>
-        </is>
-      </c>
+          <t>narrateur|Qui pousse pour livrer ?
+narrateur|Mila, Raphaël, ou tous les deux.</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12683,17 +12706,17 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. La goutte a déjà séché. Raphaël fait le tour des assiettes avec la voiture. Encore une pomme, chauffeur ? S'il te plaît. Merci. Mila aussi. Merci. On va au marché, pour de faux.</t>
+          <t>Je pousse. Moi, je garde les pommes. Mila pousse la voiture, tout autour de l'arrêt. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sami a choisi la voiture. Puis Tom. Puis le matin. On range un objet. Sami répète tout bas le geste. On dit &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Je pousse. Moi, je garde les pommes. Mila pousse la voiture, tout autour de l'arrêt. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Sami a choisi la voiture. Puis Tom. Puis le matin. On range un objet. Sami répète tout bas le geste. On dit &lt;emphasis&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa. [pause]</t>
+          <t>Je pousse. Moi, je garde les pommes. Mila pousse la voiture, tout autour de l'arrêt. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr"/>
@@ -12823,13 +12846,14 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|C'est le matin.
-narrateur|La goutte a déjà séché.
-narrateur|Raphaël fait le tour des assiettes avec la voiture.
-papa|Encore une pomme, chauffeur ?
-enfant-m|S'il te plaît.
-enfant-m|Merci. Mila aussi.
-enfant-f|Merci. On va au marché, pour de faux.</t>
+          <t>enfant-f|Je pousse.
+enfant-m|Moi, je garde les pommes.
+narrateur|Mila pousse la voiture, tout autour de l'arrêt.
+narrateur|Le bol avance. Une rondelle tremble, puis tient.
+enfant-m|Terminus, les pommes.
+narrateur|Ils posent une rondelle chacun.
+enfant-f|On croque.
+narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
@@ -12861,17 +12885,17 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>La voiture se gare contre le bol jaune. Parking pommes. Vous avez bien servi. L'histoire est finie.</t>
+          <t>La voiture se gare contre le bol. Cargaison livrée. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La voiture se gare contre le bol. Cargaison livrée. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>La voiture se gare contre le bol. Cargaison livrée. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr"/>
@@ -13001,12 +13025,14 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|La voiture se gare contre le bol jaune.
-enfant-m|Parking pommes.
-maman|Vous avez bien servi.
+          <t>narrateur|La voiture se gare contre le bol.
+enfant-m|Cargaison livrée.
+papa|Vous avez fait le voyage.
+narrateur|Les assiettes sont vides, maintenant.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -13031,17 +13057,17 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>C'est après la sieste. La voiture avance entre les miettes, tout lent. Pas trop vite. J'ai encore sommeil. Une rondelle ? S'il te plaît. Merci. Raphaël arrête la voiture près de sa main.</t>
+          <t>Je pousse. Moi, je dis les arrêts. Raphaël pousse la voiture. Mila annonce. Prochain : les assiettes. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sami s'arrête près de après la sieste. Tom est rangé. Il y a des miettes sur la table. Sami pose sa tête un moment. On dit &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Je pousse. Moi, je dis les arrêts. Raphaël pousse la voiture. Mila annonce. Prochain : les assiettes. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Sami s'arrête près de après la sieste. Tom est rangé. Il y a des miettes sur la table. Sami pose sa tête un moment. On dit &lt;emphasis&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa. [pause]</t>
+          <t>Je pousse. Moi, je dis les arrêts. Raphaël pousse la voiture. Mila annonce. Prochain : les assiettes. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr"/>
@@ -13171,13 +13197,15 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|C'est après la sieste.
-narrateur|La voiture avance entre les miettes, tout lent.
-enfant-f|Pas trop vite. J'ai encore sommeil.
-maman|Une rondelle ?
-enfant-f|S'il te plaît.
-enfant-f|Merci.
-narrateur|Raphaël arrête la voiture près de sa main.</t>
+          <t>enfant-m|Je pousse.
+enfant-f|Moi, je dis les arrêts.
+narrateur|Raphaël pousse la voiture. Mila annonce.
+enfant-f|Prochain : les assiettes.
+narrateur|Le bol avance. Une rondelle tremble, puis tient.
+enfant-m|Terminus, les pommes.
+narrateur|Ils posent une rondelle chacun.
+enfant-f|On croque.
+narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
@@ -13209,17 +13237,17 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>La voiture fait un tout petit phare : le soleil. On reste au parking. Les pommes aussi. L'histoire est finie.</t>
+          <t>La voiture se gare contre le bol. Cargaison livrée. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La voiture se gare contre le bol. Cargaison livrée. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>La voiture se gare contre le bol. Cargaison livrée. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr"/>
@@ -13349,12 +13377,14 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|La voiture fait un tout petit phare : le soleil.
-papa|On reste au parking.
-enfant-m|Les pommes aussi.
+          <t>narrateur|La voiture se gare contre le bol.
+enfant-m|Cargaison livrée.
+papa|Vous avez fait le voyage.
+narrateur|Les assiettes sont vides, maintenant.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13379,17 +13409,17 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>C'est le soir. Raphaël gare la voiture sous la table. On reprend le manteau bientôt. Encore une pomme ? S'il te plaît, papa. La dernière rondelle. Merci.</t>
+          <t>Ensemble. Toi devant. Moi derrière. Ils poussent la voiture avec quatre mains. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sami se souvient de la voiture. Et de Tom. Et de le soir. Un galet est encore chaud. Sami plie un pull. On dit &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Ensemble. Toi devant. Moi derrière. Ils poussent la voiture avec quatre mains. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Sami se souvient de la voiture. Et de Tom. Et de le soir. Un galet est encore chaud. Sami plie un pull. On dit &lt;emphasis&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa. [pause]</t>
+          <t>Ensemble. Toi devant. Moi derrière. Ils poussent la voiture avec quatre mains. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr"/>
@@ -13519,13 +13549,14 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|C'est le soir.
-narrateur|Raphaël gare la voiture sous la table.
-maman|On reprend le manteau bientôt.
-enfant-f|Encore une pomme ?
-enfant-m|S'il te plaît, papa.
-narrateur|La dernière rondelle.
-enfant-f|Merci.</t>
+          <t>enfant-m|Ensemble.
+enfant-f|Toi devant. Moi derrière.
+narrateur|Ils poussent la voiture avec quatre mains.
+narrateur|Le bol avance. Une rondelle tremble, puis tient.
+enfant-m|Terminus, les pommes.
+narrateur|Ils posent une rondelle chacun.
+enfant-f|On croque.
+narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
@@ -13557,17 +13588,17 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Mila enfile son manteau. Il est presque sec. À demain. Merci pour les pommes. L'histoire est finie.</t>
+          <t>La voiture se gare contre le bol. Cargaison livrée. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La voiture se gare contre le bol. Cargaison livrée. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>La voiture se gare contre le bol. Cargaison livrée. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr"/>
@@ -13697,12 +13728,14 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|Mila enfile son manteau. Il est presque sec.
-enfant-m|À demain.
-enfant-f|Merci pour les pommes.
+          <t>narrateur|La voiture se gare contre le bol.
+enfant-m|Cargaison livrée.
+papa|Vous avez fait le voyage.
+narrateur|Les assiettes sont vides, maintenant.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13727,17 +13760,17 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Raphaël va près de la fenêtre, avec la voiture. La vitre a encore un peu de buée. Mila dessine une route du doigt. Le torchon, s'il te plaît. Pour la route ? Oui. La buée part. La rue apparaît. Merci, papa. Ta voiture peut y aller.</t>
+          <t>La voiture va près de la fenêtre. Mila dessine une route dans la buée. J'essuie le bas. La route du haut reste. La petite voiture suit le trait. Arrêt fenêtre.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sami dit &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt; à un copain Sami. Il dit s'il te plaît. Il dit merci. C'est après la sieste. Papa montre le geste, lentement. On dit bonjour. On dit s'il te plaît. On dit merci.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>La voiture va près de la fenêtre. Mila dessine une route dans la buée. J'essuie le bas. La route du haut reste. La petite voiture suit le trait. Arrêt fenêtre.</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Sami dit &lt;emphasis&gt;bonjour&lt;/emphasis&gt; à un copain Sami. Il dit s'il te plaît. Il dit merci. C'est après la sieste. Papa montre le geste, lentement. On dit bonjour. On dit s'il te plaît. On dit merci. [pause]</t>
+          <t>La voiture va près de la fenêtre. Mila dessine une route dans la buée. J'essuie le bas. La route du haut reste. La petite voiture suit le trait. Arrêt fenêtre.</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr"/>
@@ -13867,15 +13900,11 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël va près de la fenêtre, avec la voiture.
-narrateur|La vitre a encore un peu de buée.
-narrateur|Mila dessine une route du doigt.
-enfant-m|Le torchon, s'il te plaît.
-papa|Pour la route ?
-enfant-m|Oui.
-narrateur|La buée part. La rue apparaît.
-enfant-m|Merci, papa.
-enfant-f|Ta voiture peut y aller.</t>
+          <t>narrateur|La voiture va près de la fenêtre.
+narrateur|Mila dessine une route dans la buée.
+enfant-m|J'essuie le bas. La route du haut reste.
+narrateur|La petite voiture suit le trait.
+enfant-f|Arrêt fenêtre.</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
@@ -13907,17 +13936,17 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>C'est quel moment ? Le matin, après la sieste, ou le soir.</t>
+          <t>Qui pousse pour livrer ? Mila, Raphaël, ou tous les deux.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;On peut prendre le matin, après la sieste, ou le soir.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
+          <t>Qui pousse pour livrer ? Mila, Raphaël, ou tous les deux.</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;On peut prendre le matin, après la sieste, ou le soir.&lt;/slow&gt; [pause]</t>
+          <t>Qui pousse pour livrer ? Mila, Raphaël, ou tous les deux.</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr"/>
@@ -13935,7 +13964,7 @@
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>le matin</t>
+          <t>Mila</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -13945,7 +13974,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>après la sieste</t>
+          <t>Raphaël</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -13955,7 +13984,7 @@
       </c>
       <c r="Q73" s="2" t="inlineStr">
         <is>
-          <t>le soir</t>
+          <t>tous les deux</t>
         </is>
       </c>
       <c r="R73" s="2" t="inlineStr">
@@ -14071,10 +14100,11 @@
       <c r="AV73" s="2" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|C'est quel moment ?
-narrateur|Le matin, après la sieste, ou le soir.</t>
-        </is>
-      </c>
+          <t>narrateur|Qui pousse pour livrer ?
+narrateur|Mila, Raphaël, ou tous les deux.</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -14099,17 +14129,17 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. Une vraie voiture passe, tout loin. Raphaël suit la route sur la vitre. Rondelle du voyage ? S'il te plaît. Merci. On va au marché des pommes.</t>
+          <t>Je pousse. Moi, je garde les pommes. Mila pousse la voiture, tout autour de l'arrêt. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Avec le matin. Après Léa. Près de la voiture. Sami s'arrête. On attend son tour. Sami s'assoit près de papa. On dit &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Je pousse. Moi, je garde les pommes. Mila pousse la voiture, tout autour de l'arrêt. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Avec le matin. Après Léa. Près de la voiture. Sami s'arrête. On attend son tour. Sami s'assoit près de papa. On dit &lt;emphasis&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa. [pause]</t>
+          <t>Je pousse. Moi, je garde les pommes. Mila pousse la voiture, tout autour de l'arrêt. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr"/>
@@ -14239,13 +14269,14 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|C'est le matin.
-narrateur|Une vraie voiture passe, tout loin.
-narrateur|Raphaël suit la route sur la vitre.
-maman|Rondelle du voyage ?
-enfant-f|S'il te plaît.
-enfant-f|Merci.
-enfant-m|On va au marché des pommes.</t>
+          <t>enfant-f|Je pousse.
+enfant-m|Moi, je garde les pommes.
+narrateur|Mila pousse la voiture, tout autour de l'arrêt.
+narrateur|Le bol avance. Une rondelle tremble, puis tient.
+enfant-m|Terminus, les pommes.
+narrateur|Ils posent une rondelle chacun.
+enfant-f|On croque.
+narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
@@ -14277,17 +14308,17 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>La petite voiture s'arrête au bas de la vitre. Vous êtes arrivés. Les pommes aussi. L'histoire est finie.</t>
+          <t>La voiture s'arrête au bas de la vitre. Cargaison livrée. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La voiture s'arrête au bas de la vitre. Cargaison livrée. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>La voiture s'arrête au bas de la vitre. Cargaison livrée. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr"/>
@@ -14417,12 +14448,14 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|La petite voiture s'arrête au bas de la vitre.
-papa|Vous êtes arrivés.
-enfant-m|Les pommes aussi.
+          <t>narrateur|La voiture s'arrête au bas de la vitre.
+enfant-m|Cargaison livrée.
+papa|Vous avez fait le voyage.
+narrateur|Les assiettes sont vides, maintenant.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14447,17 +14480,17 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>C'est après la sieste. La rue est calme. Raphaël pose la voiture sur le rebord, sans la pousser. Une pomme, sans bouger ? S'il te plaît. Merci. Pour Mila.</t>
+          <t>Je pousse. Moi, je dis les arrêts. Raphaël pousse la voiture. Mila annonce. Prochain : les assiettes. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sami range Léa. après la sieste reste près de la voiture. La lumière est claire. Sami serre la main de papa. On dit &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Je pousse. Moi, je dis les arrêts. Raphaël pousse la voiture. Mila annonce. Prochain : les assiettes. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Sami range Léa. après la sieste reste près de la voiture. La lumière est claire. Sami serre la main de papa. On dit &lt;emphasis&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa. [pause]</t>
+          <t>Je pousse. Moi, je dis les arrêts. Raphaël pousse la voiture. Mila annonce. Prochain : les assiettes. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr"/>
@@ -14587,12 +14620,15 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|C'est après la sieste.
-narrateur|La rue est calme.
-narrateur|Raphaël pose la voiture sur le rebord, sans la pousser.
-papa|Une pomme, sans bouger ?
-enfant-m|S'il te plaît.
-enfant-m|Merci. Pour Mila.</t>
+          <t>enfant-m|Je pousse.
+enfant-f|Moi, je dis les arrêts.
+narrateur|Raphaël pousse la voiture. Mila annonce.
+enfant-f|Prochain : les assiettes.
+narrateur|Le bol avance. Une rondelle tremble, puis tient.
+enfant-m|Terminus, les pommes.
+narrateur|Ils posent une rondelle chacun.
+enfant-f|On croque.
+narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
@@ -14624,17 +14660,17 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>La voiture reste. Mila reste. Merci. On regarde seulement. C'est bien, parfois. L'histoire est finie.</t>
+          <t>La voiture s'arrête au bas de la vitre. Cargaison livrée. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La voiture s'arrête au bas de la vitre. Cargaison livrée. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>La voiture s'arrête au bas de la vitre. Cargaison livrée. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr"/>
@@ -14764,12 +14800,14 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|La voiture reste. Mila reste.
-enfant-f|Merci. On regarde seulement.
-maman|C'est bien, parfois.
+          <t>narrateur|La voiture s'arrête au bas de la vitre.
+enfant-m|Cargaison livrée.
+papa|Vous avez fait le voyage.
+narrateur|Les assiettes sont vides, maintenant.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14794,17 +14832,17 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>C'est le soir. Des phares passent sur la vitre. Raphaël descend la voiture. On rentre. Une pomme avant le manteau ? S'il te plaît. Merci.</t>
+          <t>Ensemble. Toi devant. Moi derrière. Ils poussent la voiture avec quatre mains. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;le soir est là. Léa aussi. la voiture reste dans le souvenir. La couverture est douce. Sami range encore un peu, près de papa. On dit &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Ensemble. Toi devant. Moi derrière. Ils poussent la voiture avec quatre mains. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>le soir est là. Léa aussi. la voiture reste dans le souvenir. La couverture est douce. Sami range encore un peu, près de papa. On dit &lt;emphasis&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa. [pause]</t>
+          <t>Ensemble. Toi devant. Moi derrière. Ils poussent la voiture avec quatre mains. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr"/>
@@ -14934,13 +14972,14 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|C'est le soir.
-narrateur|Des phares passent sur la vitre.
-narrateur|Raphaël descend la voiture.
-enfant-f|On rentre.
-maman|Une pomme avant le manteau ?
-enfant-m|S'il te plaît.
-enfant-m|Merci.</t>
+          <t>enfant-m|Ensemble.
+enfant-f|Toi devant. Moi derrière.
+narrateur|Ils poussent la voiture avec quatre mains.
+narrateur|Le bol avance. Une rondelle tremble, puis tient.
+enfant-m|Terminus, les pommes.
+narrateur|Ils posent une rondelle chacun.
+enfant-f|On croque.
+narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
@@ -14972,17 +15011,17 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Mila reprend son manteau. À demain, la route. La voiture est au garage, sous la fenêtre. L'histoire est finie.</t>
+          <t>La voiture s'arrête au bas de la vitre. Cargaison livrée. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La voiture s'arrête au bas de la vitre. Cargaison livrée. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>La voiture s'arrête au bas de la vitre. Cargaison livrée. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr"/>
@@ -15112,12 +15151,14 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|Mila reprend son manteau.
-enfant-m|À demain, la route.
-papa|La voiture est au garage, sous la fenêtre.
+          <t>narrateur|La voiture s'arrête au bas de la vitre.
+enfant-m|Cargaison livrée.
+papa|Vous avez fait le voyage.
+narrateur|Les assiettes sont vides, maintenant.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -15142,17 +15183,17 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Raphaël glisse la voiture près du tabouret. Mila s'assoit. Les pieds balancent. Je monte la voiture ? S'il te plaît, tout doux. Il pose la voiture sur le bois, près d'elle. Merci, Mila. Le bol, à votre hauteur ? S'il te plaît. Merci.</t>
+          <t>La voiture arrive au tabouret. Je monte la voiture, tout doux ? Oui. Sur le bois. Il pose la voiture près d'elle. Le bol suit. Parking haut.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sami dit &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt; à un copain Sami. Il dit s'il te plaît. Il dit merci. C'est le soir. Papa dit : je suis là. On dit bonjour. On dit s'il te plaît. On dit merci.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>La voiture arrive au tabouret. Je monte la voiture, tout doux ? Oui. Sur le bois. Il pose la voiture près d'elle. Le bol suit. Parking haut.</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Sami dit &lt;emphasis&gt;bonjour&lt;/emphasis&gt; à un copain Sami. Il dit s'il te plaît. Il dit merci. C'est le soir. Papa dit : je suis là. On dit bonjour. On dit s'il te plaît. On dit merci. [pause]</t>
+          <t>La voiture arrive au tabouret. Je monte la voiture, tout doux ? Oui. Sur le bois. Il pose la voiture près d'elle. Le bol suit. Parking haut.</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr"/>
@@ -15282,15 +15323,11 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël glisse la voiture près du tabouret.
-narrateur|Mila s'assoit. Les pieds balancent.
-enfant-m|Je monte la voiture ?
-enfant-f|S'il te plaît, tout doux.
-narrateur|Il pose la voiture sur le bois, près d'elle.
-enfant-m|Merci, Mila.
-maman|Le bol, à votre hauteur ?
-enfant-m|S'il te plaît.
-enfant-m|Merci.</t>
+          <t>narrateur|La voiture arrive au tabouret.
+enfant-m|Je monte la voiture, tout doux ?
+enfant-f|Oui. Sur le bois.
+narrateur|Il pose la voiture près d'elle. Le bol suit.
+enfant-f|Parking haut.</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
@@ -15322,17 +15359,17 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>C'est quel moment ? Le matin, après la sieste, ou le soir.</t>
+          <t>Qui pousse pour livrer ? Mila, Raphaël, ou tous les deux.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;On peut prendre le matin, après la sieste, ou le soir.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
+          <t>Qui pousse pour livrer ? Mila, Raphaël, ou tous les deux.</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;On peut prendre le matin, après la sieste, ou le soir.&lt;/slow&gt; [pause]</t>
+          <t>Qui pousse pour livrer ? Mila, Raphaël, ou tous les deux.</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr"/>
@@ -15350,7 +15387,7 @@
       <c r="L81" s="2" t="inlineStr"/>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>le matin</t>
+          <t>Mila</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -15360,7 +15397,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>après la sieste</t>
+          <t>Raphaël</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -15370,7 +15407,7 @@
       </c>
       <c r="Q81" s="2" t="inlineStr">
         <is>
-          <t>le soir</t>
+          <t>tous les deux</t>
         </is>
       </c>
       <c r="R81" s="2" t="inlineStr">
@@ -15486,10 +15523,11 @@
       <c r="AV81" s="2" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|C'est quel moment ?
-narrateur|Le matin, après la sieste, ou le soir.</t>
-        </is>
-      </c>
+          <t>narrateur|Qui pousse pour livrer ?
+narrateur|Mila, Raphaël, ou tous les deux.</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15514,17 +15552,17 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. Le soleil fait un parking sur le tabouret. Raphaël gare la voiture dans le carré de lumière. Pommes du parking ? S'il te plaît. Merci. Une pour Raphaël.</t>
+          <t>Je pousse. Moi, je garde les pommes. Mila pousse la voiture, tout autour de l'arrêt. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sami rejoint le matin. Sami est rangé. la voiture est fini. Le vent est doux. Sami ferme la porte, tout doux. On dit &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Je pousse. Moi, je garde les pommes. Mila pousse la voiture, tout autour de l'arrêt. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint le matin. Sami est rangé. la voiture est fini. Le vent est doux. Sami ferme la porte, tout doux. On dit &lt;emphasis&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa. [pause]</t>
+          <t>Je pousse. Moi, je garde les pommes. Mila pousse la voiture, tout autour de l'arrêt. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr"/>
@@ -15654,12 +15692,14 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|C'est le matin.
-narrateur|Le soleil fait un parking sur le tabouret.
-narrateur|Raphaël gare la voiture dans le carré de lumière.
-papa|Pommes du parking ?
-enfant-f|S'il te plaît.
-enfant-f|Merci. Une pour Raphaël.</t>
+          <t>enfant-f|Je pousse.
+enfant-m|Moi, je garde les pommes.
+narrateur|Mila pousse la voiture, tout autour de l'arrêt.
+narrateur|Le bol avance. Une rondelle tremble, puis tient.
+enfant-m|Terminus, les pommes.
+narrateur|Ils posent une rondelle chacun.
+enfant-f|On croque.
+narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
@@ -15691,17 +15731,17 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Ils croquent, les pieds en l'air. Belle place. Vous avez bien demandé le bol. L'histoire est finie.</t>
+          <t>La voiture descend du tabouret. Cargaison livrée. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La voiture descend du tabouret. Cargaison livrée. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>La voiture descend du tabouret. Cargaison livrée. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr"/>
@@ -15831,12 +15871,14 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|Ils croquent, les pieds en l'air.
-enfant-m|Belle place.
-maman|Vous avez bien demandé le bol.
+          <t>narrateur|La voiture descend du tabouret.
+enfant-m|Cargaison livrée.
+papa|Vous avez fait le voyage.
+narrateur|Les assiettes sont vides, maintenant.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15861,17 +15903,17 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>C'est après la sieste. La voiture ne roule plus. Elle attend. Moi aussi, j'attends. Une rondelle, alors. S'il te plaît. Merci. On partage.</t>
+          <t>Je pousse. Moi, je dis les arrêts. Raphaël pousse la voiture. Mila annonce. Prochain : les assiettes. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Près de après la sieste. Sami pose Sami. la voiture est derrière. Le sol est un peu froid. Sami montre après la sieste à papa. On dit &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Je pousse. Moi, je dis les arrêts. Raphaël pousse la voiture. Mila annonce. Prochain : les assiettes. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Près de après la sieste. Sami pose Sami. la voiture est derrière. Le sol est un peu froid. Sami montre après la sieste à papa. On dit &lt;emphasis&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa. [pause]</t>
+          <t>Je pousse. Moi, je dis les arrêts. Raphaël pousse la voiture. Mila annonce. Prochain : les assiettes. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr"/>
@@ -16001,12 +16043,15 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|C'est après la sieste.
-narrateur|La voiture ne roule plus. Elle attend.
-enfant-f|Moi aussi, j'attends.
-papa|Une rondelle, alors.
-enfant-m|S'il te plaît.
-enfant-m|Merci. On partage.</t>
+          <t>enfant-m|Je pousse.
+enfant-f|Moi, je dis les arrêts.
+narrateur|Raphaël pousse la voiture. Mila annonce.
+enfant-f|Prochain : les assiettes.
+narrateur|Le bol avance. Une rondelle tremble, puis tient.
+enfant-m|Terminus, les pommes.
+narrateur|Ils posent une rondelle chacun.
+enfant-f|On croque.
+narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
@@ -16038,17 +16083,17 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Deux rondelles. Deux sourires. Le tabouret a tenu le goûter. Merci, tabouret. L'histoire est finie.</t>
+          <t>La voiture descend du tabouret. Cargaison livrée. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La voiture descend du tabouret. Cargaison livrée. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>La voiture descend du tabouret. Cargaison livrée. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr"/>
@@ -16178,12 +16223,14 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|Deux rondelles. Deux sourires.
-maman|Le tabouret a tenu le goûter.
-enfant-f|Merci, tabouret.
+          <t>narrateur|La voiture descend du tabouret.
+enfant-m|Cargaison livrée.
+papa|Vous avez fait le voyage.
+narrateur|Les assiettes sont vides, maintenant.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -16208,17 +16255,17 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>C'est le soir. Raphaël descend la voiture du tabouret. Je descends aussi. Merci d'avoir gardé la place. Manteau ? S'il te plaît. Merci. Et une pomme pour la route.</t>
+          <t>Ensemble. Toi devant. Moi derrière. Ils poussent la voiture avec quatre mains. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sami montre le soir. Papa a vu la voiture. Et Sami. On souffle doucement. Sami range la voiture dans sa tête, comme un souvenir. On dit &lt;emphasis level="moderate"&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Ensemble. Toi devant. Moi derrière. Ils poussent la voiture avec quatre mains. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Sami montre le soir. Papa a vu la voiture. Et Sami. On souffle doucement. Sami range la voiture dans sa tête, comme un souvenir. On dit &lt;emphasis&gt;bonjour&lt;/emphasis&gt;. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa. [pause]</t>
+          <t>Ensemble. Toi devant. Moi derrière. Ils poussent la voiture avec quatre mains. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr"/>
@@ -16348,14 +16395,14 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|C'est le soir.
-narrateur|Raphaël descend la voiture du tabouret.
-enfant-f|Je descends aussi.
-enfant-m|Merci d'avoir gardé la place.
-maman|Manteau ?
-enfant-f|S'il te plaît.
-enfant-f|Merci.
-papa|Et une pomme pour la route.</t>
+          <t>enfant-m|Ensemble.
+enfant-f|Toi devant. Moi derrière.
+narrateur|Ils poussent la voiture avec quatre mains.
+narrateur|Le bol avance. Une rondelle tremble, puis tient.
+enfant-m|Terminus, les pommes.
+narrateur|Ils posent une rondelle chacun.
+enfant-f|On croque.
+narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
@@ -16387,17 +16434,17 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Mila enfile son manteau. Il sent encore un peu la pluie. À demain. Merci pour les pommes et la voiture. L'histoire est finie.</t>
+          <t>La voiture descend du tabouret. Cargaison livrée. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La voiture descend du tabouret. Cargaison livrée. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>La voiture descend du tabouret. Cargaison livrée. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr"/>
@@ -16527,12 +16574,14 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|Mila enfile son manteau. Il sent encore un peu la pluie.
-enfant-m|À demain.
-enfant-f|Merci pour les pommes et la voiture.
+          <t>narrateur|La voiture descend du tabouret.
+enfant-m|Cargaison livrée.
+papa|Vous avez fait le voyage.
+narrateur|Les assiettes sont vides, maintenant.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -16551,7 +16600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16617,6 +16666,13 @@
       <c r="A9" t="inlineStr">
         <is>
           <t>F-NAR-010…015 texte : désir partager pommes, Mila D16, labels table/fenêtre/tabouret, chaîne Q bonjour/s'il te plaît/merci</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>avis 88534be : voyage des pommes, T3 qui pousse, COL.ECO.001 retiré, SSML=texte</t>
         </is>
       </c>
     </row>
